--- a/Sep_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
+++ b/Sep_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C9F3BF8-66A5-400F-B3E0-737A38DF9C67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06F41BDC-7584-49EB-AD7A-44DD747F79D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3647,18 +3647,18 @@
         <v>26</v>
       </c>
       <c r="B2" s="24">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C2" s="63">
         <f>+B2/A2</f>
-        <v>0.15384615384615385</v>
+        <v>0.23076923076923078</v>
       </c>
       <c r="D2" s="62">
         <f>+A2-B2</f>
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F2" s="94">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="G2" s="108" t="s">
         <v>38</v>
@@ -3753,34 +3753,34 @@
         <v>600</v>
       </c>
       <c r="H4" s="31">
-        <f>5+36</f>
-        <v>41</v>
+        <f>5+36+19+15</f>
+        <v>75</v>
       </c>
       <c r="I4" s="68">
         <f t="shared" ref="I4:I31" si="0">H4/G4</f>
-        <v>6.8333333333333329E-2</v>
+        <v>0.125</v>
       </c>
       <c r="J4" s="30">
         <v>550</v>
       </c>
       <c r="K4" s="8">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="L4" s="87">
         <f t="shared" ref="L4:L29" si="1">K4/J4</f>
-        <v>9.0909090909090912E-2</v>
+        <v>0.12545454545454546</v>
       </c>
       <c r="M4" s="8">
         <f t="shared" ref="M4:M6" si="2">J4-K4</f>
-        <v>500</v>
+        <v>481</v>
       </c>
       <c r="N4" s="10">
         <f t="shared" ref="N4:N6" si="3">M4/$D$2</f>
-        <v>22.727272727272727</v>
+        <v>24.05</v>
       </c>
       <c r="O4" s="69">
         <f t="shared" ref="O4:P12" si="4">K4/H4</f>
-        <v>1.2195121951219512</v>
+        <v>0.92</v>
       </c>
       <c r="P4" s="33">
         <v>3</v>
@@ -3810,34 +3810,34 @@
         <v>600</v>
       </c>
       <c r="H5" s="12">
-        <f>23+33</f>
-        <v>56</v>
+        <f>23+33+16+19</f>
+        <v>91</v>
       </c>
       <c r="I5" s="70">
         <f t="shared" si="0"/>
-        <v>9.3333333333333338E-2</v>
+        <v>0.15166666666666667</v>
       </c>
       <c r="J5" s="11">
         <v>450</v>
       </c>
       <c r="K5" s="12">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="L5" s="71">
         <f t="shared" si="1"/>
-        <v>6.6666666666666666E-2</v>
+        <v>0.11333333333333333</v>
       </c>
       <c r="M5" s="12">
         <f t="shared" si="2"/>
-        <v>420</v>
+        <v>399</v>
       </c>
       <c r="N5" s="14">
         <f t="shared" si="3"/>
-        <v>19.09090909090909</v>
+        <v>19.95</v>
       </c>
       <c r="O5" s="98">
         <f t="shared" si="4"/>
-        <v>0.5357142857142857</v>
+        <v>0.56043956043956045</v>
       </c>
       <c r="P5" s="33">
         <v>3</v>
@@ -3867,38 +3867,38 @@
         <v>600</v>
       </c>
       <c r="H6" s="12">
-        <f>6+16</f>
-        <v>22</v>
+        <f>6+16+5+3</f>
+        <v>30</v>
       </c>
       <c r="I6" s="70">
         <f t="shared" si="0"/>
-        <v>3.6666666666666667E-2</v>
+        <v>0.05</v>
       </c>
       <c r="J6" s="11">
         <v>550</v>
       </c>
       <c r="K6" s="12">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="L6" s="71">
         <f t="shared" si="1"/>
-        <v>5.0909090909090911E-2</v>
+        <v>6.9090909090909092E-2</v>
       </c>
       <c r="M6" s="12">
         <f t="shared" si="2"/>
-        <v>522</v>
+        <v>512</v>
       </c>
       <c r="N6" s="14">
         <f t="shared" si="3"/>
-        <v>23.727272727272727</v>
+        <v>25.6</v>
       </c>
       <c r="O6" s="72">
         <f t="shared" si="4"/>
-        <v>1.2727272727272727</v>
+        <v>1.2666666666666666</v>
       </c>
       <c r="P6" s="14">
         <f t="shared" si="4"/>
-        <v>1.3884297520661157</v>
+        <v>1.3818181818181818</v>
       </c>
       <c r="Q6" s="34"/>
     </row>
@@ -3925,38 +3925,38 @@
         <v>600</v>
       </c>
       <c r="H7" s="12">
-        <f>2+9</f>
-        <v>11</v>
+        <f>2+9+17+9</f>
+        <v>37</v>
       </c>
       <c r="I7" s="70">
         <f t="shared" si="0"/>
-        <v>1.8333333333333333E-2</v>
+        <v>6.1666666666666668E-2</v>
       </c>
       <c r="J7" s="11">
         <v>400</v>
       </c>
       <c r="K7" s="12">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="L7" s="71">
         <f t="shared" si="1"/>
-        <v>4.2500000000000003E-2</v>
+        <v>0.10249999999999999</v>
       </c>
       <c r="M7" s="12">
         <f t="shared" ref="M7:M31" si="5">J7-K7</f>
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="N7" s="14">
         <f t="shared" ref="N7:N31" si="6">M7/$D$2</f>
-        <v>17.40909090909091</v>
+        <v>17.95</v>
       </c>
       <c r="O7" s="72">
         <f t="shared" si="4"/>
-        <v>1.5454545454545454</v>
+        <v>1.1081081081081081</v>
       </c>
       <c r="P7" s="14">
         <f t="shared" si="4"/>
-        <v>2.3181818181818183</v>
+        <v>1.6621621621621621</v>
       </c>
       <c r="Q7" s="34"/>
     </row>
@@ -3983,38 +3983,38 @@
         <v>600</v>
       </c>
       <c r="H8" s="12">
-        <f>4+7</f>
-        <v>11</v>
+        <f>4+7+6+6</f>
+        <v>23</v>
       </c>
       <c r="I8" s="70">
         <f t="shared" si="0"/>
-        <v>1.8333333333333333E-2</v>
+        <v>3.833333333333333E-2</v>
       </c>
       <c r="J8" s="11">
         <v>575</v>
       </c>
       <c r="K8" s="12">
-        <v>12.5</v>
+        <v>28</v>
       </c>
       <c r="L8" s="71">
         <f t="shared" si="1"/>
-        <v>2.1739130434782608E-2</v>
+        <v>4.8695652173913043E-2</v>
       </c>
       <c r="M8" s="12">
         <f t="shared" si="5"/>
-        <v>562.5</v>
+        <v>547</v>
       </c>
       <c r="N8" s="14">
         <f t="shared" si="6"/>
-        <v>25.568181818181817</v>
+        <v>27.35</v>
       </c>
       <c r="O8" s="72">
         <f t="shared" si="4"/>
-        <v>1.1363636363636365</v>
+        <v>1.2173913043478262</v>
       </c>
       <c r="P8" s="14">
         <f t="shared" si="4"/>
-        <v>1.1857707509881423</v>
+        <v>1.2703213610586013</v>
       </c>
       <c r="Q8" s="34"/>
     </row>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="N9" s="14">
         <f t="shared" si="6"/>
-        <v>25</v>
+        <v>27.5</v>
       </c>
       <c r="O9" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4094,38 +4094,38 @@
         <v>200</v>
       </c>
       <c r="H10" s="12">
-        <f>2+7</f>
-        <v>9</v>
+        <f>2+7+1+6</f>
+        <v>16</v>
       </c>
       <c r="I10" s="70">
         <f t="shared" si="0"/>
-        <v>4.4999999999999998E-2</v>
+        <v>0.08</v>
       </c>
       <c r="J10" s="11">
         <v>3000</v>
       </c>
       <c r="K10" s="12">
-        <v>205</v>
+        <v>288</v>
       </c>
       <c r="L10" s="71">
         <f t="shared" si="1"/>
-        <v>6.8333333333333329E-2</v>
+        <v>9.6000000000000002E-2</v>
       </c>
       <c r="M10" s="12">
         <f t="shared" si="5"/>
-        <v>2795</v>
+        <v>2712</v>
       </c>
       <c r="N10" s="14">
         <f t="shared" si="6"/>
-        <v>127.04545454545455</v>
+        <v>135.6</v>
       </c>
       <c r="O10" s="72">
         <f t="shared" si="4"/>
-        <v>22.777777777777779</v>
+        <v>18</v>
       </c>
       <c r="P10" s="14">
         <f t="shared" si="4"/>
-        <v>1.5185185185185184</v>
+        <v>1.2</v>
       </c>
       <c r="Q10" s="34"/>
     </row>
@@ -4170,7 +4170,7 @@
       </c>
       <c r="N11" s="14">
         <f t="shared" si="6"/>
-        <v>29.545454545454547</v>
+        <v>32.5</v>
       </c>
       <c r="O11" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="N12" s="14">
         <f t="shared" si="6"/>
-        <v>25</v>
+        <v>27.5</v>
       </c>
       <c r="O12" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="N13" s="14">
         <f t="shared" ref="N13:N15" si="9">M13/$D$2</f>
-        <v>20.454545454545453</v>
+        <v>22.5</v>
       </c>
       <c r="O13" s="72" t="e">
         <f t="shared" ref="O13:O16" si="10">K13/H13</f>
@@ -4308,16 +4308,22 @@
         <v>44</v>
       </c>
       <c r="G14" s="11"/>
-      <c r="H14" s="12"/>
+      <c r="H14" s="12">
+        <v>1</v>
+      </c>
       <c r="I14" s="70" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J14" s="11"/>
-      <c r="K14" s="12"/>
-      <c r="L14" s="71" t="e">
+      <c r="J14" s="11">
+        <v>100</v>
+      </c>
+      <c r="K14" s="12">
+        <v>100</v>
+      </c>
+      <c r="L14" s="71">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
       <c r="M14" s="12">
         <f t="shared" si="5"/>
@@ -4327,9 +4333,9 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="O14" s="72" t="e">
+      <c r="O14" s="72">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>100</v>
       </c>
       <c r="P14" s="14" t="e">
         <f t="shared" si="11"/>
@@ -4530,35 +4536,35 @@
       </c>
       <c r="H19" s="40">
         <f>SUM(H4:H18)</f>
-        <v>150</v>
+        <v>273</v>
       </c>
       <c r="I19" s="79">
         <f t="shared" si="0"/>
-        <v>2.6785714285714284E-2</v>
+        <v>4.8750000000000002E-2</v>
       </c>
       <c r="J19" s="80">
         <f>SUM(J4:J18)</f>
-        <v>7725</v>
+        <v>7825</v>
       </c>
       <c r="K19" s="80">
         <f>SUM(K4:K18)</f>
-        <v>342.5</v>
+        <v>615</v>
       </c>
       <c r="L19" s="82">
         <f>K19/J19</f>
-        <v>4.4336569579288027E-2</v>
+        <v>7.8594249201277958E-2</v>
       </c>
       <c r="M19" s="81">
         <f t="shared" si="5"/>
-        <v>7382.5</v>
+        <v>7210</v>
       </c>
       <c r="N19" s="83">
         <f t="shared" si="6"/>
-        <v>335.56818181818181</v>
+        <v>360.5</v>
       </c>
       <c r="O19" s="84">
         <f>K19/H19</f>
-        <v>2.2833333333333332</v>
+        <v>2.2527472527472527</v>
       </c>
       <c r="P19" s="43" t="e">
         <f>AVERAGE(P4:P12)</f>
@@ -4611,7 +4617,7 @@
       </c>
       <c r="N20" s="10">
         <f t="shared" si="6"/>
-        <v>21.136363636363637</v>
+        <v>23.25</v>
       </c>
       <c r="O20" s="86">
         <f t="shared" ref="O20:O24" si="13">K20/H20</f>
@@ -4667,7 +4673,7 @@
       </c>
       <c r="N21" s="14">
         <f t="shared" si="6"/>
-        <v>21.227272727272727</v>
+        <v>23.35</v>
       </c>
       <c r="O21" s="72">
         <f t="shared" si="13"/>
@@ -4723,7 +4729,7 @@
       </c>
       <c r="N22" s="14">
         <f t="shared" si="6"/>
-        <v>21.09090909090909</v>
+        <v>23.2</v>
       </c>
       <c r="O22" s="72">
         <f t="shared" si="13"/>
@@ -4779,7 +4785,7 @@
       </c>
       <c r="N23" s="14">
         <f t="shared" si="6"/>
-        <v>21.5</v>
+        <v>23.65</v>
       </c>
       <c r="O23" s="72">
         <f t="shared" si="13"/>
@@ -4835,7 +4841,7 @@
       </c>
       <c r="N24" s="77">
         <f t="shared" si="6"/>
-        <v>22</v>
+        <v>24.2</v>
       </c>
       <c r="O24" s="78">
         <f t="shared" si="13"/>
@@ -4891,7 +4897,7 @@
       </c>
       <c r="N25" s="83">
         <f t="shared" si="6"/>
-        <v>106.95454545454545</v>
+        <v>117.65</v>
       </c>
       <c r="O25" s="84">
         <f>K25/H25</f>
@@ -4948,7 +4954,7 @@
       </c>
       <c r="N26" s="10">
         <f t="shared" si="6"/>
-        <v>28</v>
+        <v>30.8</v>
       </c>
       <c r="O26" s="86">
         <f t="shared" ref="O26:O29" si="15">K26/H26</f>
@@ -5004,7 +5010,7 @@
       </c>
       <c r="N27" s="14">
         <f t="shared" si="6"/>
-        <v>25.727272727272727</v>
+        <v>28.3</v>
       </c>
       <c r="O27" s="72">
         <f t="shared" si="15"/>
@@ -5060,7 +5066,7 @@
       </c>
       <c r="N28" s="14">
         <f t="shared" si="6"/>
-        <v>26.09090909090909</v>
+        <v>28.7</v>
       </c>
       <c r="O28" s="72">
         <f t="shared" si="15"/>
@@ -5116,7 +5122,7 @@
       </c>
       <c r="N29" s="77">
         <f t="shared" si="6"/>
-        <v>27.818181818181817</v>
+        <v>30.6</v>
       </c>
       <c r="O29" s="78">
         <f t="shared" si="15"/>
@@ -5172,7 +5178,7 @@
       </c>
       <c r="N30" s="83">
         <f t="shared" si="6"/>
-        <v>107.63636363636364</v>
+        <v>118.4</v>
       </c>
       <c r="O30" s="84">
         <f>K30/H30</f>
@@ -5201,35 +5207,35 @@
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31:K31" si="17">+H30+H25+H19</f>
-        <v>351</v>
+        <v>474</v>
       </c>
       <c r="I31" s="88">
         <f t="shared" si="0"/>
-        <v>5.8016528925619835E-2</v>
+        <v>7.8347107438016525E-2</v>
       </c>
       <c r="J31" s="89">
         <f t="shared" si="17"/>
-        <v>12725</v>
+        <v>12825</v>
       </c>
       <c r="K31" s="90">
         <f t="shared" si="17"/>
-        <v>621.5</v>
+        <v>894</v>
       </c>
       <c r="L31" s="91">
         <f>K31/J31</f>
-        <v>4.8840864440078582E-2</v>
+        <v>6.9707602339181288E-2</v>
       </c>
       <c r="M31" s="90">
         <f t="shared" si="5"/>
-        <v>12103.5</v>
+        <v>11931</v>
       </c>
       <c r="N31" s="92">
         <f t="shared" si="6"/>
-        <v>550.15909090909088</v>
+        <v>596.54999999999995</v>
       </c>
       <c r="O31" s="93">
         <f>K31/H31</f>
-        <v>1.7706552706552707</v>
+        <v>1.8860759493670887</v>
       </c>
       <c r="P31" s="23" t="e">
         <f>AVERAGE(P30,P19,P25)</f>

--- a/Sep_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
+++ b/Sep_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06F41BDC-7584-49EB-AD7A-44DD747F79D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCD7BE8E-6E5B-4EA4-B21F-3D92AA2A8576}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3647,18 +3647,18 @@
         <v>26</v>
       </c>
       <c r="B2" s="24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="63">
         <f>+B2/A2</f>
-        <v>0.23076923076923078</v>
+        <v>0.26923076923076922</v>
       </c>
       <c r="D2" s="62">
         <f>+A2-B2</f>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F2" s="94">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="G2" s="108" t="s">
         <v>38</v>
@@ -3753,34 +3753,34 @@
         <v>600</v>
       </c>
       <c r="H4" s="31">
-        <f>5+36+19+15</f>
-        <v>75</v>
+        <f>5+36+19+15+11</f>
+        <v>86</v>
       </c>
       <c r="I4" s="68">
         <f t="shared" ref="I4:I31" si="0">H4/G4</f>
-        <v>0.125</v>
+        <v>0.14333333333333334</v>
       </c>
       <c r="J4" s="30">
         <v>550</v>
       </c>
       <c r="K4" s="8">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="L4" s="87">
         <f t="shared" ref="L4:L29" si="1">K4/J4</f>
-        <v>0.12545454545454546</v>
+        <v>0.13636363636363635</v>
       </c>
       <c r="M4" s="8">
         <f t="shared" ref="M4:M6" si="2">J4-K4</f>
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="N4" s="10">
         <f t="shared" ref="N4:N6" si="3">M4/$D$2</f>
-        <v>24.05</v>
+        <v>25</v>
       </c>
       <c r="O4" s="69">
         <f t="shared" ref="O4:P12" si="4">K4/H4</f>
-        <v>0.92</v>
+        <v>0.87209302325581395</v>
       </c>
       <c r="P4" s="33">
         <v>3</v>
@@ -3810,34 +3810,34 @@
         <v>600</v>
       </c>
       <c r="H5" s="12">
-        <f>23+33+16+19</f>
-        <v>91</v>
+        <f>23+33+16+19+14</f>
+        <v>105</v>
       </c>
       <c r="I5" s="70">
         <f t="shared" si="0"/>
-        <v>0.15166666666666667</v>
+        <v>0.17499999999999999</v>
       </c>
       <c r="J5" s="11">
         <v>450</v>
       </c>
       <c r="K5" s="12">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="L5" s="71">
         <f t="shared" si="1"/>
-        <v>0.11333333333333333</v>
+        <v>0.13333333333333333</v>
       </c>
       <c r="M5" s="12">
         <f t="shared" si="2"/>
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="N5" s="14">
         <f t="shared" si="3"/>
-        <v>19.95</v>
+        <v>20.526315789473685</v>
       </c>
       <c r="O5" s="98">
         <f t="shared" si="4"/>
-        <v>0.56043956043956045</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P5" s="33">
         <v>3</v>
@@ -3867,38 +3867,38 @@
         <v>600</v>
       </c>
       <c r="H6" s="12">
-        <f>6+16+5+3</f>
-        <v>30</v>
+        <f>6+16+5+3+11</f>
+        <v>41</v>
       </c>
       <c r="I6" s="70">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>6.8333333333333329E-2</v>
       </c>
       <c r="J6" s="11">
         <v>550</v>
       </c>
       <c r="K6" s="12">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="L6" s="71">
         <f t="shared" si="1"/>
-        <v>6.9090909090909092E-2</v>
+        <v>8.727272727272728E-2</v>
       </c>
       <c r="M6" s="12">
         <f t="shared" si="2"/>
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="N6" s="14">
         <f t="shared" si="3"/>
-        <v>25.6</v>
+        <v>26.421052631578949</v>
       </c>
       <c r="O6" s="72">
         <f t="shared" si="4"/>
-        <v>1.2666666666666666</v>
+        <v>1.1707317073170731</v>
       </c>
       <c r="P6" s="14">
         <f t="shared" si="4"/>
-        <v>1.3818181818181818</v>
+        <v>1.2771618625277164</v>
       </c>
       <c r="Q6" s="34"/>
     </row>
@@ -3925,38 +3925,38 @@
         <v>600</v>
       </c>
       <c r="H7" s="12">
-        <f>2+9+17+9</f>
-        <v>37</v>
+        <f>2+9+17+9+5</f>
+        <v>42</v>
       </c>
       <c r="I7" s="70">
         <f t="shared" si="0"/>
-        <v>6.1666666666666668E-2</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="J7" s="11">
         <v>400</v>
       </c>
       <c r="K7" s="12">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="L7" s="71">
         <f t="shared" si="1"/>
-        <v>0.10249999999999999</v>
+        <v>0.11749999999999999</v>
       </c>
       <c r="M7" s="12">
         <f t="shared" ref="M7:M31" si="5">J7-K7</f>
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="N7" s="14">
         <f t="shared" ref="N7:N31" si="6">M7/$D$2</f>
-        <v>17.95</v>
+        <v>18.578947368421051</v>
       </c>
       <c r="O7" s="72">
         <f t="shared" si="4"/>
-        <v>1.1081081081081081</v>
+        <v>1.1190476190476191</v>
       </c>
       <c r="P7" s="14">
         <f t="shared" si="4"/>
-        <v>1.6621621621621621</v>
+        <v>1.6785714285714284</v>
       </c>
       <c r="Q7" s="34"/>
     </row>
@@ -3983,38 +3983,38 @@
         <v>600</v>
       </c>
       <c r="H8" s="12">
-        <f>4+7+6+6</f>
-        <v>23</v>
+        <f>4+7+6+6+11</f>
+        <v>34</v>
       </c>
       <c r="I8" s="70">
         <f t="shared" si="0"/>
-        <v>3.833333333333333E-2</v>
+        <v>5.6666666666666664E-2</v>
       </c>
       <c r="J8" s="11">
         <v>575</v>
       </c>
       <c r="K8" s="12">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="L8" s="71">
         <f t="shared" si="1"/>
-        <v>4.8695652173913043E-2</v>
+        <v>6.4347826086956522E-2</v>
       </c>
       <c r="M8" s="12">
         <f t="shared" si="5"/>
-        <v>547</v>
+        <v>538</v>
       </c>
       <c r="N8" s="14">
         <f t="shared" si="6"/>
-        <v>27.35</v>
+        <v>28.315789473684209</v>
       </c>
       <c r="O8" s="72">
         <f t="shared" si="4"/>
-        <v>1.2173913043478262</v>
+        <v>1.088235294117647</v>
       </c>
       <c r="P8" s="14">
         <f t="shared" si="4"/>
-        <v>1.2703213610586013</v>
+        <v>1.1355498721227621</v>
       </c>
       <c r="Q8" s="34"/>
     </row>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="N9" s="14">
         <f t="shared" si="6"/>
-        <v>27.5</v>
+        <v>28.94736842105263</v>
       </c>
       <c r="O9" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4094,38 +4094,38 @@
         <v>200</v>
       </c>
       <c r="H10" s="12">
-        <f>2+7+1+6</f>
-        <v>16</v>
+        <f>2+7+1+6+5</f>
+        <v>21</v>
       </c>
       <c r="I10" s="70">
         <f t="shared" si="0"/>
-        <v>0.08</v>
+        <v>0.105</v>
       </c>
       <c r="J10" s="11">
         <v>3000</v>
       </c>
       <c r="K10" s="12">
-        <v>288</v>
+        <v>334</v>
       </c>
       <c r="L10" s="71">
         <f t="shared" si="1"/>
-        <v>9.6000000000000002E-2</v>
+        <v>0.11133333333333334</v>
       </c>
       <c r="M10" s="12">
         <f t="shared" si="5"/>
-        <v>2712</v>
+        <v>2666</v>
       </c>
       <c r="N10" s="14">
         <f t="shared" si="6"/>
-        <v>135.6</v>
+        <v>140.31578947368422</v>
       </c>
       <c r="O10" s="72">
         <f t="shared" si="4"/>
-        <v>18</v>
+        <v>15.904761904761905</v>
       </c>
       <c r="P10" s="14">
         <f t="shared" si="4"/>
-        <v>1.2</v>
+        <v>1.0603174603174603</v>
       </c>
       <c r="Q10" s="34"/>
     </row>
@@ -4170,7 +4170,7 @@
       </c>
       <c r="N11" s="14">
         <f t="shared" si="6"/>
-        <v>32.5</v>
+        <v>34.210526315789473</v>
       </c>
       <c r="O11" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="N12" s="14">
         <f t="shared" si="6"/>
-        <v>27.5</v>
+        <v>28.94736842105263</v>
       </c>
       <c r="O12" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="N13" s="14">
         <f t="shared" ref="N13:N15" si="9">M13/$D$2</f>
-        <v>22.5</v>
+        <v>23.684210526315791</v>
       </c>
       <c r="O13" s="72" t="e">
         <f t="shared" ref="O13:O16" si="10">K13/H13</f>
@@ -4536,11 +4536,11 @@
       </c>
       <c r="H19" s="40">
         <f>SUM(H4:H18)</f>
-        <v>273</v>
+        <v>330</v>
       </c>
       <c r="I19" s="79">
         <f t="shared" si="0"/>
-        <v>4.8750000000000002E-2</v>
+        <v>5.8928571428571427E-2</v>
       </c>
       <c r="J19" s="80">
         <f>SUM(J4:J18)</f>
@@ -4548,23 +4548,23 @@
       </c>
       <c r="K19" s="80">
         <f>SUM(K4:K18)</f>
-        <v>615</v>
+        <v>701</v>
       </c>
       <c r="L19" s="82">
         <f>K19/J19</f>
-        <v>7.8594249201277958E-2</v>
+        <v>8.9584664536741215E-2</v>
       </c>
       <c r="M19" s="81">
         <f t="shared" si="5"/>
-        <v>7210</v>
+        <v>7124</v>
       </c>
       <c r="N19" s="83">
         <f t="shared" si="6"/>
-        <v>360.5</v>
+        <v>374.94736842105266</v>
       </c>
       <c r="O19" s="84">
         <f>K19/H19</f>
-        <v>2.2527472527472527</v>
+        <v>2.124242424242424</v>
       </c>
       <c r="P19" s="43" t="e">
         <f>AVERAGE(P4:P12)</f>
@@ -4617,7 +4617,7 @@
       </c>
       <c r="N20" s="10">
         <f t="shared" si="6"/>
-        <v>23.25</v>
+        <v>24.473684210526315</v>
       </c>
       <c r="O20" s="86">
         <f t="shared" ref="O20:O24" si="13">K20/H20</f>
@@ -4673,7 +4673,7 @@
       </c>
       <c r="N21" s="14">
         <f t="shared" si="6"/>
-        <v>23.35</v>
+        <v>24.578947368421051</v>
       </c>
       <c r="O21" s="72">
         <f t="shared" si="13"/>
@@ -4729,7 +4729,7 @@
       </c>
       <c r="N22" s="14">
         <f t="shared" si="6"/>
-        <v>23.2</v>
+        <v>24.421052631578949</v>
       </c>
       <c r="O22" s="72">
         <f t="shared" si="13"/>
@@ -4785,7 +4785,7 @@
       </c>
       <c r="N23" s="14">
         <f t="shared" si="6"/>
-        <v>23.65</v>
+        <v>24.894736842105264</v>
       </c>
       <c r="O23" s="72">
         <f t="shared" si="13"/>
@@ -4841,7 +4841,7 @@
       </c>
       <c r="N24" s="77">
         <f t="shared" si="6"/>
-        <v>24.2</v>
+        <v>25.473684210526315</v>
       </c>
       <c r="O24" s="78">
         <f t="shared" si="13"/>
@@ -4897,7 +4897,7 @@
       </c>
       <c r="N25" s="83">
         <f t="shared" si="6"/>
-        <v>117.65</v>
+        <v>123.84210526315789</v>
       </c>
       <c r="O25" s="84">
         <f>K25/H25</f>
@@ -4954,7 +4954,7 @@
       </c>
       <c r="N26" s="10">
         <f t="shared" si="6"/>
-        <v>30.8</v>
+        <v>32.421052631578945</v>
       </c>
       <c r="O26" s="86">
         <f t="shared" ref="O26:O29" si="15">K26/H26</f>
@@ -5010,7 +5010,7 @@
       </c>
       <c r="N27" s="14">
         <f t="shared" si="6"/>
-        <v>28.3</v>
+        <v>29.789473684210527</v>
       </c>
       <c r="O27" s="72">
         <f t="shared" si="15"/>
@@ -5066,7 +5066,7 @@
       </c>
       <c r="N28" s="14">
         <f t="shared" si="6"/>
-        <v>28.7</v>
+        <v>30.210526315789473</v>
       </c>
       <c r="O28" s="72">
         <f t="shared" si="15"/>
@@ -5122,7 +5122,7 @@
       </c>
       <c r="N29" s="77">
         <f t="shared" si="6"/>
-        <v>30.6</v>
+        <v>32.210526315789473</v>
       </c>
       <c r="O29" s="78">
         <f t="shared" si="15"/>
@@ -5178,7 +5178,7 @@
       </c>
       <c r="N30" s="83">
         <f t="shared" si="6"/>
-        <v>118.4</v>
+        <v>124.63157894736842</v>
       </c>
       <c r="O30" s="84">
         <f>K30/H30</f>
@@ -5207,11 +5207,11 @@
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31:K31" si="17">+H30+H25+H19</f>
-        <v>474</v>
+        <v>531</v>
       </c>
       <c r="I31" s="88">
         <f t="shared" si="0"/>
-        <v>7.8347107438016525E-2</v>
+        <v>8.7768595041322311E-2</v>
       </c>
       <c r="J31" s="89">
         <f t="shared" si="17"/>
@@ -5219,23 +5219,23 @@
       </c>
       <c r="K31" s="90">
         <f t="shared" si="17"/>
-        <v>894</v>
+        <v>980</v>
       </c>
       <c r="L31" s="91">
         <f>K31/J31</f>
-        <v>6.9707602339181288E-2</v>
+        <v>7.641325536062378E-2</v>
       </c>
       <c r="M31" s="90">
         <f t="shared" si="5"/>
-        <v>11931</v>
+        <v>11845</v>
       </c>
       <c r="N31" s="92">
         <f t="shared" si="6"/>
-        <v>596.54999999999995</v>
+        <v>623.42105263157896</v>
       </c>
       <c r="O31" s="93">
         <f>K31/H31</f>
-        <v>1.8860759493670887</v>
+        <v>1.8455743879472692</v>
       </c>
       <c r="P31" s="23" t="e">
         <f>AVERAGE(P30,P19,P25)</f>

--- a/Sep_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
+++ b/Sep_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCD7BE8E-6E5B-4EA4-B21F-3D92AA2A8576}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22580834-925B-460B-9D5E-1C90EED4D97C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3647,18 +3647,18 @@
         <v>26</v>
       </c>
       <c r="B2" s="24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="63">
         <f>+B2/A2</f>
-        <v>0.26923076923076922</v>
+        <v>0.30769230769230771</v>
       </c>
       <c r="D2" s="62">
         <f>+A2-B2</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F2" s="94">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="G2" s="108" t="s">
         <v>38</v>
@@ -3753,34 +3753,34 @@
         <v>600</v>
       </c>
       <c r="H4" s="31">
-        <f>5+36+19+15+11</f>
-        <v>86</v>
+        <f>5+36+19+15+11+19</f>
+        <v>105</v>
       </c>
       <c r="I4" s="68">
         <f t="shared" ref="I4:I31" si="0">H4/G4</f>
-        <v>0.14333333333333334</v>
+        <v>0.17499999999999999</v>
       </c>
       <c r="J4" s="30">
         <v>550</v>
       </c>
       <c r="K4" s="8">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="L4" s="87">
         <f t="shared" ref="L4:L29" si="1">K4/J4</f>
-        <v>0.13636363636363635</v>
+        <v>0.24</v>
       </c>
       <c r="M4" s="8">
         <f t="shared" ref="M4:M6" si="2">J4-K4</f>
-        <v>475</v>
+        <v>418</v>
       </c>
       <c r="N4" s="10">
         <f t="shared" ref="N4:N6" si="3">M4/$D$2</f>
-        <v>25</v>
+        <v>23.222222222222221</v>
       </c>
       <c r="O4" s="69">
         <f t="shared" ref="O4:P12" si="4">K4/H4</f>
-        <v>0.87209302325581395</v>
+        <v>1.2571428571428571</v>
       </c>
       <c r="P4" s="33">
         <v>3</v>
@@ -3810,34 +3810,34 @@
         <v>600</v>
       </c>
       <c r="H5" s="12">
-        <f>23+33+16+19+14</f>
-        <v>105</v>
+        <f>23+33+16+19+14+20</f>
+        <v>125</v>
       </c>
       <c r="I5" s="70">
         <f t="shared" si="0"/>
-        <v>0.17499999999999999</v>
+        <v>0.20833333333333334</v>
       </c>
       <c r="J5" s="11">
         <v>450</v>
       </c>
       <c r="K5" s="12">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="L5" s="71">
         <f t="shared" si="1"/>
-        <v>0.13333333333333333</v>
+        <v>0.15777777777777777</v>
       </c>
       <c r="M5" s="12">
         <f t="shared" si="2"/>
-        <v>390</v>
+        <v>379</v>
       </c>
       <c r="N5" s="14">
         <f t="shared" si="3"/>
-        <v>20.526315789473685</v>
+        <v>21.055555555555557</v>
       </c>
       <c r="O5" s="98">
         <f t="shared" si="4"/>
-        <v>0.5714285714285714</v>
+        <v>0.56799999999999995</v>
       </c>
       <c r="P5" s="33">
         <v>3</v>
@@ -3867,38 +3867,38 @@
         <v>600</v>
       </c>
       <c r="H6" s="12">
-        <f>6+16+5+3+11</f>
-        <v>41</v>
+        <f>6+16+5+3+11+11</f>
+        <v>52</v>
       </c>
       <c r="I6" s="70">
         <f t="shared" si="0"/>
-        <v>6.8333333333333329E-2</v>
+        <v>8.666666666666667E-2</v>
       </c>
       <c r="J6" s="11">
         <v>550</v>
       </c>
       <c r="K6" s="12">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="L6" s="71">
         <f t="shared" si="1"/>
-        <v>8.727272727272728E-2</v>
+        <v>0.12</v>
       </c>
       <c r="M6" s="12">
         <f t="shared" si="2"/>
-        <v>502</v>
+        <v>484</v>
       </c>
       <c r="N6" s="14">
         <f t="shared" si="3"/>
-        <v>26.421052631578949</v>
+        <v>26.888888888888889</v>
       </c>
       <c r="O6" s="72">
         <f t="shared" si="4"/>
-        <v>1.1707317073170731</v>
+        <v>1.2692307692307692</v>
       </c>
       <c r="P6" s="14">
         <f t="shared" si="4"/>
-        <v>1.2771618625277164</v>
+        <v>1.3846153846153846</v>
       </c>
       <c r="Q6" s="34"/>
     </row>
@@ -3925,38 +3925,38 @@
         <v>600</v>
       </c>
       <c r="H7" s="12">
-        <f>2+9+17+9+5</f>
-        <v>42</v>
+        <f>2+9+17+9+5+4</f>
+        <v>46</v>
       </c>
       <c r="I7" s="70">
         <f t="shared" si="0"/>
-        <v>7.0000000000000007E-2</v>
+        <v>7.6666666666666661E-2</v>
       </c>
       <c r="J7" s="11">
         <v>400</v>
       </c>
       <c r="K7" s="12">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="L7" s="71">
         <f t="shared" si="1"/>
-        <v>0.11749999999999999</v>
+        <v>0.13250000000000001</v>
       </c>
       <c r="M7" s="12">
         <f t="shared" ref="M7:M31" si="5">J7-K7</f>
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="N7" s="14">
         <f t="shared" ref="N7:N31" si="6">M7/$D$2</f>
-        <v>18.578947368421051</v>
+        <v>19.277777777777779</v>
       </c>
       <c r="O7" s="72">
         <f t="shared" si="4"/>
-        <v>1.1190476190476191</v>
+        <v>1.1521739130434783</v>
       </c>
       <c r="P7" s="14">
         <f t="shared" si="4"/>
-        <v>1.6785714285714284</v>
+        <v>1.7282608695652175</v>
       </c>
       <c r="Q7" s="34"/>
     </row>
@@ -3983,38 +3983,38 @@
         <v>600</v>
       </c>
       <c r="H8" s="12">
-        <f>4+7+6+6+11</f>
-        <v>34</v>
+        <f>4+7+6+6+11+2</f>
+        <v>36</v>
       </c>
       <c r="I8" s="70">
         <f t="shared" si="0"/>
-        <v>5.6666666666666664E-2</v>
+        <v>0.06</v>
       </c>
       <c r="J8" s="11">
         <v>575</v>
       </c>
       <c r="K8" s="12">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L8" s="71">
         <f t="shared" si="1"/>
-        <v>6.4347826086956522E-2</v>
+        <v>6.7826086956521744E-2</v>
       </c>
       <c r="M8" s="12">
         <f t="shared" si="5"/>
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="N8" s="14">
         <f t="shared" si="6"/>
-        <v>28.315789473684209</v>
+        <v>29.777777777777779</v>
       </c>
       <c r="O8" s="72">
         <f t="shared" si="4"/>
-        <v>1.088235294117647</v>
+        <v>1.0833333333333333</v>
       </c>
       <c r="P8" s="14">
         <f t="shared" si="4"/>
-        <v>1.1355498721227621</v>
+        <v>1.1304347826086958</v>
       </c>
       <c r="Q8" s="34"/>
     </row>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="N9" s="14">
         <f t="shared" si="6"/>
-        <v>28.94736842105263</v>
+        <v>30.555555555555557</v>
       </c>
       <c r="O9" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4094,38 +4094,38 @@
         <v>200</v>
       </c>
       <c r="H10" s="12">
-        <f>2+7+1+6+5</f>
-        <v>21</v>
+        <f>2+7+1+6+5+2</f>
+        <v>23</v>
       </c>
       <c r="I10" s="70">
         <f t="shared" si="0"/>
-        <v>0.105</v>
+        <v>0.115</v>
       </c>
       <c r="J10" s="11">
         <v>3000</v>
       </c>
       <c r="K10" s="12">
-        <v>334</v>
+        <v>504</v>
       </c>
       <c r="L10" s="71">
         <f t="shared" si="1"/>
-        <v>0.11133333333333334</v>
+        <v>0.16800000000000001</v>
       </c>
       <c r="M10" s="12">
         <f t="shared" si="5"/>
-        <v>2666</v>
+        <v>2496</v>
       </c>
       <c r="N10" s="14">
         <f t="shared" si="6"/>
-        <v>140.31578947368422</v>
+        <v>138.66666666666666</v>
       </c>
       <c r="O10" s="72">
         <f t="shared" si="4"/>
-        <v>15.904761904761905</v>
+        <v>21.913043478260871</v>
       </c>
       <c r="P10" s="14">
         <f t="shared" si="4"/>
-        <v>1.0603174603174603</v>
+        <v>1.4608695652173913</v>
       </c>
       <c r="Q10" s="34"/>
     </row>
@@ -4170,7 +4170,7 @@
       </c>
       <c r="N11" s="14">
         <f t="shared" si="6"/>
-        <v>34.210526315789473</v>
+        <v>36.111111111111114</v>
       </c>
       <c r="O11" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="N12" s="14">
         <f t="shared" si="6"/>
-        <v>28.94736842105263</v>
+        <v>30.555555555555557</v>
       </c>
       <c r="O12" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="N13" s="14">
         <f t="shared" ref="N13:N15" si="9">M13/$D$2</f>
-        <v>23.684210526315791</v>
+        <v>25</v>
       </c>
       <c r="O13" s="72" t="e">
         <f t="shared" ref="O13:O16" si="10">K13/H13</f>
@@ -4536,11 +4536,11 @@
       </c>
       <c r="H19" s="40">
         <f>SUM(H4:H18)</f>
-        <v>330</v>
+        <v>388</v>
       </c>
       <c r="I19" s="79">
         <f t="shared" si="0"/>
-        <v>5.8928571428571427E-2</v>
+        <v>6.9285714285714284E-2</v>
       </c>
       <c r="J19" s="80">
         <f>SUM(J4:J18)</f>
@@ -4548,23 +4548,23 @@
       </c>
       <c r="K19" s="80">
         <f>SUM(K4:K18)</f>
-        <v>701</v>
+        <v>965</v>
       </c>
       <c r="L19" s="82">
         <f>K19/J19</f>
-        <v>8.9584664536741215E-2</v>
+        <v>0.12332268370607029</v>
       </c>
       <c r="M19" s="81">
         <f t="shared" si="5"/>
-        <v>7124</v>
+        <v>6860</v>
       </c>
       <c r="N19" s="83">
         <f t="shared" si="6"/>
-        <v>374.94736842105266</v>
+        <v>381.11111111111109</v>
       </c>
       <c r="O19" s="84">
         <f>K19/H19</f>
-        <v>2.124242424242424</v>
+        <v>2.4871134020618557</v>
       </c>
       <c r="P19" s="43" t="e">
         <f>AVERAGE(P4:P12)</f>
@@ -4617,7 +4617,7 @@
       </c>
       <c r="N20" s="10">
         <f t="shared" si="6"/>
-        <v>24.473684210526315</v>
+        <v>25.833333333333332</v>
       </c>
       <c r="O20" s="86">
         <f t="shared" ref="O20:O24" si="13">K20/H20</f>
@@ -4673,7 +4673,7 @@
       </c>
       <c r="N21" s="14">
         <f t="shared" si="6"/>
-        <v>24.578947368421051</v>
+        <v>25.944444444444443</v>
       </c>
       <c r="O21" s="72">
         <f t="shared" si="13"/>
@@ -4729,7 +4729,7 @@
       </c>
       <c r="N22" s="14">
         <f t="shared" si="6"/>
-        <v>24.421052631578949</v>
+        <v>25.777777777777779</v>
       </c>
       <c r="O22" s="72">
         <f t="shared" si="13"/>
@@ -4785,7 +4785,7 @@
       </c>
       <c r="N23" s="14">
         <f t="shared" si="6"/>
-        <v>24.894736842105264</v>
+        <v>26.277777777777779</v>
       </c>
       <c r="O23" s="72">
         <f t="shared" si="13"/>
@@ -4841,7 +4841,7 @@
       </c>
       <c r="N24" s="77">
         <f t="shared" si="6"/>
-        <v>25.473684210526315</v>
+        <v>26.888888888888889</v>
       </c>
       <c r="O24" s="78">
         <f t="shared" si="13"/>
@@ -4897,7 +4897,7 @@
       </c>
       <c r="N25" s="83">
         <f t="shared" si="6"/>
-        <v>123.84210526315789</v>
+        <v>130.72222222222223</v>
       </c>
       <c r="O25" s="84">
         <f>K25/H25</f>
@@ -4954,7 +4954,7 @@
       </c>
       <c r="N26" s="10">
         <f t="shared" si="6"/>
-        <v>32.421052631578945</v>
+        <v>34.222222222222221</v>
       </c>
       <c r="O26" s="86">
         <f t="shared" ref="O26:O29" si="15">K26/H26</f>
@@ -5010,7 +5010,7 @@
       </c>
       <c r="N27" s="14">
         <f t="shared" si="6"/>
-        <v>29.789473684210527</v>
+        <v>31.444444444444443</v>
       </c>
       <c r="O27" s="72">
         <f t="shared" si="15"/>
@@ -5066,7 +5066,7 @@
       </c>
       <c r="N28" s="14">
         <f t="shared" si="6"/>
-        <v>30.210526315789473</v>
+        <v>31.888888888888889</v>
       </c>
       <c r="O28" s="72">
         <f t="shared" si="15"/>
@@ -5122,7 +5122,7 @@
       </c>
       <c r="N29" s="77">
         <f t="shared" si="6"/>
-        <v>32.210526315789473</v>
+        <v>34</v>
       </c>
       <c r="O29" s="78">
         <f t="shared" si="15"/>
@@ -5178,7 +5178,7 @@
       </c>
       <c r="N30" s="83">
         <f t="shared" si="6"/>
-        <v>124.63157894736842</v>
+        <v>131.55555555555554</v>
       </c>
       <c r="O30" s="84">
         <f>K30/H30</f>
@@ -5207,11 +5207,11 @@
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31:K31" si="17">+H30+H25+H19</f>
-        <v>531</v>
+        <v>589</v>
       </c>
       <c r="I31" s="88">
         <f t="shared" si="0"/>
-        <v>8.7768595041322311E-2</v>
+        <v>9.7355371900826451E-2</v>
       </c>
       <c r="J31" s="89">
         <f t="shared" si="17"/>
@@ -5219,23 +5219,23 @@
       </c>
       <c r="K31" s="90">
         <f t="shared" si="17"/>
-        <v>980</v>
+        <v>1244</v>
       </c>
       <c r="L31" s="91">
         <f>K31/J31</f>
-        <v>7.641325536062378E-2</v>
+        <v>9.6998050682261208E-2</v>
       </c>
       <c r="M31" s="90">
         <f t="shared" si="5"/>
-        <v>11845</v>
+        <v>11581</v>
       </c>
       <c r="N31" s="92">
         <f t="shared" si="6"/>
-        <v>623.42105263157896</v>
+        <v>643.38888888888891</v>
       </c>
       <c r="O31" s="93">
         <f>K31/H31</f>
-        <v>1.8455743879472692</v>
+        <v>2.1120543293718166</v>
       </c>
       <c r="P31" s="23" t="e">
         <f>AVERAGE(P30,P19,P25)</f>

--- a/Sep_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
+++ b/Sep_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22580834-925B-460B-9D5E-1C90EED4D97C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA0BFB7B-04D5-4B89-A2AF-08B808C7BAC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3647,18 +3647,18 @@
         <v>26</v>
       </c>
       <c r="B2" s="24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="63">
         <f>+B2/A2</f>
-        <v>0.30769230769230771</v>
+        <v>0.34615384615384615</v>
       </c>
       <c r="D2" s="62">
         <f>+A2-B2</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F2" s="94">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="G2" s="108" t="s">
         <v>38</v>
@@ -3753,34 +3753,34 @@
         <v>600</v>
       </c>
       <c r="H4" s="31">
-        <f>5+36+19+15+11+19</f>
-        <v>105</v>
+        <f>5+36+19+15+11+19+14</f>
+        <v>119</v>
       </c>
       <c r="I4" s="68">
         <f t="shared" ref="I4:I31" si="0">H4/G4</f>
-        <v>0.17499999999999999</v>
+        <v>0.19833333333333333</v>
       </c>
       <c r="J4" s="30">
         <v>550</v>
       </c>
       <c r="K4" s="8">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="L4" s="87">
         <f t="shared" ref="L4:L29" si="1">K4/J4</f>
-        <v>0.24</v>
+        <v>0.25818181818181818</v>
       </c>
       <c r="M4" s="8">
         <f t="shared" ref="M4:M6" si="2">J4-K4</f>
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="N4" s="10">
         <f t="shared" ref="N4:N6" si="3">M4/$D$2</f>
-        <v>23.222222222222221</v>
+        <v>24</v>
       </c>
       <c r="O4" s="69">
         <f t="shared" ref="O4:P12" si="4">K4/H4</f>
-        <v>1.2571428571428571</v>
+        <v>1.1932773109243697</v>
       </c>
       <c r="P4" s="33">
         <v>3</v>
@@ -3810,34 +3810,34 @@
         <v>600</v>
       </c>
       <c r="H5" s="12">
-        <f>23+33+16+19+14+20</f>
-        <v>125</v>
+        <f>23+33+16+19+14+20+21</f>
+        <v>146</v>
       </c>
       <c r="I5" s="70">
         <f t="shared" si="0"/>
-        <v>0.20833333333333334</v>
+        <v>0.24333333333333335</v>
       </c>
       <c r="J5" s="11">
         <v>450</v>
       </c>
       <c r="K5" s="12">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="L5" s="71">
         <f t="shared" si="1"/>
-        <v>0.15777777777777777</v>
+        <v>0.18444444444444444</v>
       </c>
       <c r="M5" s="12">
         <f t="shared" si="2"/>
-        <v>379</v>
+        <v>367</v>
       </c>
       <c r="N5" s="14">
         <f t="shared" si="3"/>
-        <v>21.055555555555557</v>
+        <v>21.588235294117649</v>
       </c>
       <c r="O5" s="98">
         <f t="shared" si="4"/>
-        <v>0.56799999999999995</v>
+        <v>0.56849315068493156</v>
       </c>
       <c r="P5" s="33">
         <v>3</v>
@@ -3867,38 +3867,38 @@
         <v>600</v>
       </c>
       <c r="H6" s="12">
-        <f>6+16+5+3+11+11</f>
-        <v>52</v>
+        <f>6+16+5+3+11+11+4</f>
+        <v>56</v>
       </c>
       <c r="I6" s="70">
         <f t="shared" si="0"/>
-        <v>8.666666666666667E-2</v>
+        <v>9.3333333333333338E-2</v>
       </c>
       <c r="J6" s="11">
         <v>550</v>
       </c>
       <c r="K6" s="12">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="L6" s="71">
         <f t="shared" si="1"/>
-        <v>0.12</v>
+        <v>0.14363636363636365</v>
       </c>
       <c r="M6" s="12">
         <f t="shared" si="2"/>
-        <v>484</v>
+        <v>471</v>
       </c>
       <c r="N6" s="14">
         <f t="shared" si="3"/>
-        <v>26.888888888888889</v>
+        <v>27.705882352941178</v>
       </c>
       <c r="O6" s="72">
         <f t="shared" si="4"/>
-        <v>1.2692307692307692</v>
+        <v>1.4107142857142858</v>
       </c>
       <c r="P6" s="14">
         <f t="shared" si="4"/>
-        <v>1.3846153846153846</v>
+        <v>1.5389610389610391</v>
       </c>
       <c r="Q6" s="34"/>
     </row>
@@ -3925,38 +3925,38 @@
         <v>600</v>
       </c>
       <c r="H7" s="12">
-        <f>2+9+17+9+5+4</f>
-        <v>46</v>
+        <f>2+9+17+9+5+4+10</f>
+        <v>56</v>
       </c>
       <c r="I7" s="70">
         <f t="shared" si="0"/>
-        <v>7.6666666666666661E-2</v>
+        <v>9.3333333333333338E-2</v>
       </c>
       <c r="J7" s="11">
         <v>400</v>
       </c>
       <c r="K7" s="12">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="L7" s="71">
         <f t="shared" si="1"/>
-        <v>0.13250000000000001</v>
+        <v>0.15</v>
       </c>
       <c r="M7" s="12">
         <f t="shared" ref="M7:M31" si="5">J7-K7</f>
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="N7" s="14">
         <f t="shared" ref="N7:N31" si="6">M7/$D$2</f>
-        <v>19.277777777777779</v>
+        <v>20</v>
       </c>
       <c r="O7" s="72">
         <f t="shared" si="4"/>
-        <v>1.1521739130434783</v>
+        <v>1.0714285714285714</v>
       </c>
       <c r="P7" s="14">
         <f t="shared" si="4"/>
-        <v>1.7282608695652175</v>
+        <v>1.607142857142857</v>
       </c>
       <c r="Q7" s="34"/>
     </row>
@@ -3983,38 +3983,38 @@
         <v>600</v>
       </c>
       <c r="H8" s="12">
-        <f>4+7+6+6+11+2</f>
-        <v>36</v>
+        <f>4+7+6+6+11+2+9</f>
+        <v>45</v>
       </c>
       <c r="I8" s="70">
         <f t="shared" si="0"/>
-        <v>0.06</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="J8" s="11">
         <v>575</v>
       </c>
       <c r="K8" s="12">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L8" s="71">
         <f t="shared" si="1"/>
-        <v>6.7826086956521744E-2</v>
+        <v>7.8260869565217397E-2</v>
       </c>
       <c r="M8" s="12">
         <f t="shared" si="5"/>
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="N8" s="14">
         <f t="shared" si="6"/>
-        <v>29.777777777777779</v>
+        <v>31.176470588235293</v>
       </c>
       <c r="O8" s="72">
         <f t="shared" si="4"/>
-        <v>1.0833333333333333</v>
+        <v>1</v>
       </c>
       <c r="P8" s="14">
         <f t="shared" si="4"/>
-        <v>1.1304347826086958</v>
+        <v>1.0434782608695654</v>
       </c>
       <c r="Q8" s="34"/>
     </row>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="N9" s="14">
         <f t="shared" si="6"/>
-        <v>30.555555555555557</v>
+        <v>32.352941176470587</v>
       </c>
       <c r="O9" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4094,38 +4094,38 @@
         <v>200</v>
       </c>
       <c r="H10" s="12">
-        <f>2+7+1+6+5+2</f>
-        <v>23</v>
+        <f>2+7+1+6+5+2+4</f>
+        <v>27</v>
       </c>
       <c r="I10" s="70">
         <f t="shared" si="0"/>
-        <v>0.115</v>
+        <v>0.13500000000000001</v>
       </c>
       <c r="J10" s="11">
         <v>3000</v>
       </c>
       <c r="K10" s="12">
-        <v>504</v>
+        <v>529</v>
       </c>
       <c r="L10" s="71">
         <f t="shared" si="1"/>
-        <v>0.16800000000000001</v>
+        <v>0.17633333333333334</v>
       </c>
       <c r="M10" s="12">
         <f t="shared" si="5"/>
-        <v>2496</v>
+        <v>2471</v>
       </c>
       <c r="N10" s="14">
         <f t="shared" si="6"/>
-        <v>138.66666666666666</v>
+        <v>145.35294117647058</v>
       </c>
       <c r="O10" s="72">
         <f t="shared" si="4"/>
-        <v>21.913043478260871</v>
+        <v>19.592592592592592</v>
       </c>
       <c r="P10" s="14">
         <f t="shared" si="4"/>
-        <v>1.4608695652173913</v>
+        <v>1.3061728395061729</v>
       </c>
       <c r="Q10" s="34"/>
     </row>
@@ -4170,7 +4170,7 @@
       </c>
       <c r="N11" s="14">
         <f t="shared" si="6"/>
-        <v>36.111111111111114</v>
+        <v>38.235294117647058</v>
       </c>
       <c r="O11" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="N12" s="14">
         <f t="shared" si="6"/>
-        <v>30.555555555555557</v>
+        <v>32.352941176470587</v>
       </c>
       <c r="O12" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="N13" s="14">
         <f t="shared" ref="N13:N15" si="9">M13/$D$2</f>
-        <v>25</v>
+        <v>26.470588235294116</v>
       </c>
       <c r="O13" s="72" t="e">
         <f t="shared" ref="O13:O16" si="10">K13/H13</f>
@@ -4536,11 +4536,11 @@
       </c>
       <c r="H19" s="40">
         <f>SUM(H4:H18)</f>
-        <v>388</v>
+        <v>450</v>
       </c>
       <c r="I19" s="79">
         <f t="shared" si="0"/>
-        <v>6.9285714285714284E-2</v>
+        <v>8.0357142857142863E-2</v>
       </c>
       <c r="J19" s="80">
         <f>SUM(J4:J18)</f>
@@ -4548,23 +4548,23 @@
       </c>
       <c r="K19" s="80">
         <f>SUM(K4:K18)</f>
-        <v>965</v>
+        <v>1038</v>
       </c>
       <c r="L19" s="82">
         <f>K19/J19</f>
-        <v>0.12332268370607029</v>
+        <v>0.13265175718849839</v>
       </c>
       <c r="M19" s="81">
         <f t="shared" si="5"/>
-        <v>6860</v>
+        <v>6787</v>
       </c>
       <c r="N19" s="83">
         <f t="shared" si="6"/>
-        <v>381.11111111111109</v>
+        <v>399.23529411764707</v>
       </c>
       <c r="O19" s="84">
         <f>K19/H19</f>
-        <v>2.4871134020618557</v>
+        <v>2.3066666666666666</v>
       </c>
       <c r="P19" s="43" t="e">
         <f>AVERAGE(P4:P12)</f>
@@ -4617,7 +4617,7 @@
       </c>
       <c r="N20" s="10">
         <f t="shared" si="6"/>
-        <v>25.833333333333332</v>
+        <v>27.352941176470587</v>
       </c>
       <c r="O20" s="86">
         <f t="shared" ref="O20:O24" si="13">K20/H20</f>
@@ -4673,7 +4673,7 @@
       </c>
       <c r="N21" s="14">
         <f t="shared" si="6"/>
-        <v>25.944444444444443</v>
+        <v>27.470588235294116</v>
       </c>
       <c r="O21" s="72">
         <f t="shared" si="13"/>
@@ -4729,7 +4729,7 @@
       </c>
       <c r="N22" s="14">
         <f t="shared" si="6"/>
-        <v>25.777777777777779</v>
+        <v>27.294117647058822</v>
       </c>
       <c r="O22" s="72">
         <f t="shared" si="13"/>
@@ -4785,7 +4785,7 @@
       </c>
       <c r="N23" s="14">
         <f t="shared" si="6"/>
-        <v>26.277777777777779</v>
+        <v>27.823529411764707</v>
       </c>
       <c r="O23" s="72">
         <f t="shared" si="13"/>
@@ -4841,7 +4841,7 @@
       </c>
       <c r="N24" s="77">
         <f t="shared" si="6"/>
-        <v>26.888888888888889</v>
+        <v>28.470588235294116</v>
       </c>
       <c r="O24" s="78">
         <f t="shared" si="13"/>
@@ -4897,7 +4897,7 @@
       </c>
       <c r="N25" s="83">
         <f t="shared" si="6"/>
-        <v>130.72222222222223</v>
+        <v>138.41176470588235</v>
       </c>
       <c r="O25" s="84">
         <f>K25/H25</f>
@@ -4954,7 +4954,7 @@
       </c>
       <c r="N26" s="10">
         <f t="shared" si="6"/>
-        <v>34.222222222222221</v>
+        <v>36.235294117647058</v>
       </c>
       <c r="O26" s="86">
         <f t="shared" ref="O26:O29" si="15">K26/H26</f>
@@ -5010,7 +5010,7 @@
       </c>
       <c r="N27" s="14">
         <f t="shared" si="6"/>
-        <v>31.444444444444443</v>
+        <v>33.294117647058826</v>
       </c>
       <c r="O27" s="72">
         <f t="shared" si="15"/>
@@ -5066,7 +5066,7 @@
       </c>
       <c r="N28" s="14">
         <f t="shared" si="6"/>
-        <v>31.888888888888889</v>
+        <v>33.764705882352942</v>
       </c>
       <c r="O28" s="72">
         <f t="shared" si="15"/>
@@ -5122,7 +5122,7 @@
       </c>
       <c r="N29" s="77">
         <f t="shared" si="6"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O29" s="78">
         <f t="shared" si="15"/>
@@ -5178,7 +5178,7 @@
       </c>
       <c r="N30" s="83">
         <f t="shared" si="6"/>
-        <v>131.55555555555554</v>
+        <v>139.29411764705881</v>
       </c>
       <c r="O30" s="84">
         <f>K30/H30</f>
@@ -5207,11 +5207,11 @@
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31:K31" si="17">+H30+H25+H19</f>
-        <v>589</v>
+        <v>651</v>
       </c>
       <c r="I31" s="88">
         <f t="shared" si="0"/>
-        <v>9.7355371900826451E-2</v>
+        <v>0.10760330578512396</v>
       </c>
       <c r="J31" s="89">
         <f t="shared" si="17"/>
@@ -5219,23 +5219,23 @@
       </c>
       <c r="K31" s="90">
         <f t="shared" si="17"/>
-        <v>1244</v>
+        <v>1317</v>
       </c>
       <c r="L31" s="91">
         <f>K31/J31</f>
-        <v>9.6998050682261208E-2</v>
+        <v>0.10269005847953216</v>
       </c>
       <c r="M31" s="90">
         <f t="shared" si="5"/>
-        <v>11581</v>
+        <v>11508</v>
       </c>
       <c r="N31" s="92">
         <f t="shared" si="6"/>
-        <v>643.38888888888891</v>
+        <v>676.94117647058829</v>
       </c>
       <c r="O31" s="93">
         <f>K31/H31</f>
-        <v>2.1120543293718166</v>
+        <v>2.0230414746543777</v>
       </c>
       <c r="P31" s="23" t="e">
         <f>AVERAGE(P30,P19,P25)</f>

--- a/Sep_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
+++ b/Sep_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA0BFB7B-04D5-4B89-A2AF-08B808C7BAC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE28A2C6-7C12-4BDB-8071-852C2A3F999A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3647,18 +3647,18 @@
         <v>26</v>
       </c>
       <c r="B2" s="24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="63">
         <f>+B2/A2</f>
-        <v>0.34615384615384615</v>
+        <v>0.38461538461538464</v>
       </c>
       <c r="D2" s="62">
         <f>+A2-B2</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F2" s="94">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="G2" s="108" t="s">
         <v>38</v>
@@ -3753,34 +3753,34 @@
         <v>600</v>
       </c>
       <c r="H4" s="31">
-        <f>5+36+19+15+11+19+14</f>
-        <v>119</v>
+        <f>5+36+19+15+11+19+14+7</f>
+        <v>126</v>
       </c>
       <c r="I4" s="68">
         <f t="shared" ref="I4:I31" si="0">H4/G4</f>
-        <v>0.19833333333333333</v>
+        <v>0.21</v>
       </c>
       <c r="J4" s="30">
         <v>550</v>
       </c>
       <c r="K4" s="8">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="L4" s="87">
         <f t="shared" ref="L4:L29" si="1">K4/J4</f>
-        <v>0.25818181818181818</v>
+        <v>0.26545454545454544</v>
       </c>
       <c r="M4" s="8">
         <f t="shared" ref="M4:M6" si="2">J4-K4</f>
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="N4" s="10">
         <f t="shared" ref="N4:N6" si="3">M4/$D$2</f>
-        <v>24</v>
+        <v>25.25</v>
       </c>
       <c r="O4" s="69">
         <f t="shared" ref="O4:P12" si="4">K4/H4</f>
-        <v>1.1932773109243697</v>
+        <v>1.1587301587301588</v>
       </c>
       <c r="P4" s="33">
         <v>3</v>
@@ -3810,34 +3810,34 @@
         <v>600</v>
       </c>
       <c r="H5" s="12">
-        <f>23+33+16+19+14+20+21</f>
-        <v>146</v>
+        <f>23+33+16+19+14+20+21+15</f>
+        <v>161</v>
       </c>
       <c r="I5" s="70">
         <f t="shared" si="0"/>
-        <v>0.24333333333333335</v>
+        <v>0.26833333333333331</v>
       </c>
       <c r="J5" s="11">
         <v>450</v>
       </c>
       <c r="K5" s="12">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="L5" s="71">
         <f t="shared" si="1"/>
-        <v>0.18444444444444444</v>
+        <v>0.20222222222222222</v>
       </c>
       <c r="M5" s="12">
         <f t="shared" si="2"/>
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="N5" s="14">
         <f t="shared" si="3"/>
-        <v>21.588235294117649</v>
+        <v>22.4375</v>
       </c>
       <c r="O5" s="98">
         <f t="shared" si="4"/>
-        <v>0.56849315068493156</v>
+        <v>0.56521739130434778</v>
       </c>
       <c r="P5" s="33">
         <v>3</v>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="N6" s="14">
         <f t="shared" si="3"/>
-        <v>27.705882352941178</v>
+        <v>29.4375</v>
       </c>
       <c r="O6" s="72">
         <f t="shared" si="4"/>
@@ -3925,38 +3925,38 @@
         <v>600</v>
       </c>
       <c r="H7" s="12">
-        <f>2+9+17+9+5+4+10</f>
-        <v>56</v>
+        <f>2+9+17+9+5+4+10+5</f>
+        <v>61</v>
       </c>
       <c r="I7" s="70">
         <f t="shared" si="0"/>
-        <v>9.3333333333333338E-2</v>
+        <v>0.10166666666666667</v>
       </c>
       <c r="J7" s="11">
         <v>400</v>
       </c>
       <c r="K7" s="12">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="L7" s="71">
         <f t="shared" si="1"/>
-        <v>0.15</v>
+        <v>0.17499999999999999</v>
       </c>
       <c r="M7" s="12">
         <f t="shared" ref="M7:M31" si="5">J7-K7</f>
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="N7" s="14">
         <f t="shared" ref="N7:N31" si="6">M7/$D$2</f>
-        <v>20</v>
+        <v>20.625</v>
       </c>
       <c r="O7" s="72">
         <f t="shared" si="4"/>
-        <v>1.0714285714285714</v>
+        <v>1.1475409836065573</v>
       </c>
       <c r="P7" s="14">
         <f t="shared" si="4"/>
-        <v>1.607142857142857</v>
+        <v>1.721311475409836</v>
       </c>
       <c r="Q7" s="34"/>
     </row>
@@ -3983,30 +3983,30 @@
         <v>600</v>
       </c>
       <c r="H8" s="12">
-        <f>4+7+6+6+11+2+9</f>
-        <v>45</v>
+        <f>4+7+6+6+11+2+9+6</f>
+        <v>51</v>
       </c>
       <c r="I8" s="70">
         <f t="shared" si="0"/>
-        <v>7.4999999999999997E-2</v>
+        <v>8.5000000000000006E-2</v>
       </c>
       <c r="J8" s="11">
         <v>575</v>
       </c>
       <c r="K8" s="12">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L8" s="71">
         <f t="shared" si="1"/>
-        <v>7.8260869565217397E-2</v>
+        <v>8.8695652173913037E-2</v>
       </c>
       <c r="M8" s="12">
         <f t="shared" si="5"/>
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="N8" s="14">
         <f t="shared" si="6"/>
-        <v>31.176470588235293</v>
+        <v>32.75</v>
       </c>
       <c r="O8" s="72">
         <f t="shared" si="4"/>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="P8" s="14">
         <f t="shared" si="4"/>
-        <v>1.0434782608695654</v>
+        <v>1.043478260869565</v>
       </c>
       <c r="Q8" s="34"/>
     </row>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="N9" s="14">
         <f t="shared" si="6"/>
-        <v>32.352941176470587</v>
+        <v>34.375</v>
       </c>
       <c r="O9" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4094,38 +4094,38 @@
         <v>200</v>
       </c>
       <c r="H10" s="12">
-        <f>2+7+1+6+5+2+4</f>
-        <v>27</v>
+        <f>2+7+1+6+5+2+4+4</f>
+        <v>31</v>
       </c>
       <c r="I10" s="70">
         <f t="shared" si="0"/>
-        <v>0.13500000000000001</v>
+        <v>0.155</v>
       </c>
       <c r="J10" s="11">
         <v>3000</v>
       </c>
       <c r="K10" s="12">
-        <v>529</v>
+        <v>618</v>
       </c>
       <c r="L10" s="71">
         <f t="shared" si="1"/>
-        <v>0.17633333333333334</v>
+        <v>0.20599999999999999</v>
       </c>
       <c r="M10" s="12">
         <f t="shared" si="5"/>
-        <v>2471</v>
+        <v>2382</v>
       </c>
       <c r="N10" s="14">
         <f t="shared" si="6"/>
-        <v>145.35294117647058</v>
+        <v>148.875</v>
       </c>
       <c r="O10" s="72">
         <f t="shared" si="4"/>
-        <v>19.592592592592592</v>
+        <v>19.93548387096774</v>
       </c>
       <c r="P10" s="14">
         <f t="shared" si="4"/>
-        <v>1.3061728395061729</v>
+        <v>1.329032258064516</v>
       </c>
       <c r="Q10" s="34"/>
     </row>
@@ -4170,7 +4170,7 @@
       </c>
       <c r="N11" s="14">
         <f t="shared" si="6"/>
-        <v>38.235294117647058</v>
+        <v>40.625</v>
       </c>
       <c r="O11" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="N12" s="14">
         <f t="shared" si="6"/>
-        <v>32.352941176470587</v>
+        <v>34.375</v>
       </c>
       <c r="O12" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="N13" s="14">
         <f t="shared" ref="N13:N15" si="9">M13/$D$2</f>
-        <v>26.470588235294116</v>
+        <v>28.125</v>
       </c>
       <c r="O13" s="72" t="e">
         <f t="shared" ref="O13:O16" si="10">K13/H13</f>
@@ -4536,11 +4536,11 @@
       </c>
       <c r="H19" s="40">
         <f>SUM(H4:H18)</f>
-        <v>450</v>
+        <v>487</v>
       </c>
       <c r="I19" s="79">
         <f t="shared" si="0"/>
-        <v>8.0357142857142863E-2</v>
+        <v>8.6964285714285716E-2</v>
       </c>
       <c r="J19" s="80">
         <f>SUM(J4:J18)</f>
@@ -4548,23 +4548,23 @@
       </c>
       <c r="K19" s="80">
         <f>SUM(K4:K18)</f>
-        <v>1038</v>
+        <v>1155</v>
       </c>
       <c r="L19" s="82">
         <f>K19/J19</f>
-        <v>0.13265175718849839</v>
+        <v>0.14760383386581469</v>
       </c>
       <c r="M19" s="81">
         <f t="shared" si="5"/>
-        <v>6787</v>
+        <v>6670</v>
       </c>
       <c r="N19" s="83">
         <f t="shared" si="6"/>
-        <v>399.23529411764707</v>
+        <v>416.875</v>
       </c>
       <c r="O19" s="84">
         <f>K19/H19</f>
-        <v>2.3066666666666666</v>
+        <v>2.3716632443531829</v>
       </c>
       <c r="P19" s="43" t="e">
         <f>AVERAGE(P4:P12)</f>
@@ -4617,7 +4617,7 @@
       </c>
       <c r="N20" s="10">
         <f t="shared" si="6"/>
-        <v>27.352941176470587</v>
+        <v>29.0625</v>
       </c>
       <c r="O20" s="86">
         <f t="shared" ref="O20:O24" si="13">K20/H20</f>
@@ -4673,7 +4673,7 @@
       </c>
       <c r="N21" s="14">
         <f t="shared" si="6"/>
-        <v>27.470588235294116</v>
+        <v>29.1875</v>
       </c>
       <c r="O21" s="72">
         <f t="shared" si="13"/>
@@ -4729,7 +4729,7 @@
       </c>
       <c r="N22" s="14">
         <f t="shared" si="6"/>
-        <v>27.294117647058822</v>
+        <v>29</v>
       </c>
       <c r="O22" s="72">
         <f t="shared" si="13"/>
@@ -4785,7 +4785,7 @@
       </c>
       <c r="N23" s="14">
         <f t="shared" si="6"/>
-        <v>27.823529411764707</v>
+        <v>29.5625</v>
       </c>
       <c r="O23" s="72">
         <f t="shared" si="13"/>
@@ -4841,7 +4841,7 @@
       </c>
       <c r="N24" s="77">
         <f t="shared" si="6"/>
-        <v>28.470588235294116</v>
+        <v>30.25</v>
       </c>
       <c r="O24" s="78">
         <f t="shared" si="13"/>
@@ -4897,7 +4897,7 @@
       </c>
       <c r="N25" s="83">
         <f t="shared" si="6"/>
-        <v>138.41176470588235</v>
+        <v>147.0625</v>
       </c>
       <c r="O25" s="84">
         <f>K25/H25</f>
@@ -4954,7 +4954,7 @@
       </c>
       <c r="N26" s="10">
         <f t="shared" si="6"/>
-        <v>36.235294117647058</v>
+        <v>38.5</v>
       </c>
       <c r="O26" s="86">
         <f t="shared" ref="O26:O29" si="15">K26/H26</f>
@@ -5010,7 +5010,7 @@
       </c>
       <c r="N27" s="14">
         <f t="shared" si="6"/>
-        <v>33.294117647058826</v>
+        <v>35.375</v>
       </c>
       <c r="O27" s="72">
         <f t="shared" si="15"/>
@@ -5066,7 +5066,7 @@
       </c>
       <c r="N28" s="14">
         <f t="shared" si="6"/>
-        <v>33.764705882352942</v>
+        <v>35.875</v>
       </c>
       <c r="O28" s="72">
         <f t="shared" si="15"/>
@@ -5122,7 +5122,7 @@
       </c>
       <c r="N29" s="77">
         <f t="shared" si="6"/>
-        <v>36</v>
+        <v>38.25</v>
       </c>
       <c r="O29" s="78">
         <f t="shared" si="15"/>
@@ -5178,7 +5178,7 @@
       </c>
       <c r="N30" s="83">
         <f t="shared" si="6"/>
-        <v>139.29411764705881</v>
+        <v>148</v>
       </c>
       <c r="O30" s="84">
         <f>K30/H30</f>
@@ -5207,11 +5207,11 @@
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31:K31" si="17">+H30+H25+H19</f>
-        <v>651</v>
+        <v>688</v>
       </c>
       <c r="I31" s="88">
         <f t="shared" si="0"/>
-        <v>0.10760330578512396</v>
+        <v>0.11371900826446281</v>
       </c>
       <c r="J31" s="89">
         <f t="shared" si="17"/>
@@ -5219,23 +5219,23 @@
       </c>
       <c r="K31" s="90">
         <f t="shared" si="17"/>
-        <v>1317</v>
+        <v>1434</v>
       </c>
       <c r="L31" s="91">
         <f>K31/J31</f>
-        <v>0.10269005847953216</v>
+        <v>0.11181286549707602</v>
       </c>
       <c r="M31" s="90">
         <f t="shared" si="5"/>
-        <v>11508</v>
+        <v>11391</v>
       </c>
       <c r="N31" s="92">
         <f t="shared" si="6"/>
-        <v>676.94117647058829</v>
+        <v>711.9375</v>
       </c>
       <c r="O31" s="93">
         <f>K31/H31</f>
-        <v>2.0230414746543777</v>
+        <v>2.0843023255813953</v>
       </c>
       <c r="P31" s="23" t="e">
         <f>AVERAGE(P30,P19,P25)</f>

--- a/Sep_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
+++ b/Sep_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DACD05E-469D-46FD-AC6F-E704ADB8BB90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20C7CA7A-AE1C-4E8D-9F96-D25B822405AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="70">
   <si>
     <t>Booking</t>
   </si>
@@ -230,6 +230,12 @@
   </si>
   <si>
     <t>Qamar Ijaz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nabeel Traders </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sohail Traders </t>
   </si>
 </sst>
 </file>
@@ -3406,22 +3412,22 @@
         <v>26</v>
       </c>
       <c r="F2" s="79">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2" s="80">
         <f>+F2/E2</f>
-        <v>0.46153846153846156</v>
+        <v>0.5</v>
       </c>
       <c r="H2" s="81">
         <f>+E2-F2</f>
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="30.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="47"/>
       <c r="B3" s="47"/>
       <c r="D3" s="82">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="E3" s="122" t="s">
         <v>31</v>
@@ -3508,34 +3514,34 @@
         <v>600</v>
       </c>
       <c r="F5" s="7">
-        <f>5+36+19+15+11+19+14+7+13+21</f>
-        <v>160</v>
+        <f>5+36+19+15+11+19+14+7+13+21+21</f>
+        <v>181</v>
       </c>
       <c r="G5" s="66">
         <f t="shared" ref="G5:G30" si="0">F5/E5</f>
-        <v>0.26666666666666666</v>
+        <v>0.30166666666666669</v>
       </c>
       <c r="H5" s="7">
         <v>550</v>
       </c>
       <c r="I5" s="7">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="J5" s="66">
         <f>I5/H5</f>
-        <v>0.32545454545454544</v>
+        <v>0.34363636363636363</v>
       </c>
       <c r="K5" s="7">
         <f t="shared" ref="K5:K7" si="1">H5-I5</f>
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="L5" s="96">
         <f>K5/H2</f>
-        <v>26.5</v>
+        <v>27.76923076923077</v>
       </c>
       <c r="M5" s="106">
         <f>I5/F5</f>
-        <v>1.1187499999999999</v>
+        <v>1.0441988950276244</v>
       </c>
       <c r="N5" s="9">
         <v>3</v>
@@ -3563,34 +3569,34 @@
         <v>600</v>
       </c>
       <c r="F6" s="11">
-        <f>23+33+16+19+14+20+21+15+9</f>
-        <v>170</v>
+        <f>23+33+16+19+14+20+21+15+9+14</f>
+        <v>184</v>
       </c>
       <c r="G6" s="50">
         <f t="shared" si="0"/>
-        <v>0.28333333333333333</v>
+        <v>0.30666666666666664</v>
       </c>
       <c r="H6" s="11">
         <v>450</v>
       </c>
       <c r="I6" s="11">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="J6" s="50">
         <f t="shared" ref="J6:J28" si="2">I6/H6</f>
-        <v>0.24444444444444444</v>
+        <v>0.26222222222222225</v>
       </c>
       <c r="K6" s="11">
         <f t="shared" si="1"/>
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="L6" s="93">
         <f>K6/H2</f>
-        <v>24.285714285714285</v>
+        <v>25.53846153846154</v>
       </c>
       <c r="M6" s="107">
         <f t="shared" ref="M6:M17" si="3">I6/F6</f>
-        <v>0.6470588235294118</v>
+        <v>0.64130434782608692</v>
       </c>
       <c r="N6" s="13">
         <v>3</v>
@@ -3614,38 +3620,38 @@
         <v>600</v>
       </c>
       <c r="F7" s="11">
-        <f>6+16+5+3+11+11+4+9</f>
-        <v>65</v>
+        <f>6+16+5+3+11+11+4+9+16</f>
+        <v>81</v>
       </c>
       <c r="G7" s="50">
         <f t="shared" si="0"/>
-        <v>0.10833333333333334</v>
+        <v>0.13500000000000001</v>
       </c>
       <c r="H7" s="11">
         <v>550</v>
       </c>
       <c r="I7" s="11">
-        <v>85</v>
+        <v>122</v>
       </c>
       <c r="J7" s="50">
         <f t="shared" si="2"/>
-        <v>0.15454545454545454</v>
+        <v>0.22181818181818183</v>
       </c>
       <c r="K7" s="11">
         <f t="shared" si="1"/>
-        <v>465</v>
+        <v>428</v>
       </c>
       <c r="L7" s="93">
         <f>K7/H2</f>
-        <v>33.214285714285715</v>
+        <v>32.92307692307692</v>
       </c>
       <c r="M7" s="107">
         <f t="shared" si="3"/>
-        <v>1.3076923076923077</v>
+        <v>1.5061728395061729</v>
       </c>
       <c r="N7" s="13">
         <f t="shared" ref="N7:N13" si="4">J7/G7</f>
-        <v>1.4265734265734265</v>
+        <v>1.6430976430976432</v>
       </c>
       <c r="O7" s="88"/>
     </row>
@@ -3666,38 +3672,38 @@
         <v>600</v>
       </c>
       <c r="F8" s="11">
-        <f>2+9+17+9+5+4+10+5+11+7</f>
-        <v>79</v>
+        <f>2+9+17+9+5+4+10+5+11+7+9</f>
+        <v>88</v>
       </c>
       <c r="G8" s="50">
         <f t="shared" si="0"/>
-        <v>0.13166666666666665</v>
+        <v>0.14666666666666667</v>
       </c>
       <c r="H8" s="11">
         <v>400</v>
       </c>
       <c r="I8" s="11">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="J8" s="50">
         <f t="shared" si="2"/>
-        <v>0.23499999999999999</v>
+        <v>0.27</v>
       </c>
       <c r="K8" s="11">
         <f t="shared" ref="K8:K30" si="5">H8-I8</f>
-        <v>306</v>
+        <v>292</v>
       </c>
       <c r="L8" s="93">
         <f>K8/H2</f>
-        <v>21.857142857142858</v>
+        <v>22.46153846153846</v>
       </c>
       <c r="M8" s="107">
         <f t="shared" si="3"/>
-        <v>1.1898734177215189</v>
+        <v>1.2272727272727273</v>
       </c>
       <c r="N8" s="13">
         <f t="shared" si="4"/>
-        <v>1.7848101265822784</v>
+        <v>1.8409090909090911</v>
       </c>
       <c r="O8" s="88"/>
     </row>
@@ -3718,38 +3724,38 @@
         <v>600</v>
       </c>
       <c r="F9" s="11">
-        <f>4+7+6+6+11+2+9+6+2+10</f>
-        <v>63</v>
+        <f>4+7+6+6+11+2+9+6+2+10+1</f>
+        <v>64</v>
       </c>
       <c r="G9" s="50">
         <f t="shared" si="0"/>
-        <v>0.105</v>
+        <v>0.10666666666666667</v>
       </c>
       <c r="H9" s="11">
         <v>575</v>
       </c>
       <c r="I9" s="11">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="J9" s="50">
         <f t="shared" si="2"/>
-        <v>0.11130434782608696</v>
+        <v>0.11826086956521739</v>
       </c>
       <c r="K9" s="11">
         <f t="shared" si="5"/>
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="L9" s="93">
         <f>K9/H2</f>
-        <v>36.5</v>
+        <v>39</v>
       </c>
       <c r="M9" s="107">
         <f t="shared" si="3"/>
-        <v>1.0158730158730158</v>
+        <v>1.0625</v>
       </c>
       <c r="N9" s="13">
         <f t="shared" si="4"/>
-        <v>1.0600414078674949</v>
+        <v>1.1086956521739131</v>
       </c>
       <c r="O9" s="88"/>
     </row>
@@ -3788,7 +3794,7 @@
       </c>
       <c r="L10" s="93">
         <f>K10/H2</f>
-        <v>39.285714285714285</v>
+        <v>42.307692307692307</v>
       </c>
       <c r="M10" s="107" t="e">
         <f t="shared" si="3"/>
@@ -3817,38 +3823,38 @@
         <v>200</v>
       </c>
       <c r="F11" s="11">
-        <f>2+7+1+6+5+2+4+4+4</f>
-        <v>35</v>
+        <f>2+7+1+6+5+2+4+4+4+4</f>
+        <v>39</v>
       </c>
       <c r="G11" s="50">
         <f t="shared" si="0"/>
-        <v>0.17499999999999999</v>
+        <v>0.19500000000000001</v>
       </c>
       <c r="H11" s="11">
         <v>3000</v>
       </c>
       <c r="I11" s="11">
-        <v>676</v>
+        <v>720</v>
       </c>
       <c r="J11" s="50">
         <f t="shared" si="2"/>
-        <v>0.22533333333333333</v>
+        <v>0.24</v>
       </c>
       <c r="K11" s="11">
         <f t="shared" si="5"/>
-        <v>2324</v>
+        <v>2280</v>
       </c>
       <c r="L11" s="93">
         <f>K11/H2</f>
-        <v>166</v>
+        <v>175.38461538461539</v>
       </c>
       <c r="M11" s="107">
         <f t="shared" si="3"/>
-        <v>19.314285714285713</v>
+        <v>18.46153846153846</v>
       </c>
       <c r="N11" s="13">
         <f t="shared" si="4"/>
-        <v>1.2876190476190477</v>
+        <v>1.2307692307692306</v>
       </c>
       <c r="O11" s="88"/>
     </row>
@@ -3860,7 +3866,7 @@
         <v>66</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="D12" s="16" t="s">
         <v>51</v>
@@ -3868,34 +3874,38 @@
       <c r="E12" s="11">
         <v>600</v>
       </c>
-      <c r="F12" s="11"/>
+      <c r="F12" s="11">
+        <v>170</v>
+      </c>
       <c r="G12" s="50">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.28333333333333333</v>
       </c>
       <c r="H12" s="11">
         <v>650</v>
       </c>
-      <c r="I12" s="11"/>
+      <c r="I12" s="11">
+        <v>244</v>
+      </c>
       <c r="J12" s="50">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.37538461538461537</v>
       </c>
       <c r="K12" s="11">
         <f t="shared" si="5"/>
-        <v>650</v>
+        <v>406</v>
       </c>
       <c r="L12" s="93">
         <f>K12/H2</f>
-        <v>46.428571428571431</v>
-      </c>
-      <c r="M12" s="10" t="e">
+        <v>31.23076923076923</v>
+      </c>
+      <c r="M12" s="10">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N12" s="13" t="e">
+        <v>1.4352941176470588</v>
+      </c>
+      <c r="N12" s="13">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>1.3248868778280543</v>
       </c>
       <c r="O12" s="88"/>
     </row>
@@ -3907,7 +3917,7 @@
         <v>66</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="D13" s="16" t="s">
         <v>52</v>
@@ -3915,34 +3925,38 @@
       <c r="E13" s="11">
         <v>600</v>
       </c>
-      <c r="F13" s="11"/>
+      <c r="F13" s="11">
+        <v>113</v>
+      </c>
       <c r="G13" s="50">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.18833333333333332</v>
       </c>
       <c r="H13" s="11">
         <v>550</v>
       </c>
-      <c r="I13" s="11"/>
+      <c r="I13" s="11">
+        <v>123</v>
+      </c>
       <c r="J13" s="50">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.22363636363636363</v>
       </c>
       <c r="K13" s="11">
         <f t="shared" si="5"/>
-        <v>550</v>
+        <v>427</v>
       </c>
       <c r="L13" s="93">
         <f>K13/H2</f>
-        <v>39.285714285714285</v>
-      </c>
-      <c r="M13" s="10" t="e">
+        <v>32.846153846153847</v>
+      </c>
+      <c r="M13" s="10">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N13" s="13" t="e">
+        <v>1.0884955752212389</v>
+      </c>
+      <c r="N13" s="13">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>1.1874497184231698</v>
       </c>
       <c r="O13" s="88"/>
     </row>
@@ -3954,7 +3968,7 @@
         <v>66</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="D14" s="16" t="s">
         <v>65</v>
@@ -3981,7 +3995,7 @@
       </c>
       <c r="L14" s="93">
         <f>K14/H2</f>
-        <v>32.142857142857146</v>
+        <v>34.615384615384613</v>
       </c>
       <c r="M14" s="10" t="e">
         <f t="shared" si="3"/>
@@ -4001,7 +4015,7 @@
         <v>66</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>18</v>
+        <v>69</v>
       </c>
       <c r="D15" s="41" t="s">
         <v>36</v>
@@ -4071,9 +4085,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L16" s="93" t="e">
+      <c r="L16" s="93">
         <f t="shared" ref="L16:L17" si="9">I16/F13</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="M16" s="10" t="e">
         <f t="shared" si="3"/>
@@ -4093,7 +4107,7 @@
         <v>66</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="D17" s="42" t="s">
         <v>53</v>
@@ -4143,11 +4157,11 @@
       </c>
       <c r="F18" s="33">
         <f>SUM(F5:F17)</f>
-        <v>573</v>
+        <v>921</v>
       </c>
       <c r="G18" s="58">
         <f t="shared" si="0"/>
-        <v>0.10232142857142858</v>
+        <v>0.1644642857142857</v>
       </c>
       <c r="H18" s="33">
         <f>SUM(H5:H17)</f>
@@ -4155,23 +4169,23 @@
       </c>
       <c r="I18" s="33">
         <f>SUM(I5:I17)</f>
-        <v>1308</v>
+        <v>1792</v>
       </c>
       <c r="J18" s="102">
         <f>I18/H18</f>
-        <v>0.16715654952076678</v>
+        <v>0.22900958466453675</v>
       </c>
       <c r="K18" s="34">
         <f t="shared" si="5"/>
-        <v>6517</v>
+        <v>6033</v>
       </c>
       <c r="L18" s="36">
         <f>K18/H2</f>
-        <v>465.5</v>
+        <v>464.07692307692309</v>
       </c>
       <c r="M18" s="63">
         <f>I18/F18</f>
-        <v>2.2827225130890052</v>
+        <v>1.9457111834961998</v>
       </c>
       <c r="N18" s="36" t="e">
         <f>AVERAGE(N5:N13)</f>
@@ -4744,11 +4758,11 @@
       </c>
       <c r="F30" s="20">
         <f t="shared" ref="F30:I30" si="16">+F29+F24+F18</f>
-        <v>774</v>
+        <v>1122</v>
       </c>
       <c r="G30" s="67">
         <f t="shared" si="0"/>
-        <v>0.12793388429752067</v>
+        <v>0.18545454545454546</v>
       </c>
       <c r="H30" s="68">
         <f t="shared" si="16"/>
@@ -4756,15 +4770,15 @@
       </c>
       <c r="I30" s="69">
         <f t="shared" si="16"/>
-        <v>1587</v>
+        <v>2071</v>
       </c>
       <c r="J30" s="70">
         <f>I30/H30</f>
-        <v>0.12374269005847953</v>
+        <v>0.16148148148148148</v>
       </c>
       <c r="K30" s="69">
         <f t="shared" si="5"/>
-        <v>11238</v>
+        <v>10754</v>
       </c>
       <c r="L30" s="71" t="e">
         <f t="shared" si="11"/>
@@ -4772,7 +4786,7 @@
       </c>
       <c r="M30" s="72">
         <f>I30/F30</f>
-        <v>2.0503875968992249</v>
+        <v>1.8458110516934045</v>
       </c>
       <c r="N30" s="22" t="e">
         <f>AVERAGE(N29,N18,N24)</f>

--- a/Sep_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
+++ b/Sep_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20C7CA7A-AE1C-4E8D-9F96-D25B822405AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D524797-ECE1-4139-BDD4-6466C5EE86DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="69">
   <si>
     <t>Booking</t>
   </si>
@@ -218,9 +218,6 @@
   </si>
   <si>
     <t>Furqan</t>
-  </si>
-  <si>
-    <t>Pendings</t>
   </si>
   <si>
     <t xml:space="preserve">Yasir </t>
@@ -1632,7 +1629,7 @@
     </row>
     <row r="2" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D2" s="73">
-        <v>46279</v>
+        <v>46281</v>
       </c>
       <c r="E2" s="117" t="s">
         <v>2</v>
@@ -1729,7 +1726,7 @@
         <v>17</v>
       </c>
       <c r="B4" s="39" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C4" s="39" t="s">
         <v>18</v>
@@ -1741,57 +1738,57 @@
         <v>50</v>
       </c>
       <c r="F4" s="11">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="G4" s="50">
         <f t="shared" ref="G4:G28" si="0">F4/E4</f>
-        <v>0.44</v>
+        <v>0.08</v>
       </c>
       <c r="H4" s="11">
         <v>40</v>
       </c>
       <c r="I4" s="11">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J4" s="50">
         <f t="shared" ref="J4:J11" si="1">I4/H4</f>
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="K4" s="11">
         <f t="shared" ref="K4:L11" si="2">I4/F4</f>
-        <v>0.54545454545454541</v>
+        <v>1</v>
       </c>
       <c r="L4" s="11">
         <f t="shared" si="2"/>
-        <v>0.68181818181818177</v>
+        <v>1.25</v>
       </c>
       <c r="M4" s="11">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N4" s="74">
         <v>21</v>
       </c>
       <c r="O4" s="50">
         <f t="shared" ref="O4:O11" si="3">N4/M4</f>
-        <v>1</v>
+        <v>0.91304347826086951</v>
       </c>
       <c r="P4" s="11">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="Q4" s="74">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="R4" s="50">
         <f t="shared" ref="R4:R11" si="4">Q4/P4</f>
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="S4" s="11">
         <f t="shared" ref="S4:T11" si="5">Q4/N4</f>
-        <v>0.8571428571428571</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="T4" s="11">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0.8761904761904763</v>
       </c>
       <c r="U4" s="92"/>
     </row>
@@ -1800,7 +1797,7 @@
         <v>17</v>
       </c>
       <c r="B5" s="39" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C5" s="15" t="s">
         <v>18</v>
@@ -1812,57 +1809,57 @@
         <v>50</v>
       </c>
       <c r="F5" s="11">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G5" s="50">
         <f t="shared" si="0"/>
-        <v>0.32</v>
+        <v>0.24</v>
       </c>
       <c r="H5" s="11">
         <v>30</v>
       </c>
       <c r="I5" s="11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J5" s="50">
         <f t="shared" si="1"/>
-        <v>0.33333333333333331</v>
+        <v>0.23333333333333334</v>
       </c>
       <c r="K5" s="11">
         <f t="shared" si="2"/>
-        <v>0.625</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="L5" s="11">
         <f t="shared" si="2"/>
-        <v>1.0416666666666665</v>
+        <v>0.97222222222222232</v>
       </c>
       <c r="M5" s="11">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N5" s="74">
-        <v>0</v>
-      </c>
-      <c r="O5" s="50" t="e">
+        <v>21</v>
+      </c>
+      <c r="O5" s="50">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
+        <v>0.95454545454545459</v>
       </c>
       <c r="P5" s="11">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Q5" s="74">
-        <v>0</v>
-      </c>
-      <c r="R5" s="50" t="e">
+        <v>14</v>
+      </c>
+      <c r="R5" s="50">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S5" s="11" t="e">
+        <v>0.82352941176470584</v>
+      </c>
+      <c r="S5" s="11">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T5" s="11" t="e">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="T5" s="11">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>0.86274509803921562</v>
       </c>
       <c r="U5" s="92"/>
     </row>
@@ -1871,7 +1868,7 @@
         <v>17</v>
       </c>
       <c r="B6" s="39" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C6" s="15" t="s">
         <v>18</v>
@@ -1883,68 +1880,66 @@
         <v>50</v>
       </c>
       <c r="F6" s="11">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G6" s="50">
         <f t="shared" si="0"/>
-        <v>0.22</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="H6" s="11">
         <v>25</v>
       </c>
       <c r="I6" s="11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J6" s="50">
         <f t="shared" si="1"/>
-        <v>0.4</v>
+        <v>0.32</v>
       </c>
       <c r="K6" s="11">
         <f t="shared" si="2"/>
-        <v>0.90909090909090906</v>
+        <v>1.1428571428571428</v>
       </c>
       <c r="L6" s="11">
         <f t="shared" si="2"/>
-        <v>1.8181818181818183</v>
+        <v>2.2857142857142856</v>
       </c>
       <c r="M6" s="11">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N6" s="74">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O6" s="50">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="P6" s="11">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="Q6" s="74">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R6" s="50">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S6" s="11" t="e">
+        <v>0.75</v>
+      </c>
+      <c r="S6" s="11">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T6" s="11" t="e">
+        <v>1</v>
+      </c>
+      <c r="T6" s="11">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U6" s="92" t="s">
-        <v>64</v>
-      </c>
+        <v>0.875</v>
+      </c>
+      <c r="U6" s="92"/>
     </row>
     <row r="7" spans="1:26" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A7" s="28" t="s">
         <v>17</v>
       </c>
       <c r="B7" s="39" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>18</v>
@@ -1956,57 +1951,57 @@
         <v>50</v>
       </c>
       <c r="F7" s="11">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G7" s="50">
         <f t="shared" si="0"/>
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="H7" s="11">
         <v>30</v>
       </c>
       <c r="I7" s="11">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J7" s="50">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0.43333333333333335</v>
       </c>
       <c r="K7" s="11">
         <f t="shared" si="2"/>
-        <v>1.6666666666666667</v>
+        <v>1.1818181818181819</v>
       </c>
       <c r="L7" s="11">
         <f t="shared" si="2"/>
-        <v>2.7777777777777777</v>
+        <v>1.9696969696969697</v>
       </c>
       <c r="M7" s="11">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N7" s="74">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O7" s="50">
         <f t="shared" si="3"/>
-        <v>0.875</v>
+        <v>1</v>
       </c>
       <c r="P7" s="11">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="Q7" s="74">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="R7" s="50">
         <f t="shared" si="4"/>
-        <v>0.93333333333333335</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="S7" s="11">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>0.75</v>
       </c>
       <c r="T7" s="11">
         <f t="shared" si="5"/>
-        <v>1.0666666666666667</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="U7" s="92"/>
     </row>
@@ -2015,7 +2010,7 @@
         <v>17</v>
       </c>
       <c r="B8" s="39" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C8" s="15" t="s">
         <v>18</v>
@@ -2027,57 +2022,57 @@
         <v>50</v>
       </c>
       <c r="F8" s="11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G8" s="50">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="H8" s="11">
         <v>20</v>
       </c>
       <c r="I8" s="11">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J8" s="50">
         <f t="shared" si="1"/>
-        <v>0.65</v>
+        <v>0.45</v>
       </c>
       <c r="K8" s="11">
         <f t="shared" si="2"/>
-        <v>1.3</v>
+        <v>1.125</v>
       </c>
       <c r="L8" s="11">
         <f t="shared" si="2"/>
-        <v>3.25</v>
+        <v>2.8125</v>
       </c>
       <c r="M8" s="11">
         <v>12</v>
       </c>
       <c r="N8" s="74">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O8" s="50">
         <f t="shared" si="3"/>
-        <v>0.83333333333333337</v>
+        <v>8.3333333333333329E-2</v>
       </c>
       <c r="P8" s="11">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Q8" s="74">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="R8" s="50">
         <f t="shared" si="4"/>
-        <v>0.90909090909090906</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="S8" s="11">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T8" s="11">
         <f t="shared" si="5"/>
-        <v>1.0909090909090908</v>
+        <v>6.8571428571428568</v>
       </c>
       <c r="U8" s="92"/>
     </row>
@@ -2086,7 +2081,7 @@
         <v>17</v>
       </c>
       <c r="B9" s="39" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C9" s="15" t="s">
         <v>18</v>
@@ -2098,17 +2093,17 @@
         <v>25</v>
       </c>
       <c r="F9" s="11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G9" s="50">
         <f t="shared" si="0"/>
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
       <c r="H9" s="11">
         <v>0</v>
       </c>
       <c r="I9" s="11">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J9" s="50" t="e">
         <f t="shared" si="1"/>
@@ -2116,35 +2111,41 @@
       </c>
       <c r="K9" s="11">
         <f t="shared" si="2"/>
-        <v>3.75</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="L9" s="11" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M9" s="11"/>
-      <c r="N9" s="74"/>
-      <c r="O9" s="50" t="e">
+      <c r="M9" s="11">
+        <v>5</v>
+      </c>
+      <c r="N9" s="74">
+        <v>93</v>
+      </c>
+      <c r="O9" s="50">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="74"/>
-      <c r="R9" s="50" t="e">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="P9" s="11">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="74">
+        <v>4</v>
+      </c>
+      <c r="R9" s="50">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S9" s="11" t="e">
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="S9" s="11">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T9" s="11" t="e">
+        <v>4.3010752688172046E-2</v>
+      </c>
+      <c r="T9" s="11">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U9" s="92" t="s">
-        <v>64</v>
-      </c>
+        <v>7.1684587813620068E-2</v>
+      </c>
+      <c r="U9" s="92"/>
       <c r="Z9">
         <v>33</v>
       </c>
@@ -2154,7 +2155,7 @@
         <v>17</v>
       </c>
       <c r="B10" s="39" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C10" s="15" t="s">
         <v>18</v>
@@ -2216,7 +2217,7 @@
         <v>17</v>
       </c>
       <c r="B11" s="39" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C11" s="15" t="s">
         <v>18</v>
@@ -2278,13 +2279,13 @@
         <v>17</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C12" s="15" t="s">
         <v>18</v>
       </c>
       <c r="D12" s="41" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
@@ -2312,7 +2313,7 @@
         <v>17</v>
       </c>
       <c r="B13" s="39" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C13" s="15" t="s">
         <v>18</v>
@@ -2346,7 +2347,7 @@
         <v>17</v>
       </c>
       <c r="B14" s="39" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C14" s="15" t="s">
         <v>18</v>
@@ -2380,7 +2381,7 @@
         <v>17</v>
       </c>
       <c r="B15" s="39" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C15" s="15" t="s">
         <v>18</v>
@@ -2424,11 +2425,11 @@
       </c>
       <c r="F16" s="60">
         <f>SUM(F4:F15)</f>
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="G16" s="89">
         <f t="shared" si="0"/>
-        <v>0.192</v>
+        <v>0.12</v>
       </c>
       <c r="H16" s="59">
         <f>SUM(H4:H15)</f>
@@ -2436,15 +2437,15 @@
       </c>
       <c r="I16" s="60">
         <f>SUM(I4:I15)</f>
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="J16" s="89">
         <f t="shared" ref="J16" si="6">I16/H16</f>
-        <v>0.20547945205479451</v>
+        <v>0.16712328767123288</v>
       </c>
       <c r="K16" s="59">
         <f>I16/F16</f>
-        <v>1.0416666666666667</v>
+        <v>1.3555555555555556</v>
       </c>
       <c r="L16" s="62" t="e">
         <f>AVERAGE(L4:L15)</f>
@@ -2452,31 +2453,31 @@
       </c>
       <c r="M16" s="59">
         <f>SUM(M4:M15)</f>
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="N16" s="60">
         <f>SUM(N4:N15)</f>
-        <v>38</v>
+        <v>146</v>
       </c>
       <c r="O16" s="89">
         <f t="shared" ref="O16" si="7">N16/M16</f>
-        <v>0.76</v>
+        <v>2</v>
       </c>
       <c r="P16" s="59">
         <f>SUM(P4:P15)</f>
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="Q16" s="60">
         <f>SUM(Q4:Q15)</f>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="R16" s="89">
         <f t="shared" ref="R16" si="8">Q16/P16</f>
-        <v>0.56000000000000005</v>
+        <v>0.75438596491228072</v>
       </c>
       <c r="S16" s="59">
         <f>Q16/N16</f>
-        <v>1.1052631578947369</v>
+        <v>0.29452054794520549</v>
       </c>
       <c r="T16" s="62" t="e">
         <f>AVERAGE(T4:T15)</f>
@@ -3283,11 +3284,11 @@
       </c>
       <c r="F28" s="20">
         <f t="shared" ref="F28" si="24">+F27+F22+F16</f>
-        <v>210</v>
+        <v>183</v>
       </c>
       <c r="G28" s="21">
         <f t="shared" si="0"/>
-        <v>6.9421487603305784E-2</v>
+        <v>6.0495867768595044E-2</v>
       </c>
       <c r="H28" s="19">
         <f>+H27+H22+H16</f>
@@ -3295,15 +3296,15 @@
       </c>
       <c r="I28" s="20">
         <f t="shared" ref="I28" si="25">+I27+I22+I16</f>
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="J28" s="21">
         <f t="shared" si="9"/>
-        <v>9.4346978557504874E-2</v>
+        <v>8.8888888888888892E-2</v>
       </c>
       <c r="K28" s="19">
         <f>I28/F28</f>
-        <v>1.1523809523809523</v>
+        <v>1.2459016393442623</v>
       </c>
       <c r="L28" s="22" t="e">
         <f>AVERAGE(L27,L16,L22)</f>
@@ -3311,31 +3312,31 @@
       </c>
       <c r="M28" s="19">
         <f>+M27+M22+M16</f>
-        <v>199</v>
+        <v>222</v>
       </c>
       <c r="N28" s="20">
         <f t="shared" ref="N28" si="26">+N27+N22+N16</f>
-        <v>151</v>
+        <v>259</v>
       </c>
       <c r="O28" s="21">
         <f t="shared" si="11"/>
-        <v>0.75879396984924619</v>
+        <v>1.1666666666666667</v>
       </c>
       <c r="P28" s="19">
         <f>+P27+P22+P16</f>
-        <v>314</v>
+        <v>296</v>
       </c>
       <c r="Q28" s="20">
         <f t="shared" ref="Q28" si="27">+Q27+Q22+Q16</f>
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="R28" s="21">
         <f t="shared" si="12"/>
-        <v>0.54777070063694266</v>
+        <v>0.58445945945945943</v>
       </c>
       <c r="S28" s="19">
         <f>Q28/N28</f>
-        <v>1.1390728476821192</v>
+        <v>0.66795366795366795</v>
       </c>
       <c r="T28" s="22" t="e">
         <f>AVERAGE(T27,T16,T22)</f>
@@ -3412,22 +3413,22 @@
         <v>26</v>
       </c>
       <c r="F2" s="79">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" s="80">
         <f>+F2/E2</f>
-        <v>0.5</v>
+        <v>0.53846153846153844</v>
       </c>
       <c r="H2" s="81">
         <f>+E2-F2</f>
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="30.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="47"/>
       <c r="B3" s="47"/>
       <c r="D3" s="82">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="E3" s="122" t="s">
         <v>31</v>
@@ -3502,7 +3503,7 @@
         <v>17</v>
       </c>
       <c r="B5" s="39" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C5" s="14" t="s">
         <v>18</v>
@@ -3514,34 +3515,34 @@
         <v>600</v>
       </c>
       <c r="F5" s="7">
-        <f>5+36+19+15+11+19+14+7+13+21+21</f>
-        <v>181</v>
+        <f>5+36+19+15+11+19+14+7+13+21+21+21</f>
+        <v>202</v>
       </c>
       <c r="G5" s="66">
         <f t="shared" ref="G5:G30" si="0">F5/E5</f>
-        <v>0.30166666666666669</v>
+        <v>0.33666666666666667</v>
       </c>
       <c r="H5" s="7">
         <v>550</v>
       </c>
       <c r="I5" s="7">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="J5" s="66">
         <f>I5/H5</f>
-        <v>0.34363636363636363</v>
+        <v>0.36545454545454548</v>
       </c>
       <c r="K5" s="7">
         <f t="shared" ref="K5:K7" si="1">H5-I5</f>
-        <v>361</v>
+        <v>349</v>
       </c>
       <c r="L5" s="96">
         <f>K5/H2</f>
-        <v>27.76923076923077</v>
+        <v>29.083333333333332</v>
       </c>
       <c r="M5" s="106">
         <f>I5/F5</f>
-        <v>1.0441988950276244</v>
+        <v>0.99504950495049505</v>
       </c>
       <c r="N5" s="9">
         <v>3</v>
@@ -3557,7 +3558,7 @@
         <v>17</v>
       </c>
       <c r="B6" s="39" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C6" s="15" t="s">
         <v>18</v>
@@ -3569,34 +3570,34 @@
         <v>600</v>
       </c>
       <c r="F6" s="11">
-        <f>23+33+16+19+14+20+21+15+9+14</f>
-        <v>184</v>
+        <f>23+33+16+19+14+20+21+15+9+14+21</f>
+        <v>205</v>
       </c>
       <c r="G6" s="50">
         <f t="shared" si="0"/>
-        <v>0.30666666666666664</v>
+        <v>0.34166666666666667</v>
       </c>
       <c r="H6" s="11">
         <v>450</v>
       </c>
       <c r="I6" s="11">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="J6" s="50">
         <f t="shared" ref="J6:J28" si="2">I6/H6</f>
-        <v>0.26222222222222225</v>
+        <v>0.29333333333333333</v>
       </c>
       <c r="K6" s="11">
         <f t="shared" si="1"/>
-        <v>332</v>
+        <v>318</v>
       </c>
       <c r="L6" s="93">
         <f>K6/H2</f>
-        <v>25.53846153846154</v>
+        <v>26.5</v>
       </c>
       <c r="M6" s="107">
         <f t="shared" ref="M6:M17" si="3">I6/F6</f>
-        <v>0.64130434782608692</v>
+        <v>0.64390243902439026</v>
       </c>
       <c r="N6" s="13">
         <v>3</v>
@@ -3608,7 +3609,7 @@
         <v>17</v>
       </c>
       <c r="B7" s="39" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>18</v>
@@ -3620,38 +3621,38 @@
         <v>600</v>
       </c>
       <c r="F7" s="11">
-        <f>6+16+5+3+11+11+4+9+16</f>
-        <v>81</v>
+        <f>6+16+5+3+11+11+4+9+16+6</f>
+        <v>87</v>
       </c>
       <c r="G7" s="50">
         <f t="shared" si="0"/>
-        <v>0.13500000000000001</v>
+        <v>0.14499999999999999</v>
       </c>
       <c r="H7" s="11">
         <v>550</v>
       </c>
       <c r="I7" s="11">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="J7" s="50">
         <f t="shared" si="2"/>
-        <v>0.22181818181818183</v>
+        <v>0.23272727272727273</v>
       </c>
       <c r="K7" s="11">
         <f t="shared" si="1"/>
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="L7" s="93">
         <f>K7/H2</f>
-        <v>32.92307692307692</v>
+        <v>35.166666666666664</v>
       </c>
       <c r="M7" s="107">
         <f t="shared" si="3"/>
-        <v>1.5061728395061729</v>
+        <v>1.4712643678160919</v>
       </c>
       <c r="N7" s="13">
         <f t="shared" ref="N7:N13" si="4">J7/G7</f>
-        <v>1.6430976430976432</v>
+        <v>1.6050156739811914</v>
       </c>
       <c r="O7" s="88"/>
     </row>
@@ -3660,7 +3661,7 @@
         <v>17</v>
       </c>
       <c r="B8" s="39" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C8" s="15" t="s">
         <v>18</v>
@@ -3672,38 +3673,38 @@
         <v>600</v>
       </c>
       <c r="F8" s="11">
-        <f>2+9+17+9+5+4+10+5+11+7+9</f>
-        <v>88</v>
+        <f>2+9+17+9+5+4+10+5+11+7+9+4</f>
+        <v>92</v>
       </c>
       <c r="G8" s="50">
         <f t="shared" si="0"/>
-        <v>0.14666666666666667</v>
+        <v>0.15333333333333332</v>
       </c>
       <c r="H8" s="11">
         <v>400</v>
       </c>
       <c r="I8" s="11">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="J8" s="50">
         <f t="shared" si="2"/>
-        <v>0.27</v>
+        <v>0.27750000000000002</v>
       </c>
       <c r="K8" s="11">
         <f t="shared" ref="K8:K30" si="5">H8-I8</f>
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="L8" s="93">
         <f>K8/H2</f>
-        <v>22.46153846153846</v>
+        <v>24.083333333333332</v>
       </c>
       <c r="M8" s="107">
         <f t="shared" si="3"/>
-        <v>1.2272727272727273</v>
+        <v>1.2065217391304348</v>
       </c>
       <c r="N8" s="13">
         <f t="shared" si="4"/>
-        <v>1.8409090909090911</v>
+        <v>1.8097826086956526</v>
       </c>
       <c r="O8" s="88"/>
     </row>
@@ -3712,7 +3713,7 @@
         <v>17</v>
       </c>
       <c r="B9" s="39" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C9" s="15" t="s">
         <v>18</v>
@@ -3724,38 +3725,38 @@
         <v>600</v>
       </c>
       <c r="F9" s="11">
-        <f>4+7+6+6+11+2+9+6+2+10+1</f>
-        <v>64</v>
+        <f>4+7+6+6+11+2+9+6+2+10+1+5</f>
+        <v>69</v>
       </c>
       <c r="G9" s="50">
         <f t="shared" si="0"/>
-        <v>0.10666666666666667</v>
+        <v>0.115</v>
       </c>
       <c r="H9" s="11">
         <v>575</v>
       </c>
       <c r="I9" s="11">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="J9" s="50">
         <f t="shared" si="2"/>
-        <v>0.11826086956521739</v>
+        <v>0.12521739130434784</v>
       </c>
       <c r="K9" s="11">
         <f t="shared" si="5"/>
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="L9" s="93">
         <f>K9/H2</f>
-        <v>39</v>
+        <v>41.916666666666664</v>
       </c>
       <c r="M9" s="107">
         <f t="shared" si="3"/>
-        <v>1.0625</v>
+        <v>1.0434782608695652</v>
       </c>
       <c r="N9" s="13">
         <f t="shared" si="4"/>
-        <v>1.1086956521739131</v>
+        <v>1.0888468809073724</v>
       </c>
       <c r="O9" s="88"/>
     </row>
@@ -3764,7 +3765,7 @@
         <v>17</v>
       </c>
       <c r="B10" s="39" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C10" s="15" t="s">
         <v>18</v>
@@ -3794,7 +3795,7 @@
       </c>
       <c r="L10" s="93">
         <f>K10/H2</f>
-        <v>42.307692307692307</v>
+        <v>45.833333333333336</v>
       </c>
       <c r="M10" s="107" t="e">
         <f t="shared" si="3"/>
@@ -3811,7 +3812,7 @@
         <v>17</v>
       </c>
       <c r="B11" s="39" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C11" s="15" t="s">
         <v>18</v>
@@ -3823,38 +3824,38 @@
         <v>200</v>
       </c>
       <c r="F11" s="11">
-        <f>2+7+1+6+5+2+4+4+4+4</f>
-        <v>39</v>
+        <f>2+7+1+6+5+2+4+4+4+4+1</f>
+        <v>40</v>
       </c>
       <c r="G11" s="50">
         <f t="shared" si="0"/>
-        <v>0.19500000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="H11" s="11">
         <v>3000</v>
       </c>
       <c r="I11" s="11">
-        <v>720</v>
+        <v>736</v>
       </c>
       <c r="J11" s="50">
         <f t="shared" si="2"/>
-        <v>0.24</v>
+        <v>0.24533333333333332</v>
       </c>
       <c r="K11" s="11">
         <f t="shared" si="5"/>
-        <v>2280</v>
+        <v>2264</v>
       </c>
       <c r="L11" s="93">
         <f>K11/H2</f>
-        <v>175.38461538461539</v>
+        <v>188.66666666666666</v>
       </c>
       <c r="M11" s="107">
         <f t="shared" si="3"/>
-        <v>18.46153846153846</v>
+        <v>18.399999999999999</v>
       </c>
       <c r="N11" s="13">
         <f t="shared" si="4"/>
-        <v>1.2307692307692306</v>
+        <v>1.2266666666666666</v>
       </c>
       <c r="O11" s="88"/>
     </row>
@@ -3863,10 +3864,10 @@
         <v>17</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D12" s="16" t="s">
         <v>51</v>
@@ -3897,7 +3898,7 @@
       </c>
       <c r="L12" s="93">
         <f>K12/H2</f>
-        <v>31.23076923076923</v>
+        <v>33.833333333333336</v>
       </c>
       <c r="M12" s="10">
         <f t="shared" si="3"/>
@@ -3914,10 +3915,10 @@
         <v>17</v>
       </c>
       <c r="B13" s="39" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D13" s="16" t="s">
         <v>52</v>
@@ -3948,7 +3949,7 @@
       </c>
       <c r="L13" s="93">
         <f>K13/H2</f>
-        <v>32.846153846153847</v>
+        <v>35.583333333333336</v>
       </c>
       <c r="M13" s="10">
         <f t="shared" si="3"/>
@@ -3965,13 +3966,13 @@
         <v>17</v>
       </c>
       <c r="B14" s="39" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E14" s="11">
         <v>600</v>
@@ -3995,7 +3996,7 @@
       </c>
       <c r="L14" s="93">
         <f>K14/H2</f>
-        <v>34.615384615384613</v>
+        <v>37.5</v>
       </c>
       <c r="M14" s="10" t="e">
         <f t="shared" si="3"/>
@@ -4012,10 +4013,10 @@
         <v>17</v>
       </c>
       <c r="B15" s="39" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D15" s="41" t="s">
         <v>36</v>
@@ -4061,7 +4062,7 @@
         <v>17</v>
       </c>
       <c r="B16" s="39" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C16" s="15" t="s">
         <v>18</v>
@@ -4104,10 +4105,10 @@
         <v>17</v>
       </c>
       <c r="B17" s="99" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D17" s="42" t="s">
         <v>53</v>
@@ -4157,11 +4158,11 @@
       </c>
       <c r="F18" s="33">
         <f>SUM(F5:F17)</f>
-        <v>921</v>
+        <v>979</v>
       </c>
       <c r="G18" s="58">
         <f t="shared" si="0"/>
-        <v>0.1644642857142857</v>
+        <v>0.17482142857142857</v>
       </c>
       <c r="H18" s="33">
         <f>SUM(H5:H17)</f>
@@ -4169,23 +4170,23 @@
       </c>
       <c r="I18" s="33">
         <f>SUM(I5:I17)</f>
-        <v>1792</v>
+        <v>1847</v>
       </c>
       <c r="J18" s="102">
         <f>I18/H18</f>
-        <v>0.22900958466453675</v>
+        <v>0.23603833865814697</v>
       </c>
       <c r="K18" s="34">
         <f t="shared" si="5"/>
-        <v>6033</v>
+        <v>5978</v>
       </c>
       <c r="L18" s="36">
         <f>K18/H2</f>
-        <v>464.07692307692309</v>
+        <v>498.16666666666669</v>
       </c>
       <c r="M18" s="63">
         <f>I18/F18</f>
-        <v>1.9457111834961998</v>
+        <v>1.8866189989785496</v>
       </c>
       <c r="N18" s="36" t="e">
         <f>AVERAGE(N5:N13)</f>
@@ -4758,11 +4759,11 @@
       </c>
       <c r="F30" s="20">
         <f t="shared" ref="F30:I30" si="16">+F29+F24+F18</f>
-        <v>1122</v>
+        <v>1180</v>
       </c>
       <c r="G30" s="67">
         <f t="shared" si="0"/>
-        <v>0.18545454545454546</v>
+        <v>0.19504132231404958</v>
       </c>
       <c r="H30" s="68">
         <f t="shared" si="16"/>
@@ -4770,15 +4771,15 @@
       </c>
       <c r="I30" s="69">
         <f t="shared" si="16"/>
-        <v>2071</v>
+        <v>2126</v>
       </c>
       <c r="J30" s="70">
         <f>I30/H30</f>
-        <v>0.16148148148148148</v>
+        <v>0.16576998050682262</v>
       </c>
       <c r="K30" s="69">
         <f t="shared" si="5"/>
-        <v>10754</v>
+        <v>10699</v>
       </c>
       <c r="L30" s="71" t="e">
         <f t="shared" si="11"/>
@@ -4786,7 +4787,7 @@
       </c>
       <c r="M30" s="72">
         <f>I30/F30</f>
-        <v>1.8458110516934045</v>
+        <v>1.8016949152542372</v>
       </c>
       <c r="N30" s="22" t="e">
         <f>AVERAGE(N29,N18,N24)</f>

--- a/Sep_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
+++ b/Sep_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D524797-ECE1-4139-BDD4-6466C5EE86DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A13E2C75-3E6B-47E7-8C9C-30CA79C0E6C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Sep_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
+++ b/Sep_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A13E2C75-3E6B-47E7-8C9C-30CA79C0E6C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC3B6DE4-AD41-4187-A154-91B2EF74A5CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Today Performance" sheetId="1" r:id="rId1"/>
@@ -3413,22 +3413,22 @@
         <v>26</v>
       </c>
       <c r="F2" s="79">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G2" s="80">
         <f>+F2/E2</f>
-        <v>0.53846153846153844</v>
+        <v>0.57692307692307687</v>
       </c>
       <c r="H2" s="81">
         <f>+E2-F2</f>
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="30.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="47"/>
       <c r="B3" s="47"/>
       <c r="D3" s="82">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="E3" s="122" t="s">
         <v>31</v>
@@ -3515,34 +3515,34 @@
         <v>600</v>
       </c>
       <c r="F5" s="7">
-        <f>5+36+19+15+11+19+14+7+13+21+21+21</f>
-        <v>202</v>
+        <f>5+36+19+15+11+19+14+7+13+21+21+21+4</f>
+        <v>206</v>
       </c>
       <c r="G5" s="66">
         <f t="shared" ref="G5:G30" si="0">F5/E5</f>
-        <v>0.33666666666666667</v>
+        <v>0.34333333333333332</v>
       </c>
       <c r="H5" s="7">
         <v>550</v>
       </c>
       <c r="I5" s="7">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="J5" s="66">
         <f>I5/H5</f>
-        <v>0.36545454545454548</v>
+        <v>0.37090909090909091</v>
       </c>
       <c r="K5" s="7">
         <f t="shared" ref="K5:K7" si="1">H5-I5</f>
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="L5" s="96">
         <f>K5/H2</f>
-        <v>29.083333333333332</v>
+        <v>31.454545454545453</v>
       </c>
       <c r="M5" s="106">
         <f>I5/F5</f>
-        <v>0.99504950495049505</v>
+        <v>0.99029126213592233</v>
       </c>
       <c r="N5" s="9">
         <v>3</v>
@@ -3570,34 +3570,34 @@
         <v>600</v>
       </c>
       <c r="F6" s="11">
-        <f>23+33+16+19+14+20+21+15+9+14+21</f>
-        <v>205</v>
+        <f>23+33+16+19+14+20+21+15+9+14+21+12</f>
+        <v>217</v>
       </c>
       <c r="G6" s="50">
         <f t="shared" si="0"/>
-        <v>0.34166666666666667</v>
+        <v>0.36166666666666669</v>
       </c>
       <c r="H6" s="11">
         <v>450</v>
       </c>
       <c r="I6" s="11">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="J6" s="50">
         <f t="shared" ref="J6:J28" si="2">I6/H6</f>
-        <v>0.29333333333333333</v>
+        <v>0.30888888888888888</v>
       </c>
       <c r="K6" s="11">
         <f t="shared" si="1"/>
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="L6" s="93">
         <f>K6/H2</f>
-        <v>26.5</v>
+        <v>28.272727272727273</v>
       </c>
       <c r="M6" s="107">
         <f t="shared" ref="M6:M17" si="3">I6/F6</f>
-        <v>0.64390243902439026</v>
+        <v>0.64055299539170507</v>
       </c>
       <c r="N6" s="13">
         <v>3</v>
@@ -3621,38 +3621,38 @@
         <v>600</v>
       </c>
       <c r="F7" s="11">
-        <f>6+16+5+3+11+11+4+9+16+6</f>
-        <v>87</v>
+        <f>6+16+5+3+11+11+4+9+16+6+7</f>
+        <v>94</v>
       </c>
       <c r="G7" s="50">
         <f t="shared" si="0"/>
-        <v>0.14499999999999999</v>
+        <v>0.15666666666666668</v>
       </c>
       <c r="H7" s="11">
         <v>550</v>
       </c>
       <c r="I7" s="11">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="J7" s="50">
         <f t="shared" si="2"/>
-        <v>0.23272727272727273</v>
+        <v>0.24727272727272728</v>
       </c>
       <c r="K7" s="11">
         <f t="shared" si="1"/>
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="L7" s="93">
         <f>K7/H2</f>
-        <v>35.166666666666664</v>
+        <v>37.636363636363633</v>
       </c>
       <c r="M7" s="107">
         <f t="shared" si="3"/>
-        <v>1.4712643678160919</v>
+        <v>1.446808510638298</v>
       </c>
       <c r="N7" s="13">
         <f t="shared" ref="N7:N13" si="4">J7/G7</f>
-        <v>1.6050156739811914</v>
+        <v>1.5783365570599612</v>
       </c>
       <c r="O7" s="88"/>
     </row>
@@ -3673,38 +3673,38 @@
         <v>600</v>
       </c>
       <c r="F8" s="11">
-        <f>2+9+17+9+5+4+10+5+11+7+9+4</f>
-        <v>92</v>
+        <f>2+9+17+9+5+4+10+5+11+7+9+4+10</f>
+        <v>102</v>
       </c>
       <c r="G8" s="50">
         <f t="shared" si="0"/>
-        <v>0.15333333333333332</v>
+        <v>0.17</v>
       </c>
       <c r="H8" s="11">
         <v>400</v>
       </c>
       <c r="I8" s="11">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="J8" s="50">
         <f t="shared" si="2"/>
-        <v>0.27750000000000002</v>
+        <v>0.3075</v>
       </c>
       <c r="K8" s="11">
         <f t="shared" ref="K8:K30" si="5">H8-I8</f>
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="L8" s="93">
         <f>K8/H2</f>
-        <v>24.083333333333332</v>
+        <v>25.181818181818183</v>
       </c>
       <c r="M8" s="107">
         <f t="shared" si="3"/>
-        <v>1.2065217391304348</v>
+        <v>1.2058823529411764</v>
       </c>
       <c r="N8" s="13">
         <f t="shared" si="4"/>
-        <v>1.8097826086956526</v>
+        <v>1.8088235294117645</v>
       </c>
       <c r="O8" s="88"/>
     </row>
@@ -3725,38 +3725,38 @@
         <v>600</v>
       </c>
       <c r="F9" s="11">
-        <f>4+7+6+6+11+2+9+6+2+10+1+5</f>
-        <v>69</v>
+        <f>4+7+6+6+11+2+9+6+2+10+1+5+6</f>
+        <v>75</v>
       </c>
       <c r="G9" s="50">
         <f t="shared" si="0"/>
-        <v>0.115</v>
+        <v>0.125</v>
       </c>
       <c r="H9" s="11">
         <v>575</v>
       </c>
       <c r="I9" s="11">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="J9" s="50">
         <f t="shared" si="2"/>
-        <v>0.12521739130434784</v>
+        <v>0.13391304347826086</v>
       </c>
       <c r="K9" s="11">
         <f t="shared" si="5"/>
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="L9" s="93">
         <f>K9/H2</f>
-        <v>41.916666666666664</v>
+        <v>45.272727272727273</v>
       </c>
       <c r="M9" s="107">
         <f t="shared" si="3"/>
-        <v>1.0434782608695652</v>
+        <v>1.0266666666666666</v>
       </c>
       <c r="N9" s="13">
         <f t="shared" si="4"/>
-        <v>1.0888468809073724</v>
+        <v>1.0713043478260869</v>
       </c>
       <c r="O9" s="88"/>
     </row>
@@ -3795,7 +3795,7 @@
       </c>
       <c r="L10" s="93">
         <f>K10/H2</f>
-        <v>45.833333333333336</v>
+        <v>50</v>
       </c>
       <c r="M10" s="107" t="e">
         <f t="shared" si="3"/>
@@ -3824,38 +3824,38 @@
         <v>200</v>
       </c>
       <c r="F11" s="11">
-        <f>2+7+1+6+5+2+4+4+4+4+1</f>
-        <v>40</v>
+        <f>2+7+1+6+5+2+4+4+4+4+1+4</f>
+        <v>44</v>
       </c>
       <c r="G11" s="50">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="H11" s="11">
         <v>3000</v>
       </c>
       <c r="I11" s="11">
-        <v>736</v>
+        <v>1030</v>
       </c>
       <c r="J11" s="50">
         <f t="shared" si="2"/>
-        <v>0.24533333333333332</v>
+        <v>0.34333333333333332</v>
       </c>
       <c r="K11" s="11">
         <f t="shared" si="5"/>
-        <v>2264</v>
+        <v>1970</v>
       </c>
       <c r="L11" s="93">
         <f>K11/H2</f>
-        <v>188.66666666666666</v>
+        <v>179.09090909090909</v>
       </c>
       <c r="M11" s="107">
         <f t="shared" si="3"/>
-        <v>18.399999999999999</v>
+        <v>23.40909090909091</v>
       </c>
       <c r="N11" s="13">
         <f t="shared" si="4"/>
-        <v>1.2266666666666666</v>
+        <v>1.5606060606060606</v>
       </c>
       <c r="O11" s="88"/>
     </row>
@@ -3898,7 +3898,7 @@
       </c>
       <c r="L12" s="93">
         <f>K12/H2</f>
-        <v>33.833333333333336</v>
+        <v>36.909090909090907</v>
       </c>
       <c r="M12" s="10">
         <f t="shared" si="3"/>
@@ -3949,7 +3949,7 @@
       </c>
       <c r="L13" s="93">
         <f>K13/H2</f>
-        <v>35.583333333333336</v>
+        <v>38.81818181818182</v>
       </c>
       <c r="M13" s="10">
         <f t="shared" si="3"/>
@@ -3996,7 +3996,7 @@
       </c>
       <c r="L14" s="93">
         <f>K14/H2</f>
-        <v>37.5</v>
+        <v>40.909090909090907</v>
       </c>
       <c r="M14" s="10" t="e">
         <f t="shared" si="3"/>
@@ -4158,11 +4158,11 @@
       </c>
       <c r="F18" s="33">
         <f>SUM(F5:F17)</f>
-        <v>979</v>
+        <v>1022</v>
       </c>
       <c r="G18" s="58">
         <f t="shared" si="0"/>
-        <v>0.17482142857142857</v>
+        <v>0.1825</v>
       </c>
       <c r="H18" s="33">
         <f>SUM(H5:H17)</f>
@@ -4170,23 +4170,23 @@
       </c>
       <c r="I18" s="33">
         <f>SUM(I5:I17)</f>
-        <v>1847</v>
+        <v>2176</v>
       </c>
       <c r="J18" s="102">
         <f>I18/H18</f>
-        <v>0.23603833865814697</v>
+        <v>0.27808306709265174</v>
       </c>
       <c r="K18" s="34">
         <f t="shared" si="5"/>
-        <v>5978</v>
+        <v>5649</v>
       </c>
       <c r="L18" s="36">
         <f>K18/H2</f>
-        <v>498.16666666666669</v>
+        <v>513.5454545454545</v>
       </c>
       <c r="M18" s="63">
         <f>I18/F18</f>
-        <v>1.8866189989785496</v>
+        <v>2.1291585127201564</v>
       </c>
       <c r="N18" s="36" t="e">
         <f>AVERAGE(N5:N13)</f>
@@ -4759,11 +4759,11 @@
       </c>
       <c r="F30" s="20">
         <f t="shared" ref="F30:I30" si="16">+F29+F24+F18</f>
-        <v>1180</v>
+        <v>1223</v>
       </c>
       <c r="G30" s="67">
         <f t="shared" si="0"/>
-        <v>0.19504132231404958</v>
+        <v>0.20214876033057852</v>
       </c>
       <c r="H30" s="68">
         <f t="shared" si="16"/>
@@ -4771,15 +4771,15 @@
       </c>
       <c r="I30" s="69">
         <f t="shared" si="16"/>
-        <v>2126</v>
+        <v>2455</v>
       </c>
       <c r="J30" s="70">
         <f>I30/H30</f>
-        <v>0.16576998050682262</v>
+        <v>0.19142300194931774</v>
       </c>
       <c r="K30" s="69">
         <f t="shared" si="5"/>
-        <v>10699</v>
+        <v>10370</v>
       </c>
       <c r="L30" s="71" t="e">
         <f t="shared" si="11"/>
@@ -4787,7 +4787,7 @@
       </c>
       <c r="M30" s="72">
         <f>I30/F30</f>
-        <v>1.8016949152542372</v>
+        <v>2.0073589533932954</v>
       </c>
       <c r="N30" s="22" t="e">
         <f>AVERAGE(N29,N18,N24)</f>

--- a/Sep_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
+++ b/Sep_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC3B6DE4-AD41-4187-A154-91B2EF74A5CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76BE53DA-9EC1-45BA-AB7E-37FEDD814FC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1629,7 +1629,7 @@
     </row>
     <row r="2" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D2" s="73">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="E2" s="117" t="s">
         <v>2</v>
@@ -1738,57 +1738,57 @@
         <v>50</v>
       </c>
       <c r="F4" s="11">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G4" s="50">
         <f t="shared" ref="G4:G28" si="0">F4/E4</f>
-        <v>0.08</v>
+        <v>0.24</v>
       </c>
       <c r="H4" s="11">
         <v>40</v>
       </c>
       <c r="I4" s="11">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J4" s="50">
         <f t="shared" ref="J4:J11" si="1">I4/H4</f>
-        <v>0.1</v>
+        <v>0.27500000000000002</v>
       </c>
       <c r="K4" s="11">
         <f t="shared" ref="K4:L11" si="2">I4/F4</f>
-        <v>1</v>
+        <v>0.91666666666666663</v>
       </c>
       <c r="L4" s="11">
         <f t="shared" si="2"/>
-        <v>1.25</v>
+        <v>1.1458333333333335</v>
       </c>
       <c r="M4" s="11">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="N4" s="74">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="O4" s="50">
         <f t="shared" ref="O4:O11" si="3">N4/M4</f>
-        <v>0.91304347826086951</v>
+        <v>1</v>
       </c>
       <c r="P4" s="11">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="Q4" s="74">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="R4" s="50">
         <f t="shared" ref="R4:R11" si="4">Q4/P4</f>
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="S4" s="11">
         <f t="shared" ref="S4:T11" si="5">Q4/N4</f>
-        <v>0.5714285714285714</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="T4" s="11">
         <f t="shared" si="5"/>
-        <v>0.8761904761904763</v>
+        <v>1</v>
       </c>
       <c r="U4" s="92"/>
     </row>
@@ -1809,11 +1809,11 @@
         <v>50</v>
       </c>
       <c r="F5" s="11">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G5" s="50">
         <f t="shared" si="0"/>
-        <v>0.24</v>
+        <v>0.4</v>
       </c>
       <c r="H5" s="11">
         <v>30</v>
@@ -1827,39 +1827,39 @@
       </c>
       <c r="K5" s="11">
         <f t="shared" si="2"/>
-        <v>0.58333333333333337</v>
+        <v>0.35</v>
       </c>
       <c r="L5" s="11">
         <f t="shared" si="2"/>
-        <v>0.97222222222222232</v>
+        <v>0.58333333333333326</v>
       </c>
       <c r="M5" s="11">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="N5" s="74">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="O5" s="50">
         <f t="shared" si="3"/>
-        <v>0.95454545454545459</v>
+        <v>0.92307692307692313</v>
       </c>
       <c r="P5" s="11">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="Q5" s="74">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="R5" s="50">
         <f t="shared" si="4"/>
-        <v>0.82352941176470584</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="S5" s="11">
         <f t="shared" si="5"/>
-        <v>0.66666666666666663</v>
+        <v>0.5</v>
       </c>
       <c r="T5" s="11">
         <f t="shared" si="5"/>
-        <v>0.86274509803921562</v>
+        <v>0.92857142857142849</v>
       </c>
       <c r="U5" s="92"/>
     </row>
@@ -1880,45 +1880,45 @@
         <v>50</v>
       </c>
       <c r="F6" s="11">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G6" s="50">
         <f t="shared" si="0"/>
-        <v>0.14000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="H6" s="11">
         <v>25</v>
       </c>
       <c r="I6" s="11">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J6" s="50">
         <f t="shared" si="1"/>
-        <v>0.32</v>
+        <v>0.2</v>
       </c>
       <c r="K6" s="11">
         <f t="shared" si="2"/>
-        <v>1.1428571428571428</v>
+        <v>1.25</v>
       </c>
       <c r="L6" s="11">
         <f t="shared" si="2"/>
-        <v>2.2857142857142856</v>
+        <v>2.5</v>
       </c>
       <c r="M6" s="11">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N6" s="74">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O6" s="50">
         <f t="shared" si="3"/>
-        <v>0.8571428571428571</v>
+        <v>0.75</v>
       </c>
       <c r="P6" s="11">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q6" s="74">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R6" s="50">
         <f t="shared" si="4"/>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="T6" s="11">
         <f t="shared" si="5"/>
-        <v>0.875</v>
+        <v>1</v>
       </c>
       <c r="U6" s="92"/>
     </row>
@@ -1951,199 +1951,199 @@
         <v>50</v>
       </c>
       <c r="F7" s="11">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G7" s="50">
         <f t="shared" si="0"/>
-        <v>0.22</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="H7" s="11">
         <v>30</v>
       </c>
       <c r="I7" s="11">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J7" s="50">
         <f t="shared" si="1"/>
-        <v>0.43333333333333335</v>
+        <v>0.4</v>
       </c>
       <c r="K7" s="11">
         <f t="shared" si="2"/>
-        <v>1.1818181818181819</v>
+        <v>1.7142857142857142</v>
       </c>
       <c r="L7" s="11">
         <f t="shared" si="2"/>
-        <v>1.9696969696969697</v>
+        <v>2.8571428571428572</v>
       </c>
       <c r="M7" s="11">
+        <v>0</v>
+      </c>
+      <c r="N7" s="74">
+        <v>0</v>
+      </c>
+      <c r="O7" s="50" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P7" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="74">
+        <v>0</v>
+      </c>
+      <c r="R7" s="50" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S7" s="11" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T7" s="11" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U7" s="92"/>
+    </row>
+    <row r="8" spans="1:26" ht="17" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A8" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="E8" s="11">
+        <v>50</v>
+      </c>
+      <c r="F8" s="11">
+        <v>0</v>
+      </c>
+      <c r="G8" s="50">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H8" s="11">
+        <v>20</v>
+      </c>
+      <c r="I8" s="11">
+        <v>0</v>
+      </c>
+      <c r="J8" s="50">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K8" s="11" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L8" s="11" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M8" s="11">
+        <v>5</v>
+      </c>
+      <c r="N8" s="74">
         <v>4</v>
       </c>
-      <c r="N7" s="74">
+      <c r="O8" s="50">
+        <f t="shared" si="3"/>
+        <v>0.8</v>
+      </c>
+      <c r="P8" s="11">
+        <v>7</v>
+      </c>
+      <c r="Q8" s="74">
+        <v>6</v>
+      </c>
+      <c r="R8" s="50">
+        <f t="shared" si="4"/>
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="S8" s="11">
+        <f t="shared" si="5"/>
+        <v>1.5</v>
+      </c>
+      <c r="T8" s="11">
+        <f t="shared" si="5"/>
+        <v>1.0714285714285714</v>
+      </c>
+      <c r="U8" s="92"/>
+    </row>
+    <row r="9" spans="1:26" ht="17" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="11">
+        <v>25</v>
+      </c>
+      <c r="F9" s="11">
+        <v>7</v>
+      </c>
+      <c r="G9" s="50">
+        <f t="shared" si="0"/>
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="H9" s="11">
+        <v>0</v>
+      </c>
+      <c r="I9" s="11">
+        <v>78</v>
+      </c>
+      <c r="J9" s="50" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K9" s="11">
+        <f t="shared" si="2"/>
+        <v>11.142857142857142</v>
+      </c>
+      <c r="L9" s="11" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M9" s="11">
         <v>4</v>
       </c>
-      <c r="O7" s="50">
+      <c r="N9" s="74">
+        <v>4</v>
+      </c>
+      <c r="O9" s="50">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="P7" s="11">
-        <v>7</v>
-      </c>
-      <c r="Q7" s="74">
-        <v>3</v>
-      </c>
-      <c r="R7" s="50">
-        <f t="shared" si="4"/>
-        <v>0.42857142857142855</v>
-      </c>
-      <c r="S7" s="11">
-        <f t="shared" si="5"/>
-        <v>0.75</v>
-      </c>
-      <c r="T7" s="11">
-        <f t="shared" si="5"/>
-        <v>0.42857142857142855</v>
-      </c>
-      <c r="U7" s="92"/>
-    </row>
-    <row r="8" spans="1:26" ht="17" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A8" s="28" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="39" t="s">
-        <v>66</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="E8" s="11">
+      <c r="P9" s="11">
         <v>50</v>
       </c>
-      <c r="F8" s="11">
-        <v>8</v>
-      </c>
-      <c r="G8" s="50">
-        <f t="shared" si="0"/>
-        <v>0.16</v>
-      </c>
-      <c r="H8" s="11">
-        <v>20</v>
-      </c>
-      <c r="I8" s="11">
-        <v>9</v>
-      </c>
-      <c r="J8" s="50">
-        <f t="shared" si="1"/>
-        <v>0.45</v>
-      </c>
-      <c r="K8" s="11">
-        <f t="shared" si="2"/>
-        <v>1.125</v>
-      </c>
-      <c r="L8" s="11">
-        <f t="shared" si="2"/>
-        <v>2.8125</v>
-      </c>
-      <c r="M8" s="11">
-        <v>12</v>
-      </c>
-      <c r="N8" s="74">
-        <v>1</v>
-      </c>
-      <c r="O8" s="50">
-        <f t="shared" si="3"/>
-        <v>8.3333333333333329E-2</v>
-      </c>
-      <c r="P8" s="11">
-        <v>7</v>
-      </c>
-      <c r="Q8" s="74">
-        <v>4</v>
-      </c>
-      <c r="R8" s="50">
-        <f t="shared" si="4"/>
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="S8" s="11">
-        <f t="shared" si="5"/>
-        <v>4</v>
-      </c>
-      <c r="T8" s="11">
-        <f t="shared" si="5"/>
-        <v>6.8571428571428568</v>
-      </c>
-      <c r="U8" s="92"/>
-    </row>
-    <row r="9" spans="1:26" ht="17" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A9" s="28" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="39" t="s">
-        <v>66</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9" s="11">
-        <v>25</v>
-      </c>
-      <c r="F9" s="11">
-        <v>3</v>
-      </c>
-      <c r="G9" s="50">
-        <f t="shared" si="0"/>
-        <v>0.12</v>
-      </c>
-      <c r="H9" s="11">
-        <v>0</v>
-      </c>
-      <c r="I9" s="11">
-        <v>20</v>
-      </c>
-      <c r="J9" s="50" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K9" s="11">
-        <f t="shared" si="2"/>
-        <v>6.666666666666667</v>
-      </c>
-      <c r="L9" s="11" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M9" s="11">
-        <v>5</v>
-      </c>
-      <c r="N9" s="74">
-        <v>93</v>
-      </c>
-      <c r="O9" s="50">
-        <f t="shared" si="3"/>
-        <v>18.600000000000001</v>
-      </c>
-      <c r="P9" s="11">
-        <v>3</v>
-      </c>
       <c r="Q9" s="74">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="R9" s="50">
         <f t="shared" si="4"/>
-        <v>1.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="S9" s="11">
         <f t="shared" si="5"/>
-        <v>4.3010752688172046E-2</v>
+        <v>12.5</v>
       </c>
       <c r="T9" s="11">
         <f t="shared" si="5"/>
-        <v>7.1684587813620068E-2</v>
+        <v>1</v>
       </c>
       <c r="U9" s="92"/>
       <c r="Z9">
@@ -2425,11 +2425,11 @@
       </c>
       <c r="F16" s="60">
         <f>SUM(F4:F15)</f>
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="G16" s="89">
         <f t="shared" si="0"/>
-        <v>0.12</v>
+        <v>0.13333333333333333</v>
       </c>
       <c r="H16" s="59">
         <f>SUM(H4:H15)</f>
@@ -2437,15 +2437,15 @@
       </c>
       <c r="I16" s="60">
         <f>SUM(I4:I15)</f>
-        <v>61</v>
+        <v>113</v>
       </c>
       <c r="J16" s="89">
         <f t="shared" ref="J16" si="6">I16/H16</f>
-        <v>0.16712328767123288</v>
+        <v>0.30958904109589042</v>
       </c>
       <c r="K16" s="59">
         <f>I16/F16</f>
-        <v>1.3555555555555556</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="L16" s="62" t="e">
         <f>AVERAGE(L4:L15)</f>
@@ -2453,31 +2453,31 @@
       </c>
       <c r="M16" s="59">
         <f>SUM(M4:M15)</f>
-        <v>73</v>
+        <v>33</v>
       </c>
       <c r="N16" s="60">
         <f>SUM(N4:N15)</f>
-        <v>146</v>
+        <v>30</v>
       </c>
       <c r="O16" s="89">
         <f t="shared" ref="O16" si="7">N16/M16</f>
-        <v>2</v>
+        <v>0.90909090909090906</v>
       </c>
       <c r="P16" s="59">
         <f>SUM(P4:P15)</f>
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="Q16" s="60">
         <f>SUM(Q4:Q15)</f>
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="R16" s="89">
         <f t="shared" ref="R16" si="8">Q16/P16</f>
-        <v>0.75438596491228072</v>
+        <v>0.95945945945945943</v>
       </c>
       <c r="S16" s="59">
         <f>Q16/N16</f>
-        <v>0.29452054794520549</v>
+        <v>2.3666666666666667</v>
       </c>
       <c r="T16" s="62" t="e">
         <f>AVERAGE(T4:T15)</f>
@@ -3284,11 +3284,11 @@
       </c>
       <c r="F28" s="20">
         <f t="shared" ref="F28" si="24">+F27+F22+F16</f>
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="G28" s="21">
         <f t="shared" si="0"/>
-        <v>6.0495867768595044E-2</v>
+        <v>6.2148760330578513E-2</v>
       </c>
       <c r="H28" s="19">
         <f>+H27+H22+H16</f>
@@ -3296,15 +3296,15 @@
       </c>
       <c r="I28" s="20">
         <f t="shared" ref="I28" si="25">+I27+I22+I16</f>
-        <v>228</v>
+        <v>280</v>
       </c>
       <c r="J28" s="21">
         <f t="shared" si="9"/>
-        <v>8.8888888888888892E-2</v>
+        <v>0.10916179337231968</v>
       </c>
       <c r="K28" s="19">
         <f>I28/F28</f>
-        <v>1.2459016393442623</v>
+        <v>1.4893617021276595</v>
       </c>
       <c r="L28" s="22" t="e">
         <f>AVERAGE(L27,L16,L22)</f>
@@ -3312,31 +3312,31 @@
       </c>
       <c r="M28" s="19">
         <f>+M27+M22+M16</f>
-        <v>222</v>
+        <v>182</v>
       </c>
       <c r="N28" s="20">
         <f t="shared" ref="N28" si="26">+N27+N22+N16</f>
-        <v>259</v>
+        <v>143</v>
       </c>
       <c r="O28" s="21">
         <f t="shared" si="11"/>
-        <v>1.1666666666666667</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="P28" s="19">
         <f>+P27+P22+P16</f>
-        <v>296</v>
+        <v>313</v>
       </c>
       <c r="Q28" s="20">
         <f t="shared" ref="Q28" si="27">+Q27+Q22+Q16</f>
-        <v>173</v>
+        <v>201</v>
       </c>
       <c r="R28" s="21">
         <f t="shared" si="12"/>
-        <v>0.58445945945945943</v>
+        <v>0.64217252396166136</v>
       </c>
       <c r="S28" s="19">
         <f>Q28/N28</f>
-        <v>0.66795366795366795</v>
+        <v>1.4055944055944056</v>
       </c>
       <c r="T28" s="22" t="e">
         <f>AVERAGE(T27,T16,T22)</f>
@@ -3413,22 +3413,22 @@
         <v>26</v>
       </c>
       <c r="F2" s="79">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G2" s="80">
         <f>+F2/E2</f>
-        <v>0.57692307692307687</v>
+        <v>0.61538461538461542</v>
       </c>
       <c r="H2" s="81">
         <f>+E2-F2</f>
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="30.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="47"/>
       <c r="B3" s="47"/>
       <c r="D3" s="82">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="E3" s="122" t="s">
         <v>31</v>
@@ -3515,34 +3515,34 @@
         <v>600</v>
       </c>
       <c r="F5" s="7">
-        <f>5+36+19+15+11+19+14+7+13+21+21+21+4</f>
-        <v>206</v>
+        <f>5+36+19+15+11+19+14+7+13+21+21+21+4+7</f>
+        <v>213</v>
       </c>
       <c r="G5" s="66">
         <f t="shared" ref="G5:G30" si="0">F5/E5</f>
-        <v>0.34333333333333332</v>
+        <v>0.35499999999999998</v>
       </c>
       <c r="H5" s="7">
         <v>550</v>
       </c>
       <c r="I5" s="7">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="J5" s="66">
         <f>I5/H5</f>
-        <v>0.37090909090909091</v>
+        <v>0.38181818181818183</v>
       </c>
       <c r="K5" s="7">
         <f t="shared" ref="K5:K7" si="1">H5-I5</f>
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="L5" s="96">
         <f>K5/H2</f>
-        <v>31.454545454545453</v>
+        <v>34</v>
       </c>
       <c r="M5" s="106">
         <f>I5/F5</f>
-        <v>0.99029126213592233</v>
+        <v>0.9859154929577465</v>
       </c>
       <c r="N5" s="9">
         <v>3</v>
@@ -3570,34 +3570,34 @@
         <v>600</v>
       </c>
       <c r="F6" s="11">
-        <f>23+33+16+19+14+20+21+15+9+14+21+12</f>
-        <v>217</v>
+        <f>23+33+16+19+14+20+21+15+9+14+21+12+13</f>
+        <v>230</v>
       </c>
       <c r="G6" s="50">
         <f t="shared" si="0"/>
-        <v>0.36166666666666669</v>
+        <v>0.38333333333333336</v>
       </c>
       <c r="H6" s="11">
         <v>450</v>
       </c>
       <c r="I6" s="11">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="J6" s="50">
         <f t="shared" ref="J6:J28" si="2">I6/H6</f>
-        <v>0.30888888888888888</v>
+        <v>0.32222222222222224</v>
       </c>
       <c r="K6" s="11">
         <f t="shared" si="1"/>
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="L6" s="93">
         <f>K6/H2</f>
-        <v>28.272727272727273</v>
+        <v>30.5</v>
       </c>
       <c r="M6" s="107">
         <f t="shared" ref="M6:M17" si="3">I6/F6</f>
-        <v>0.64055299539170507</v>
+        <v>0.63043478260869568</v>
       </c>
       <c r="N6" s="13">
         <v>3</v>
@@ -3621,38 +3621,38 @@
         <v>600</v>
       </c>
       <c r="F7" s="11">
-        <f>6+16+5+3+11+11+4+9+16+6+7</f>
-        <v>94</v>
+        <f>6+16+5+3+11+11+4+9+16+6+7+3</f>
+        <v>97</v>
       </c>
       <c r="G7" s="50">
         <f t="shared" si="0"/>
-        <v>0.15666666666666668</v>
+        <v>0.16166666666666665</v>
       </c>
       <c r="H7" s="11">
         <v>550</v>
       </c>
       <c r="I7" s="11">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="J7" s="50">
         <f t="shared" si="2"/>
-        <v>0.24727272727272728</v>
+        <v>0.25272727272727274</v>
       </c>
       <c r="K7" s="11">
         <f t="shared" si="1"/>
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="L7" s="93">
         <f>K7/H2</f>
-        <v>37.636363636363633</v>
+        <v>41.1</v>
       </c>
       <c r="M7" s="107">
         <f t="shared" si="3"/>
-        <v>1.446808510638298</v>
+        <v>1.4329896907216495</v>
       </c>
       <c r="N7" s="13">
         <f t="shared" ref="N7:N13" si="4">J7/G7</f>
-        <v>1.5783365570599612</v>
+        <v>1.5632614807872542</v>
       </c>
       <c r="O7" s="88"/>
     </row>
@@ -3696,7 +3696,7 @@
       </c>
       <c r="L8" s="93">
         <f>K8/H2</f>
-        <v>25.181818181818183</v>
+        <v>27.7</v>
       </c>
       <c r="M8" s="107">
         <f t="shared" si="3"/>
@@ -3725,38 +3725,38 @@
         <v>600</v>
       </c>
       <c r="F9" s="11">
-        <f>4+7+6+6+11+2+9+6+2+10+1+5+6</f>
-        <v>75</v>
+        <f>4+7+6+6+11+2+9+6+2+10+1+5+6+4</f>
+        <v>79</v>
       </c>
       <c r="G9" s="50">
         <f t="shared" si="0"/>
-        <v>0.125</v>
+        <v>0.13166666666666665</v>
       </c>
       <c r="H9" s="11">
         <v>575</v>
       </c>
       <c r="I9" s="11">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="J9" s="50">
         <f t="shared" si="2"/>
-        <v>0.13391304347826086</v>
+        <v>0.14434782608695651</v>
       </c>
       <c r="K9" s="11">
         <f t="shared" si="5"/>
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="L9" s="93">
         <f>K9/H2</f>
-        <v>45.272727272727273</v>
+        <v>49.2</v>
       </c>
       <c r="M9" s="107">
         <f t="shared" si="3"/>
-        <v>1.0266666666666666</v>
+        <v>1.0506329113924051</v>
       </c>
       <c r="N9" s="13">
         <f t="shared" si="4"/>
-        <v>1.0713043478260869</v>
+        <v>1.0963126031920749</v>
       </c>
       <c r="O9" s="88"/>
     </row>
@@ -3795,7 +3795,7 @@
       </c>
       <c r="L10" s="93">
         <f>K10/H2</f>
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="M10" s="107" t="e">
         <f t="shared" si="3"/>
@@ -3824,38 +3824,38 @@
         <v>200</v>
       </c>
       <c r="F11" s="11">
-        <f>2+7+1+6+5+2+4+4+4+4+1+4</f>
-        <v>44</v>
+        <f>2+7+1+6+5+2+4+4+4+4+1+4+4</f>
+        <v>48</v>
       </c>
       <c r="G11" s="50">
         <f t="shared" si="0"/>
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="H11" s="11">
         <v>3000</v>
       </c>
       <c r="I11" s="11">
-        <v>1030</v>
+        <v>1080</v>
       </c>
       <c r="J11" s="50">
         <f t="shared" si="2"/>
-        <v>0.34333333333333332</v>
+        <v>0.36</v>
       </c>
       <c r="K11" s="11">
         <f t="shared" si="5"/>
-        <v>1970</v>
+        <v>1920</v>
       </c>
       <c r="L11" s="93">
         <f>K11/H2</f>
-        <v>179.09090909090909</v>
+        <v>192</v>
       </c>
       <c r="M11" s="107">
         <f t="shared" si="3"/>
-        <v>23.40909090909091</v>
+        <v>22.5</v>
       </c>
       <c r="N11" s="13">
         <f t="shared" si="4"/>
-        <v>1.5606060606060606</v>
+        <v>1.5</v>
       </c>
       <c r="O11" s="88"/>
     </row>
@@ -3898,7 +3898,7 @@
       </c>
       <c r="L12" s="93">
         <f>K12/H2</f>
-        <v>36.909090909090907</v>
+        <v>40.6</v>
       </c>
       <c r="M12" s="10">
         <f t="shared" si="3"/>
@@ -3949,7 +3949,7 @@
       </c>
       <c r="L13" s="93">
         <f>K13/H2</f>
-        <v>38.81818181818182</v>
+        <v>42.7</v>
       </c>
       <c r="M13" s="10">
         <f t="shared" si="3"/>
@@ -3996,7 +3996,7 @@
       </c>
       <c r="L14" s="93">
         <f>K14/H2</f>
-        <v>40.909090909090907</v>
+        <v>45</v>
       </c>
       <c r="M14" s="10" t="e">
         <f t="shared" si="3"/>
@@ -4158,11 +4158,11 @@
       </c>
       <c r="F18" s="33">
         <f>SUM(F5:F17)</f>
-        <v>1022</v>
+        <v>1053</v>
       </c>
       <c r="G18" s="58">
         <f t="shared" si="0"/>
-        <v>0.1825</v>
+        <v>0.18803571428571428</v>
       </c>
       <c r="H18" s="33">
         <f>SUM(H5:H17)</f>
@@ -4170,23 +4170,23 @@
       </c>
       <c r="I18" s="33">
         <f>SUM(I5:I17)</f>
-        <v>2176</v>
+        <v>2247</v>
       </c>
       <c r="J18" s="102">
         <f>I18/H18</f>
-        <v>0.27808306709265174</v>
+        <v>0.28715654952076675</v>
       </c>
       <c r="K18" s="34">
         <f t="shared" si="5"/>
-        <v>5649</v>
+        <v>5578</v>
       </c>
       <c r="L18" s="36">
         <f>K18/H2</f>
-        <v>513.5454545454545</v>
+        <v>557.79999999999995</v>
       </c>
       <c r="M18" s="63">
         <f>I18/F18</f>
-        <v>2.1291585127201564</v>
+        <v>2.133903133903134</v>
       </c>
       <c r="N18" s="36" t="e">
         <f>AVERAGE(N5:N13)</f>
@@ -4759,11 +4759,11 @@
       </c>
       <c r="F30" s="20">
         <f t="shared" ref="F30:I30" si="16">+F29+F24+F18</f>
-        <v>1223</v>
+        <v>1254</v>
       </c>
       <c r="G30" s="67">
         <f t="shared" si="0"/>
-        <v>0.20214876033057852</v>
+        <v>0.20727272727272728</v>
       </c>
       <c r="H30" s="68">
         <f t="shared" si="16"/>
@@ -4771,15 +4771,15 @@
       </c>
       <c r="I30" s="69">
         <f t="shared" si="16"/>
-        <v>2455</v>
+        <v>2526</v>
       </c>
       <c r="J30" s="70">
         <f>I30/H30</f>
-        <v>0.19142300194931774</v>
+        <v>0.19695906432748539</v>
       </c>
       <c r="K30" s="69">
         <f t="shared" si="5"/>
-        <v>10370</v>
+        <v>10299</v>
       </c>
       <c r="L30" s="71" t="e">
         <f t="shared" si="11"/>
@@ -4787,7 +4787,7 @@
       </c>
       <c r="M30" s="72">
         <f>I30/F30</f>
-        <v>2.0073589533932954</v>
+        <v>2.0143540669856459</v>
       </c>
       <c r="N30" s="22" t="e">
         <f>AVERAGE(N29,N18,N24)</f>

--- a/Sep_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
+++ b/Sep_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76BE53DA-9EC1-45BA-AB7E-37FEDD814FC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{576A6920-0132-42B4-A077-AFAD6C9EBC3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Today Performance" sheetId="1" r:id="rId1"/>
@@ -3413,22 +3413,22 @@
         <v>26</v>
       </c>
       <c r="F2" s="79">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G2" s="80">
         <f>+F2/E2</f>
-        <v>0.61538461538461542</v>
+        <v>0.65384615384615385</v>
       </c>
       <c r="H2" s="81">
         <f>+E2-F2</f>
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="30.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="47"/>
       <c r="B3" s="47"/>
       <c r="D3" s="82">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="E3" s="122" t="s">
         <v>31</v>
@@ -3515,34 +3515,34 @@
         <v>600</v>
       </c>
       <c r="F5" s="7">
-        <f>5+36+19+15+11+19+14+7+13+21+21+21+4+7</f>
-        <v>213</v>
+        <f>5+36+19+15+11+19+14+7+13+21+21+21+4+7+12</f>
+        <v>225</v>
       </c>
       <c r="G5" s="66">
         <f t="shared" ref="G5:G30" si="0">F5/E5</f>
-        <v>0.35499999999999998</v>
+        <v>0.375</v>
       </c>
       <c r="H5" s="7">
         <v>550</v>
       </c>
       <c r="I5" s="7">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="J5" s="66">
         <f>I5/H5</f>
-        <v>0.38181818181818183</v>
+        <v>0.4018181818181818</v>
       </c>
       <c r="K5" s="7">
         <f t="shared" ref="K5:K7" si="1">H5-I5</f>
-        <v>340</v>
+        <v>329</v>
       </c>
       <c r="L5" s="96">
         <f>K5/H2</f>
-        <v>34</v>
+        <v>36.555555555555557</v>
       </c>
       <c r="M5" s="106">
         <f>I5/F5</f>
-        <v>0.9859154929577465</v>
+        <v>0.98222222222222222</v>
       </c>
       <c r="N5" s="9">
         <v>3</v>
@@ -3570,34 +3570,34 @@
         <v>600</v>
       </c>
       <c r="F6" s="11">
-        <f>23+33+16+19+14+20+21+15+9+14+21+12+13</f>
-        <v>230</v>
+        <f>23+33+16+19+14+20+21+15+9+14+21+12+13+19</f>
+        <v>249</v>
       </c>
       <c r="G6" s="50">
         <f t="shared" si="0"/>
-        <v>0.38333333333333336</v>
+        <v>0.41499999999999998</v>
       </c>
       <c r="H6" s="11">
         <v>450</v>
       </c>
       <c r="I6" s="11">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="J6" s="50">
         <f t="shared" ref="J6:J28" si="2">I6/H6</f>
-        <v>0.32222222222222224</v>
+        <v>0.33111111111111113</v>
       </c>
       <c r="K6" s="11">
         <f t="shared" si="1"/>
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="L6" s="93">
         <f>K6/H2</f>
-        <v>30.5</v>
+        <v>33.444444444444443</v>
       </c>
       <c r="M6" s="107">
         <f t="shared" ref="M6:M17" si="3">I6/F6</f>
-        <v>0.63043478260869568</v>
+        <v>0.59839357429718876</v>
       </c>
       <c r="N6" s="13">
         <v>3</v>
@@ -3621,38 +3621,38 @@
         <v>600</v>
       </c>
       <c r="F7" s="11">
-        <f>6+16+5+3+11+11+4+9+16+6+7+3</f>
-        <v>97</v>
+        <f>6+16+5+3+11+11+4+9+16+6+7+3+3</f>
+        <v>100</v>
       </c>
       <c r="G7" s="50">
         <f t="shared" si="0"/>
-        <v>0.16166666666666665</v>
+        <v>0.16666666666666666</v>
       </c>
       <c r="H7" s="11">
         <v>550</v>
       </c>
       <c r="I7" s="11">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="J7" s="50">
         <f t="shared" si="2"/>
-        <v>0.25272727272727274</v>
+        <v>0.25636363636363635</v>
       </c>
       <c r="K7" s="11">
         <f t="shared" si="1"/>
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="L7" s="93">
         <f>K7/H2</f>
-        <v>41.1</v>
+        <v>45.444444444444443</v>
       </c>
       <c r="M7" s="107">
         <f t="shared" si="3"/>
-        <v>1.4329896907216495</v>
+        <v>1.41</v>
       </c>
       <c r="N7" s="13">
         <f t="shared" ref="N7:N13" si="4">J7/G7</f>
-        <v>1.5632614807872542</v>
+        <v>1.5381818181818181</v>
       </c>
       <c r="O7" s="88"/>
     </row>
@@ -3673,38 +3673,38 @@
         <v>600</v>
       </c>
       <c r="F8" s="11">
-        <f>2+9+17+9+5+4+10+5+11+7+9+4+10</f>
-        <v>102</v>
+        <f>2+9+17+9+5+4+10+5+11+7+9+4+10+3</f>
+        <v>105</v>
       </c>
       <c r="G8" s="50">
         <f t="shared" si="0"/>
-        <v>0.17</v>
+        <v>0.17499999999999999</v>
       </c>
       <c r="H8" s="11">
         <v>400</v>
       </c>
       <c r="I8" s="11">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="J8" s="50">
         <f t="shared" si="2"/>
-        <v>0.3075</v>
+        <v>0.315</v>
       </c>
       <c r="K8" s="11">
         <f t="shared" ref="K8:K30" si="5">H8-I8</f>
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="L8" s="93">
         <f>K8/H2</f>
-        <v>27.7</v>
+        <v>30.444444444444443</v>
       </c>
       <c r="M8" s="107">
         <f t="shared" si="3"/>
-        <v>1.2058823529411764</v>
+        <v>1.2</v>
       </c>
       <c r="N8" s="13">
         <f t="shared" si="4"/>
-        <v>1.8088235294117645</v>
+        <v>1.8</v>
       </c>
       <c r="O8" s="88"/>
     </row>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="L9" s="93">
         <f>K9/H2</f>
-        <v>49.2</v>
+        <v>54.666666666666664</v>
       </c>
       <c r="M9" s="107">
         <f t="shared" si="3"/>
@@ -3795,7 +3795,7 @@
       </c>
       <c r="L10" s="93">
         <f>K10/H2</f>
-        <v>55</v>
+        <v>61.111111111111114</v>
       </c>
       <c r="M10" s="107" t="e">
         <f t="shared" si="3"/>
@@ -3824,38 +3824,38 @@
         <v>200</v>
       </c>
       <c r="F11" s="11">
-        <f>2+7+1+6+5+2+4+4+4+4+1+4+4</f>
-        <v>48</v>
+        <f>2+7+1+6+5+2+4+4+4+4+1+4+4+8</f>
+        <v>56</v>
       </c>
       <c r="G11" s="50">
         <f t="shared" si="0"/>
-        <v>0.24</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="H11" s="11">
         <v>3000</v>
       </c>
       <c r="I11" s="11">
-        <v>1080</v>
+        <v>1159</v>
       </c>
       <c r="J11" s="50">
         <f t="shared" si="2"/>
-        <v>0.36</v>
+        <v>0.38633333333333331</v>
       </c>
       <c r="K11" s="11">
         <f t="shared" si="5"/>
-        <v>1920</v>
+        <v>1841</v>
       </c>
       <c r="L11" s="93">
         <f>K11/H2</f>
-        <v>192</v>
+        <v>204.55555555555554</v>
       </c>
       <c r="M11" s="107">
         <f t="shared" si="3"/>
-        <v>22.5</v>
+        <v>20.696428571428573</v>
       </c>
       <c r="N11" s="13">
         <f t="shared" si="4"/>
-        <v>1.5</v>
+        <v>1.3797619047619045</v>
       </c>
       <c r="O11" s="88"/>
     </row>
@@ -3886,27 +3886,28 @@
         <v>650</v>
       </c>
       <c r="I12" s="11">
-        <v>244</v>
+        <f>244+61</f>
+        <v>305</v>
       </c>
       <c r="J12" s="50">
         <f t="shared" si="2"/>
-        <v>0.37538461538461537</v>
+        <v>0.46923076923076923</v>
       </c>
       <c r="K12" s="11">
         <f t="shared" si="5"/>
-        <v>406</v>
+        <v>345</v>
       </c>
       <c r="L12" s="93">
         <f>K12/H2</f>
-        <v>40.6</v>
+        <v>38.333333333333336</v>
       </c>
       <c r="M12" s="10">
         <f t="shared" si="3"/>
-        <v>1.4352941176470588</v>
+        <v>1.7941176470588236</v>
       </c>
       <c r="N12" s="13">
         <f t="shared" si="4"/>
-        <v>1.3248868778280543</v>
+        <v>1.656108597285068</v>
       </c>
       <c r="O12" s="88"/>
     </row>
@@ -3937,27 +3938,28 @@
         <v>550</v>
       </c>
       <c r="I13" s="11">
-        <v>123</v>
+        <f>123+40</f>
+        <v>163</v>
       </c>
       <c r="J13" s="50">
         <f t="shared" si="2"/>
-        <v>0.22363636363636363</v>
+        <v>0.29636363636363638</v>
       </c>
       <c r="K13" s="11">
         <f t="shared" si="5"/>
-        <v>427</v>
+        <v>387</v>
       </c>
       <c r="L13" s="93">
         <f>K13/H2</f>
-        <v>42.7</v>
+        <v>43</v>
       </c>
       <c r="M13" s="10">
         <f t="shared" si="3"/>
-        <v>1.0884955752212389</v>
+        <v>1.4424778761061947</v>
       </c>
       <c r="N13" s="13">
         <f t="shared" si="4"/>
-        <v>1.1874497184231698</v>
+        <v>1.5736122284794853</v>
       </c>
       <c r="O13" s="88"/>
     </row>
@@ -3977,34 +3979,38 @@
       <c r="E14" s="11">
         <v>600</v>
       </c>
-      <c r="F14" s="11"/>
+      <c r="F14" s="11">
+        <v>95</v>
+      </c>
       <c r="G14" s="50">
         <f t="shared" ref="G14:G16" si="6">F14/E14</f>
-        <v>0</v>
+        <v>0.15833333333333333</v>
       </c>
       <c r="H14" s="11">
         <v>450</v>
       </c>
-      <c r="I14" s="11"/>
+      <c r="I14" s="11">
+        <v>80</v>
+      </c>
       <c r="J14" s="50">
         <f t="shared" ref="J14:J17" si="7">I14/H14</f>
-        <v>0</v>
+        <v>0.17777777777777778</v>
       </c>
       <c r="K14" s="11">
         <f t="shared" si="5"/>
-        <v>450</v>
+        <v>370</v>
       </c>
       <c r="L14" s="93">
         <f>K14/H2</f>
-        <v>45</v>
-      </c>
-      <c r="M14" s="10" t="e">
+        <v>41.111111111111114</v>
+      </c>
+      <c r="M14" s="10">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N14" s="13" t="e">
+        <v>0.84210526315789469</v>
+      </c>
+      <c r="N14" s="13">
         <f t="shared" ref="N14:N17" si="8">J14/G14</f>
-        <v>#DIV/0!</v>
+        <v>1.1228070175438598</v>
       </c>
       <c r="O14" s="88"/>
     </row>
@@ -4129,9 +4135,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L17" s="101" t="e">
+      <c r="L17" s="101">
         <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="M17" s="29" t="e">
         <f t="shared" si="3"/>
@@ -4158,11 +4164,11 @@
       </c>
       <c r="F18" s="33">
         <f>SUM(F5:F17)</f>
-        <v>1053</v>
+        <v>1193</v>
       </c>
       <c r="G18" s="58">
         <f t="shared" si="0"/>
-        <v>0.18803571428571428</v>
+        <v>0.21303571428571427</v>
       </c>
       <c r="H18" s="33">
         <f>SUM(H5:H17)</f>
@@ -4170,23 +4176,23 @@
       </c>
       <c r="I18" s="33">
         <f>SUM(I5:I17)</f>
-        <v>2247</v>
+        <v>2527</v>
       </c>
       <c r="J18" s="102">
         <f>I18/H18</f>
-        <v>0.28715654952076675</v>
+        <v>0.32293929712460062</v>
       </c>
       <c r="K18" s="34">
         <f t="shared" si="5"/>
-        <v>5578</v>
+        <v>5298</v>
       </c>
       <c r="L18" s="36">
         <f>K18/H2</f>
-        <v>557.79999999999995</v>
+        <v>588.66666666666663</v>
       </c>
       <c r="M18" s="63">
         <f>I18/F18</f>
-        <v>2.133903133903134</v>
+        <v>2.1181894383906119</v>
       </c>
       <c r="N18" s="36" t="e">
         <f>AVERAGE(N5:N13)</f>
@@ -4759,11 +4765,11 @@
       </c>
       <c r="F30" s="20">
         <f t="shared" ref="F30:I30" si="16">+F29+F24+F18</f>
-        <v>1254</v>
+        <v>1394</v>
       </c>
       <c r="G30" s="67">
         <f t="shared" si="0"/>
-        <v>0.20727272727272728</v>
+        <v>0.23041322314049587</v>
       </c>
       <c r="H30" s="68">
         <f t="shared" si="16"/>
@@ -4771,15 +4777,15 @@
       </c>
       <c r="I30" s="69">
         <f t="shared" si="16"/>
-        <v>2526</v>
+        <v>2806</v>
       </c>
       <c r="J30" s="70">
         <f>I30/H30</f>
-        <v>0.19695906432748539</v>
+        <v>0.21879142300194931</v>
       </c>
       <c r="K30" s="69">
         <f t="shared" si="5"/>
-        <v>10299</v>
+        <v>10019</v>
       </c>
       <c r="L30" s="71" t="e">
         <f t="shared" si="11"/>
@@ -4787,7 +4793,7 @@
       </c>
       <c r="M30" s="72">
         <f>I30/F30</f>
-        <v>2.0143540669856459</v>
+        <v>2.0129124820659969</v>
       </c>
       <c r="N30" s="22" t="e">
         <f>AVERAGE(N29,N18,N24)</f>

--- a/Sep_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
+++ b/Sep_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{576A6920-0132-42B4-A077-AFAD6C9EBC3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7E02A7F-DB9D-4CBD-84C9-7B63430A8A29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="71">
   <si>
     <t>Booking</t>
   </si>
@@ -233,6 +233,12 @@
   </si>
   <si>
     <t xml:space="preserve">Sohail Traders </t>
+  </si>
+  <si>
+    <t>On Leave</t>
+  </si>
+  <si>
+    <t>Punding</t>
   </si>
 </sst>
 </file>
@@ -3413,22 +3419,22 @@
         <v>26</v>
       </c>
       <c r="F2" s="79">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G2" s="80">
         <f>+F2/E2</f>
-        <v>0.65384615384615385</v>
+        <v>0.69230769230769229</v>
       </c>
       <c r="H2" s="81">
         <f>+E2-F2</f>
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="30.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="47"/>
       <c r="B3" s="47"/>
       <c r="D3" s="82">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="E3" s="122" t="s">
         <v>31</v>
@@ -3515,34 +3521,34 @@
         <v>600</v>
       </c>
       <c r="F5" s="7">
-        <f>5+36+19+15+11+19+14+7+13+21+21+21+4+7+12</f>
-        <v>225</v>
+        <f>5+36+19+15+11+19+14+7+13+21+21+21+4+7+12+11</f>
+        <v>236</v>
       </c>
       <c r="G5" s="66">
         <f t="shared" ref="G5:G30" si="0">F5/E5</f>
-        <v>0.375</v>
+        <v>0.39333333333333331</v>
       </c>
       <c r="H5" s="7">
         <v>550</v>
       </c>
       <c r="I5" s="7">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="J5" s="66">
         <f>I5/H5</f>
-        <v>0.4018181818181818</v>
+        <v>0.40727272727272729</v>
       </c>
       <c r="K5" s="7">
         <f t="shared" ref="K5:K7" si="1">H5-I5</f>
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="L5" s="96">
         <f>K5/H2</f>
-        <v>36.555555555555557</v>
+        <v>40.75</v>
       </c>
       <c r="M5" s="106">
         <f>I5/F5</f>
-        <v>0.98222222222222222</v>
+        <v>0.94915254237288138</v>
       </c>
       <c r="N5" s="9">
         <v>3</v>
@@ -3570,34 +3576,34 @@
         <v>600</v>
       </c>
       <c r="F6" s="11">
-        <f>23+33+16+19+14+20+21+15+9+14+21+12+13+19</f>
-        <v>249</v>
+        <f>23+33+16+19+14+20+21+15+9+14+21+12+13+19+10</f>
+        <v>259</v>
       </c>
       <c r="G6" s="50">
         <f t="shared" si="0"/>
-        <v>0.41499999999999998</v>
+        <v>0.43166666666666664</v>
       </c>
       <c r="H6" s="11">
         <v>450</v>
       </c>
       <c r="I6" s="11">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="J6" s="50">
         <f t="shared" ref="J6:J28" si="2">I6/H6</f>
-        <v>0.33111111111111113</v>
+        <v>0.34444444444444444</v>
       </c>
       <c r="K6" s="11">
         <f t="shared" si="1"/>
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="L6" s="93">
         <f>K6/H2</f>
-        <v>33.444444444444443</v>
+        <v>36.875</v>
       </c>
       <c r="M6" s="107">
         <f t="shared" ref="M6:M17" si="3">I6/F6</f>
-        <v>0.59839357429718876</v>
+        <v>0.59845559845559848</v>
       </c>
       <c r="N6" s="13">
         <v>3</v>
@@ -3621,38 +3627,38 @@
         <v>600</v>
       </c>
       <c r="F7" s="11">
-        <f>6+16+5+3+11+11+4+9+16+6+7+3+3</f>
-        <v>100</v>
+        <f>6+16+5+3+11+11+4+9+16+6+7+3+3+6</f>
+        <v>106</v>
       </c>
       <c r="G7" s="50">
         <f t="shared" si="0"/>
-        <v>0.16666666666666666</v>
+        <v>0.17666666666666667</v>
       </c>
       <c r="H7" s="11">
         <v>550</v>
       </c>
       <c r="I7" s="11">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="J7" s="50">
         <f t="shared" si="2"/>
-        <v>0.25636363636363635</v>
+        <v>0.26545454545454544</v>
       </c>
       <c r="K7" s="11">
         <f t="shared" si="1"/>
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="L7" s="93">
         <f>K7/H2</f>
-        <v>45.444444444444443</v>
+        <v>50.5</v>
       </c>
       <c r="M7" s="107">
         <f t="shared" si="3"/>
-        <v>1.41</v>
+        <v>1.3773584905660377</v>
       </c>
       <c r="N7" s="13">
         <f t="shared" ref="N7:N13" si="4">J7/G7</f>
-        <v>1.5381818181818181</v>
+        <v>1.5025728987993139</v>
       </c>
       <c r="O7" s="88"/>
     </row>
@@ -3673,38 +3679,38 @@
         <v>600</v>
       </c>
       <c r="F8" s="11">
-        <f>2+9+17+9+5+4+10+5+11+7+9+4+10+3</f>
-        <v>105</v>
+        <f>2+9+17+9+5+4+10+5+11+7+9+4+10+3+5</f>
+        <v>110</v>
       </c>
       <c r="G8" s="50">
         <f t="shared" si="0"/>
-        <v>0.17499999999999999</v>
+        <v>0.18333333333333332</v>
       </c>
       <c r="H8" s="11">
         <v>400</v>
       </c>
       <c r="I8" s="11">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="J8" s="50">
         <f t="shared" si="2"/>
-        <v>0.315</v>
+        <v>0.34</v>
       </c>
       <c r="K8" s="11">
         <f t="shared" ref="K8:K30" si="5">H8-I8</f>
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="L8" s="93">
         <f>K8/H2</f>
-        <v>30.444444444444443</v>
+        <v>33</v>
       </c>
       <c r="M8" s="107">
         <f t="shared" si="3"/>
-        <v>1.2</v>
+        <v>1.2363636363636363</v>
       </c>
       <c r="N8" s="13">
         <f t="shared" si="4"/>
-        <v>1.8</v>
+        <v>1.8545454545454547</v>
       </c>
       <c r="O8" s="88"/>
     </row>
@@ -3748,7 +3754,7 @@
       </c>
       <c r="L9" s="93">
         <f>K9/H2</f>
-        <v>54.666666666666664</v>
+        <v>61.5</v>
       </c>
       <c r="M9" s="107">
         <f t="shared" si="3"/>
@@ -3758,7 +3764,9 @@
         <f t="shared" si="4"/>
         <v>1.0963126031920749</v>
       </c>
-      <c r="O9" s="88"/>
+      <c r="O9" s="88" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="10" spans="1:20" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A10" s="28" t="s">
@@ -3795,7 +3803,7 @@
       </c>
       <c r="L10" s="93">
         <f>K10/H2</f>
-        <v>61.111111111111114</v>
+        <v>68.75</v>
       </c>
       <c r="M10" s="107" t="e">
         <f t="shared" si="3"/>
@@ -3847,7 +3855,7 @@
       </c>
       <c r="L11" s="93">
         <f>K11/H2</f>
-        <v>204.55555555555554</v>
+        <v>230.125</v>
       </c>
       <c r="M11" s="107">
         <f t="shared" si="3"/>
@@ -3857,7 +3865,9 @@
         <f t="shared" si="4"/>
         <v>1.3797619047619045</v>
       </c>
-      <c r="O11" s="88"/>
+      <c r="O11" s="88" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="12" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A12" s="28" t="s">
@@ -3876,38 +3886,39 @@
         <v>600</v>
       </c>
       <c r="F12" s="11">
-        <v>170</v>
+        <f>170+17+18</f>
+        <v>205</v>
       </c>
       <c r="G12" s="50">
         <f t="shared" si="0"/>
-        <v>0.28333333333333333</v>
+        <v>0.34166666666666667</v>
       </c>
       <c r="H12" s="11">
         <v>650</v>
       </c>
       <c r="I12" s="11">
-        <f>244+61</f>
-        <v>305</v>
+        <f>244+61+22+23</f>
+        <v>350</v>
       </c>
       <c r="J12" s="50">
         <f t="shared" si="2"/>
-        <v>0.46923076923076923</v>
+        <v>0.53846153846153844</v>
       </c>
       <c r="K12" s="11">
         <f t="shared" si="5"/>
-        <v>345</v>
+        <v>300</v>
       </c>
       <c r="L12" s="93">
         <f>K12/H2</f>
-        <v>38.333333333333336</v>
+        <v>37.5</v>
       </c>
       <c r="M12" s="10">
         <f t="shared" si="3"/>
-        <v>1.7941176470588236</v>
+        <v>1.7073170731707317</v>
       </c>
       <c r="N12" s="13">
         <f t="shared" si="4"/>
-        <v>1.656108597285068</v>
+        <v>1.5759849906191368</v>
       </c>
       <c r="O12" s="88"/>
     </row>
@@ -3928,38 +3939,39 @@
         <v>600</v>
       </c>
       <c r="F13" s="11">
-        <v>113</v>
+        <f>113+11+12+10</f>
+        <v>146</v>
       </c>
       <c r="G13" s="50">
         <f t="shared" si="0"/>
-        <v>0.18833333333333332</v>
+        <v>0.24333333333333335</v>
       </c>
       <c r="H13" s="11">
         <v>550</v>
       </c>
       <c r="I13" s="11">
-        <f>123+40</f>
-        <v>163</v>
+        <f>123+40+9+11+8</f>
+        <v>191</v>
       </c>
       <c r="J13" s="50">
         <f t="shared" si="2"/>
-        <v>0.29636363636363638</v>
+        <v>0.34727272727272729</v>
       </c>
       <c r="K13" s="11">
         <f t="shared" si="5"/>
-        <v>387</v>
+        <v>359</v>
       </c>
       <c r="L13" s="93">
         <f>K13/H2</f>
-        <v>43</v>
+        <v>44.875</v>
       </c>
       <c r="M13" s="10">
         <f t="shared" si="3"/>
-        <v>1.4424778761061947</v>
+        <v>1.3082191780821917</v>
       </c>
       <c r="N13" s="13">
         <f t="shared" si="4"/>
-        <v>1.5736122284794853</v>
+        <v>1.4271481942714819</v>
       </c>
       <c r="O13" s="88"/>
     </row>
@@ -3980,37 +3992,39 @@
         <v>600</v>
       </c>
       <c r="F14" s="11">
-        <v>95</v>
+        <f>95+15+8+8+5</f>
+        <v>131</v>
       </c>
       <c r="G14" s="50">
         <f t="shared" ref="G14:G16" si="6">F14/E14</f>
-        <v>0.15833333333333333</v>
+        <v>0.21833333333333332</v>
       </c>
       <c r="H14" s="11">
         <v>450</v>
       </c>
       <c r="I14" s="11">
-        <v>80</v>
+        <f>80+13+11+2+7+6</f>
+        <v>119</v>
       </c>
       <c r="J14" s="50">
         <f t="shared" ref="J14:J17" si="7">I14/H14</f>
-        <v>0.17777777777777778</v>
+        <v>0.26444444444444443</v>
       </c>
       <c r="K14" s="11">
         <f t="shared" si="5"/>
-        <v>370</v>
+        <v>331</v>
       </c>
       <c r="L14" s="93">
         <f>K14/H2</f>
-        <v>41.111111111111114</v>
+        <v>41.375</v>
       </c>
       <c r="M14" s="10">
         <f t="shared" si="3"/>
-        <v>0.84210526315789469</v>
+        <v>0.90839694656488545</v>
       </c>
       <c r="N14" s="13">
         <f t="shared" ref="N14:N17" si="8">J14/G14</f>
-        <v>1.1228070175438598</v>
+        <v>1.2111959287531806</v>
       </c>
       <c r="O14" s="88"/>
     </row>
@@ -4164,11 +4178,11 @@
       </c>
       <c r="F18" s="33">
         <f>SUM(F5:F17)</f>
-        <v>1193</v>
+        <v>1329</v>
       </c>
       <c r="G18" s="58">
         <f t="shared" si="0"/>
-        <v>0.21303571428571427</v>
+        <v>0.23732142857142857</v>
       </c>
       <c r="H18" s="33">
         <f>SUM(H5:H17)</f>
@@ -4176,23 +4190,23 @@
       </c>
       <c r="I18" s="33">
         <f>SUM(I5:I17)</f>
-        <v>2527</v>
+        <v>2663</v>
       </c>
       <c r="J18" s="102">
         <f>I18/H18</f>
-        <v>0.32293929712460062</v>
+        <v>0.34031948881789137</v>
       </c>
       <c r="K18" s="34">
         <f t="shared" si="5"/>
-        <v>5298</v>
+        <v>5162</v>
       </c>
       <c r="L18" s="36">
         <f>K18/H2</f>
-        <v>588.66666666666663</v>
+        <v>645.25</v>
       </c>
       <c r="M18" s="63">
         <f>I18/F18</f>
-        <v>2.1181894383906119</v>
+        <v>2.0037622272385254</v>
       </c>
       <c r="N18" s="36" t="e">
         <f>AVERAGE(N5:N13)</f>
@@ -4765,11 +4779,11 @@
       </c>
       <c r="F30" s="20">
         <f t="shared" ref="F30:I30" si="16">+F29+F24+F18</f>
-        <v>1394</v>
+        <v>1530</v>
       </c>
       <c r="G30" s="67">
         <f t="shared" si="0"/>
-        <v>0.23041322314049587</v>
+        <v>0.2528925619834711</v>
       </c>
       <c r="H30" s="68">
         <f t="shared" si="16"/>
@@ -4777,15 +4791,15 @@
       </c>
       <c r="I30" s="69">
         <f t="shared" si="16"/>
-        <v>2806</v>
+        <v>2942</v>
       </c>
       <c r="J30" s="70">
         <f>I30/H30</f>
-        <v>0.21879142300194931</v>
+        <v>0.22939571150097465</v>
       </c>
       <c r="K30" s="69">
         <f t="shared" si="5"/>
-        <v>10019</v>
+        <v>9883</v>
       </c>
       <c r="L30" s="71" t="e">
         <f t="shared" si="11"/>
@@ -4793,7 +4807,7 @@
       </c>
       <c r="M30" s="72">
         <f>I30/F30</f>
-        <v>2.0129124820659969</v>
+        <v>1.9228758169934641</v>
       </c>
       <c r="N30" s="22" t="e">
         <f>AVERAGE(N29,N18,N24)</f>

--- a/Sep_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
+++ b/Sep_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7E02A7F-DB9D-4CBD-84C9-7B63430A8A29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E15F031-1C8E-400B-A498-488559FACADD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="70">
   <si>
     <t>Booking</t>
   </si>
@@ -235,10 +235,7 @@
     <t xml:space="preserve">Sohail Traders </t>
   </si>
   <si>
-    <t>On Leave</t>
-  </si>
-  <si>
-    <t>Punding</t>
+    <t xml:space="preserve">On Leave </t>
   </si>
 </sst>
 </file>
@@ -1635,7 +1632,7 @@
     </row>
     <row r="2" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D2" s="73">
-        <v>46283</v>
+        <v>46288</v>
       </c>
       <c r="E2" s="117" t="s">
         <v>2</v>
@@ -1744,57 +1741,57 @@
         <v>50</v>
       </c>
       <c r="F4" s="11">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G4" s="50">
         <f t="shared" ref="G4:G28" si="0">F4/E4</f>
-        <v>0.24</v>
+        <v>0.18</v>
       </c>
       <c r="H4" s="11">
         <v>40</v>
       </c>
       <c r="I4" s="11">
-        <v>11</v>
+        <v>14.425000000000001</v>
       </c>
       <c r="J4" s="50">
         <f t="shared" ref="J4:J11" si="1">I4/H4</f>
-        <v>0.27500000000000002</v>
+        <v>0.36062500000000003</v>
       </c>
       <c r="K4" s="11">
         <f t="shared" ref="K4:L11" si="2">I4/F4</f>
-        <v>0.91666666666666663</v>
+        <v>1.6027777777777779</v>
       </c>
       <c r="L4" s="11">
         <f t="shared" si="2"/>
-        <v>1.1458333333333335</v>
+        <v>2.0034722222222223</v>
       </c>
       <c r="M4" s="11">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="N4" s="74">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="O4" s="50">
         <f t="shared" ref="O4:O11" si="3">N4/M4</f>
-        <v>1</v>
+        <v>0.94117647058823528</v>
       </c>
       <c r="P4" s="11">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q4" s="74">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R4" s="50">
         <f t="shared" ref="R4:R11" si="4">Q4/P4</f>
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="S4" s="11">
         <f t="shared" ref="S4:T11" si="5">Q4/N4</f>
-        <v>0.8571428571428571</v>
+        <v>0.1875</v>
       </c>
       <c r="T4" s="11">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0.796875</v>
       </c>
       <c r="U4" s="92"/>
     </row>
@@ -1815,59 +1812,61 @@
         <v>50</v>
       </c>
       <c r="F5" s="11">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G5" s="50">
         <f t="shared" si="0"/>
-        <v>0.4</v>
+        <v>0.42</v>
       </c>
       <c r="H5" s="11">
         <v>30</v>
       </c>
       <c r="I5" s="11">
-        <v>7</v>
+        <v>9.5</v>
       </c>
       <c r="J5" s="50">
         <f t="shared" si="1"/>
-        <v>0.23333333333333334</v>
+        <v>0.31666666666666665</v>
       </c>
       <c r="K5" s="11">
         <f t="shared" si="2"/>
-        <v>0.35</v>
+        <v>0.45238095238095238</v>
       </c>
       <c r="L5" s="11">
         <f t="shared" si="2"/>
-        <v>0.58333333333333326</v>
+        <v>0.75396825396825395</v>
       </c>
       <c r="M5" s="11">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="N5" s="74">
-        <v>12</v>
-      </c>
-      <c r="O5" s="50">
+        <v>0</v>
+      </c>
+      <c r="O5" s="50" t="e">
         <f t="shared" si="3"/>
-        <v>0.92307692307692313</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="P5" s="11">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="74">
-        <v>6</v>
-      </c>
-      <c r="R5" s="50">
+        <v>0</v>
+      </c>
+      <c r="R5" s="50" t="e">
         <f t="shared" si="4"/>
-        <v>0.8571428571428571</v>
-      </c>
-      <c r="S5" s="11">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S5" s="11" t="e">
         <f t="shared" si="5"/>
-        <v>0.5</v>
-      </c>
-      <c r="T5" s="11">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T5" s="11" t="e">
         <f t="shared" si="5"/>
-        <v>0.92857142857142849</v>
-      </c>
-      <c r="U5" s="92"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U5" s="92" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="6" spans="1:26" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A6" s="28" t="s">
@@ -1886,53 +1885,53 @@
         <v>50</v>
       </c>
       <c r="F6" s="11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G6" s="50">
         <f t="shared" si="0"/>
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="H6" s="11">
         <v>25</v>
       </c>
       <c r="I6" s="11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J6" s="50">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="K6" s="11">
         <f t="shared" si="2"/>
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="L6" s="11">
         <f t="shared" si="2"/>
-        <v>2.5</v>
+        <v>2.8000000000000003</v>
       </c>
       <c r="M6" s="11">
         <v>4</v>
       </c>
       <c r="N6" s="74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O6" s="50">
         <f t="shared" si="3"/>
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="P6" s="11">
-        <v>4</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="Q6" s="74">
-        <v>3</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="R6" s="50">
         <f t="shared" si="4"/>
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="S6" s="11">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0.61250000000000004</v>
       </c>
       <c r="T6" s="11">
         <f t="shared" si="5"/>
@@ -1957,57 +1956,57 @@
         <v>50</v>
       </c>
       <c r="F7" s="11">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G7" s="50">
         <f t="shared" si="0"/>
-        <v>0.14000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="H7" s="11">
         <v>30</v>
       </c>
       <c r="I7" s="11">
-        <v>12</v>
+        <v>3.6</v>
       </c>
       <c r="J7" s="50">
         <f t="shared" si="1"/>
-        <v>0.4</v>
+        <v>0.12000000000000001</v>
       </c>
       <c r="K7" s="11">
         <f t="shared" si="2"/>
-        <v>1.7142857142857142</v>
+        <v>0.72</v>
       </c>
       <c r="L7" s="11">
         <f t="shared" si="2"/>
-        <v>2.8571428571428572</v>
+        <v>1.2</v>
       </c>
       <c r="M7" s="11">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N7" s="74">
-        <v>0</v>
-      </c>
-      <c r="O7" s="50" t="e">
+        <v>4</v>
+      </c>
+      <c r="O7" s="50">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
+        <v>0.8</v>
       </c>
       <c r="P7" s="11">
-        <v>0</v>
+        <v>3.375</v>
       </c>
       <c r="Q7" s="74">
-        <v>0</v>
-      </c>
-      <c r="R7" s="50" t="e">
+        <v>2.7749999999999999</v>
+      </c>
+      <c r="R7" s="50">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S7" s="11" t="e">
+        <v>0.82222222222222219</v>
+      </c>
+      <c r="S7" s="11">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T7" s="11" t="e">
+        <v>0.69374999999999998</v>
+      </c>
+      <c r="T7" s="11">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>1.0277777777777777</v>
       </c>
       <c r="U7" s="92"/>
     </row>
@@ -2028,57 +2027,57 @@
         <v>50</v>
       </c>
       <c r="F8" s="11">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G8" s="50">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="H8" s="11">
         <v>20</v>
       </c>
       <c r="I8" s="11">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="J8" s="50">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K8" s="11" t="e">
+        <v>0.215</v>
+      </c>
+      <c r="K8" s="11">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L8" s="11" t="e">
+        <v>0.71666666666666667</v>
+      </c>
+      <c r="L8" s="11">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+        <v>1.7916666666666667</v>
       </c>
       <c r="M8" s="11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N8" s="74">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O8" s="50">
         <f t="shared" si="3"/>
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="P8" s="11">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="Q8" s="74">
-        <v>6</v>
+        <v>8.6</v>
       </c>
       <c r="R8" s="50">
         <f t="shared" si="4"/>
-        <v>0.8571428571428571</v>
+        <v>1</v>
       </c>
       <c r="S8" s="11">
         <f t="shared" si="5"/>
-        <v>1.5</v>
+        <v>1.4333333333333333</v>
       </c>
       <c r="T8" s="11">
         <f t="shared" si="5"/>
-        <v>1.0714285714285714</v>
+        <v>1</v>
       </c>
       <c r="U8" s="92"/>
     </row>
@@ -2099,17 +2098,17 @@
         <v>25</v>
       </c>
       <c r="F9" s="11">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G9" s="50">
         <f t="shared" si="0"/>
-        <v>0.28000000000000003</v>
+        <v>0.04</v>
       </c>
       <c r="H9" s="11">
         <v>0</v>
       </c>
       <c r="I9" s="11">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="J9" s="50" t="e">
         <f t="shared" si="1"/>
@@ -2117,39 +2116,39 @@
       </c>
       <c r="K9" s="11">
         <f t="shared" si="2"/>
-        <v>11.142857142857142</v>
+        <v>40</v>
       </c>
       <c r="L9" s="11" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="M9" s="11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N9" s="74">
         <v>4</v>
       </c>
       <c r="O9" s="50">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>1.3333333333333333</v>
       </c>
       <c r="P9" s="11">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="Q9" s="74">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="R9" s="50">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>1.2264150943396226</v>
       </c>
       <c r="S9" s="11">
         <f t="shared" si="5"/>
-        <v>12.5</v>
+        <v>16.25</v>
       </c>
       <c r="T9" s="11">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0.91981132075471694</v>
       </c>
       <c r="U9" s="92"/>
       <c r="Z9">
@@ -2431,11 +2430,11 @@
       </c>
       <c r="F16" s="60">
         <f>SUM(F4:F15)</f>
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G16" s="89">
         <f t="shared" si="0"/>
-        <v>0.13333333333333333</v>
+        <v>0.12533333333333332</v>
       </c>
       <c r="H16" s="59">
         <f>SUM(H4:H15)</f>
@@ -2443,15 +2442,15 @@
       </c>
       <c r="I16" s="60">
         <f>SUM(I4:I15)</f>
-        <v>113</v>
+        <v>78.824999999999989</v>
       </c>
       <c r="J16" s="89">
         <f t="shared" ref="J16" si="6">I16/H16</f>
-        <v>0.30958904109589042</v>
+        <v>0.21595890410958901</v>
       </c>
       <c r="K16" s="59">
         <f>I16/F16</f>
-        <v>2.2599999999999998</v>
+        <v>1.6771276595744677</v>
       </c>
       <c r="L16" s="62" t="e">
         <f>AVERAGE(L4:L15)</f>
@@ -2459,31 +2458,31 @@
       </c>
       <c r="M16" s="59">
         <f>SUM(M4:M15)</f>
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="N16" s="60">
         <f>SUM(N4:N15)</f>
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="O16" s="89">
         <f t="shared" ref="O16" si="7">N16/M16</f>
-        <v>0.90909090909090906</v>
+        <v>0.97142857142857142</v>
       </c>
       <c r="P16" s="59">
         <f>SUM(P4:P15)</f>
-        <v>74</v>
+        <v>71.424999999999997</v>
       </c>
       <c r="Q16" s="60">
         <f>SUM(Q4:Q15)</f>
-        <v>71</v>
+        <v>81.825000000000003</v>
       </c>
       <c r="R16" s="89">
         <f t="shared" ref="R16" si="8">Q16/P16</f>
-        <v>0.95945945945945943</v>
+        <v>1.1456072803640183</v>
       </c>
       <c r="S16" s="59">
         <f>Q16/N16</f>
-        <v>2.3666666666666667</v>
+        <v>2.4066176470588236</v>
       </c>
       <c r="T16" s="62" t="e">
         <f>AVERAGE(T4:T15)</f>
@@ -3290,11 +3289,11 @@
       </c>
       <c r="F28" s="20">
         <f t="shared" ref="F28" si="24">+F27+F22+F16</f>
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="G28" s="21">
         <f t="shared" si="0"/>
-        <v>6.2148760330578513E-2</v>
+        <v>6.1157024793388429E-2</v>
       </c>
       <c r="H28" s="19">
         <f>+H27+H22+H16</f>
@@ -3302,15 +3301,15 @@
       </c>
       <c r="I28" s="20">
         <f t="shared" ref="I28" si="25">+I27+I22+I16</f>
-        <v>280</v>
+        <v>245.82499999999999</v>
       </c>
       <c r="J28" s="21">
         <f t="shared" si="9"/>
-        <v>0.10916179337231968</v>
+        <v>9.5838206627680306E-2</v>
       </c>
       <c r="K28" s="19">
         <f>I28/F28</f>
-        <v>1.4893617021276595</v>
+        <v>1.3287837837837837</v>
       </c>
       <c r="L28" s="22" t="e">
         <f>AVERAGE(L27,L16,L22)</f>
@@ -3318,31 +3317,31 @@
       </c>
       <c r="M28" s="19">
         <f>+M27+M22+M16</f>
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="N28" s="20">
         <f t="shared" ref="N28" si="26">+N27+N22+N16</f>
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="O28" s="21">
         <f t="shared" si="11"/>
-        <v>0.7857142857142857</v>
+        <v>0.79891304347826086</v>
       </c>
       <c r="P28" s="19">
         <f>+P27+P22+P16</f>
-        <v>313</v>
+        <v>310.42500000000001</v>
       </c>
       <c r="Q28" s="20">
         <f t="shared" ref="Q28" si="27">+Q27+Q22+Q16</f>
-        <v>201</v>
+        <v>211.82499999999999</v>
       </c>
       <c r="R28" s="21">
         <f t="shared" si="12"/>
-        <v>0.64217252396166136</v>
+        <v>0.68237094306193113</v>
       </c>
       <c r="S28" s="19">
         <f>Q28/N28</f>
-        <v>1.4055944055944056</v>
+        <v>1.440986394557823</v>
       </c>
       <c r="T28" s="22" t="e">
         <f>AVERAGE(T27,T16,T22)</f>
@@ -3419,22 +3418,22 @@
         <v>26</v>
       </c>
       <c r="F2" s="79">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G2" s="80">
         <f>+F2/E2</f>
-        <v>0.69230769230769229</v>
+        <v>0.76923076923076927</v>
       </c>
       <c r="H2" s="81">
         <f>+E2-F2</f>
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="30.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="47"/>
       <c r="B3" s="47"/>
       <c r="D3" s="82">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="E3" s="122" t="s">
         <v>31</v>
@@ -3521,34 +3520,34 @@
         <v>600</v>
       </c>
       <c r="F5" s="7">
-        <f>5+36+19+15+11+19+14+7+13+21+21+21+4+7+12+11</f>
-        <v>236</v>
+        <f>5+36+19+15+11+19+14+7+13+21+21+21+4+7+12+11+19+16</f>
+        <v>271</v>
       </c>
       <c r="G5" s="66">
         <f t="shared" ref="G5:G30" si="0">F5/E5</f>
-        <v>0.39333333333333331</v>
+        <v>0.45166666666666666</v>
       </c>
       <c r="H5" s="7">
         <v>550</v>
       </c>
       <c r="I5" s="7">
-        <v>224</v>
+        <v>246.75</v>
       </c>
       <c r="J5" s="66">
         <f>I5/H5</f>
-        <v>0.40727272727272729</v>
+        <v>0.44863636363636361</v>
       </c>
       <c r="K5" s="7">
         <f t="shared" ref="K5:K7" si="1">H5-I5</f>
-        <v>326</v>
+        <v>303.25</v>
       </c>
       <c r="L5" s="96">
         <f>K5/H2</f>
-        <v>40.75</v>
+        <v>50.541666666666664</v>
       </c>
       <c r="M5" s="106">
         <f>I5/F5</f>
-        <v>0.94915254237288138</v>
+        <v>0.91051660516605171</v>
       </c>
       <c r="N5" s="9">
         <v>3</v>
@@ -3576,34 +3575,34 @@
         <v>600</v>
       </c>
       <c r="F6" s="11">
-        <f>23+33+16+19+14+20+21+15+9+14+21+12+13+19+10</f>
-        <v>259</v>
+        <f>23+33+16+19+14+20+21+15+9+14+21+12+13+19+10+18</f>
+        <v>277</v>
       </c>
       <c r="G6" s="50">
         <f t="shared" si="0"/>
-        <v>0.43166666666666664</v>
+        <v>0.46166666666666667</v>
       </c>
       <c r="H6" s="11">
         <v>450</v>
       </c>
       <c r="I6" s="11">
-        <v>155</v>
+        <v>161.80000000000001</v>
       </c>
       <c r="J6" s="50">
         <f t="shared" ref="J6:J28" si="2">I6/H6</f>
-        <v>0.34444444444444444</v>
+        <v>0.35955555555555557</v>
       </c>
       <c r="K6" s="11">
         <f t="shared" si="1"/>
-        <v>295</v>
+        <v>288.2</v>
       </c>
       <c r="L6" s="93">
         <f>K6/H2</f>
-        <v>36.875</v>
+        <v>48.033333333333331</v>
       </c>
       <c r="M6" s="107">
         <f t="shared" ref="M6:M17" si="3">I6/F6</f>
-        <v>0.59845559845559848</v>
+        <v>0.58411552346570406</v>
       </c>
       <c r="N6" s="13">
         <v>3</v>
@@ -3627,38 +3626,38 @@
         <v>600</v>
       </c>
       <c r="F7" s="11">
-        <f>6+16+5+3+11+11+4+9+16+6+7+3+3+6</f>
-        <v>106</v>
+        <f>6+16+5+3+11+11+4+9+16+6+7+3+3+6+7+4</f>
+        <v>117</v>
       </c>
       <c r="G7" s="50">
         <f t="shared" si="0"/>
-        <v>0.17666666666666667</v>
+        <v>0.19500000000000001</v>
       </c>
       <c r="H7" s="11">
         <v>550</v>
       </c>
       <c r="I7" s="11">
-        <v>146</v>
+        <v>154.52500000000001</v>
       </c>
       <c r="J7" s="50">
         <f t="shared" si="2"/>
-        <v>0.26545454545454544</v>
+        <v>0.28095454545454546</v>
       </c>
       <c r="K7" s="11">
         <f t="shared" si="1"/>
-        <v>404</v>
+        <v>395.47500000000002</v>
       </c>
       <c r="L7" s="93">
         <f>K7/H2</f>
-        <v>50.5</v>
+        <v>65.912500000000009</v>
       </c>
       <c r="M7" s="107">
         <f t="shared" si="3"/>
-        <v>1.3773584905660377</v>
+        <v>1.3207264957264957</v>
       </c>
       <c r="N7" s="13">
         <f t="shared" ref="N7:N13" si="4">J7/G7</f>
-        <v>1.5025728987993139</v>
+        <v>1.4407925407925408</v>
       </c>
       <c r="O7" s="88"/>
     </row>
@@ -3679,38 +3678,38 @@
         <v>600</v>
       </c>
       <c r="F8" s="11">
-        <f>2+9+17+9+5+4+10+5+11+7+9+4+10+3+5</f>
-        <v>110</v>
+        <f>2+9+17+9+5+4+10+5+11+7+9+4+10+3+5+7+4</f>
+        <v>121</v>
       </c>
       <c r="G8" s="50">
         <f t="shared" si="0"/>
-        <v>0.18333333333333332</v>
+        <v>0.20166666666666666</v>
       </c>
       <c r="H8" s="11">
         <v>400</v>
       </c>
       <c r="I8" s="11">
-        <v>136</v>
+        <v>149.75</v>
       </c>
       <c r="J8" s="50">
         <f t="shared" si="2"/>
-        <v>0.34</v>
+        <v>0.37437500000000001</v>
       </c>
       <c r="K8" s="11">
         <f t="shared" ref="K8:K30" si="5">H8-I8</f>
-        <v>264</v>
+        <v>250.25</v>
       </c>
       <c r="L8" s="93">
         <f>K8/H2</f>
-        <v>33</v>
+        <v>41.708333333333336</v>
       </c>
       <c r="M8" s="107">
         <f t="shared" si="3"/>
-        <v>1.2363636363636363</v>
+        <v>1.2376033057851239</v>
       </c>
       <c r="N8" s="13">
         <f t="shared" si="4"/>
-        <v>1.8545454545454547</v>
+        <v>1.8564049586776861</v>
       </c>
       <c r="O8" s="88"/>
     </row>
@@ -3731,42 +3730,40 @@
         <v>600</v>
       </c>
       <c r="F9" s="11">
-        <f>4+7+6+6+11+2+9+6+2+10+1+5+6+4</f>
-        <v>79</v>
+        <f>4+7+6+6+11+2+9+6+2+10+1+5+6+4+6</f>
+        <v>85</v>
       </c>
       <c r="G9" s="50">
         <f t="shared" si="0"/>
-        <v>0.13166666666666665</v>
+        <v>0.14166666666666666</v>
       </c>
       <c r="H9" s="11">
         <v>575</v>
       </c>
       <c r="I9" s="11">
-        <v>83</v>
+        <v>91.724999999999994</v>
       </c>
       <c r="J9" s="50">
         <f t="shared" si="2"/>
-        <v>0.14434782608695651</v>
+        <v>0.15952173913043477</v>
       </c>
       <c r="K9" s="11">
         <f t="shared" si="5"/>
-        <v>492</v>
+        <v>483.27499999999998</v>
       </c>
       <c r="L9" s="93">
         <f>K9/H2</f>
-        <v>61.5</v>
+        <v>80.545833333333334</v>
       </c>
       <c r="M9" s="107">
         <f t="shared" si="3"/>
-        <v>1.0506329113924051</v>
+        <v>1.0791176470588235</v>
       </c>
       <c r="N9" s="13">
         <f t="shared" si="4"/>
-        <v>1.0963126031920749</v>
-      </c>
-      <c r="O9" s="88" t="s">
-        <v>69</v>
-      </c>
+        <v>1.1260358056265984</v>
+      </c>
+      <c r="O9" s="88"/>
     </row>
     <row r="10" spans="1:20" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A10" s="28" t="s">
@@ -3792,18 +3789,20 @@
       <c r="H10" s="11">
         <v>550</v>
       </c>
-      <c r="I10" s="11"/>
+      <c r="I10" s="11">
+        <v>1494.5250000000001</v>
+      </c>
       <c r="J10" s="50">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2.717318181818182</v>
       </c>
       <c r="K10" s="11">
         <f t="shared" si="5"/>
-        <v>550</v>
+        <v>-944.52500000000009</v>
       </c>
       <c r="L10" s="93">
         <f>K10/H2</f>
-        <v>68.75</v>
+        <v>-157.42083333333335</v>
       </c>
       <c r="M10" s="107" t="e">
         <f t="shared" si="3"/>
@@ -3832,42 +3831,40 @@
         <v>200</v>
       </c>
       <c r="F11" s="11">
-        <f>2+7+1+6+5+2+4+4+4+4+1+4+4+8</f>
-        <v>56</v>
+        <f>2+7+1+6+5+2+4+4+4+4+1+4+4+8+13+4</f>
+        <v>73</v>
       </c>
       <c r="G11" s="50">
         <f t="shared" si="0"/>
-        <v>0.28000000000000003</v>
+        <v>0.36499999999999999</v>
       </c>
       <c r="H11" s="11">
         <v>3000</v>
       </c>
       <c r="I11" s="11">
-        <v>1159</v>
+        <v>1494.5250000000001</v>
       </c>
       <c r="J11" s="50">
         <f t="shared" si="2"/>
-        <v>0.38633333333333331</v>
+        <v>0.49817500000000003</v>
       </c>
       <c r="K11" s="11">
         <f t="shared" si="5"/>
-        <v>1841</v>
+        <v>1505.4749999999999</v>
       </c>
       <c r="L11" s="93">
         <f>K11/H2</f>
-        <v>230.125</v>
+        <v>250.91249999999999</v>
       </c>
       <c r="M11" s="107">
         <f t="shared" si="3"/>
-        <v>20.696428571428573</v>
+        <v>20.472945205479455</v>
       </c>
       <c r="N11" s="13">
         <f t="shared" si="4"/>
-        <v>1.3797619047619045</v>
-      </c>
-      <c r="O11" s="88" t="s">
-        <v>70</v>
-      </c>
+        <v>1.3648630136986302</v>
+      </c>
+      <c r="O11" s="88"/>
     </row>
     <row r="12" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A12" s="28" t="s">
@@ -3886,39 +3883,39 @@
         <v>600</v>
       </c>
       <c r="F12" s="11">
-        <f>170+17+18</f>
-        <v>205</v>
+        <f>170+17+18+14</f>
+        <v>219</v>
       </c>
       <c r="G12" s="50">
         <f t="shared" si="0"/>
-        <v>0.34166666666666667</v>
+        <v>0.36499999999999999</v>
       </c>
       <c r="H12" s="11">
         <v>650</v>
       </c>
       <c r="I12" s="11">
-        <f>244+61+22+23</f>
-        <v>350</v>
+        <f>244+61+22+23+21</f>
+        <v>371</v>
       </c>
       <c r="J12" s="50">
         <f t="shared" si="2"/>
-        <v>0.53846153846153844</v>
+        <v>0.57076923076923081</v>
       </c>
       <c r="K12" s="11">
         <f t="shared" si="5"/>
-        <v>300</v>
+        <v>279</v>
       </c>
       <c r="L12" s="93">
         <f>K12/H2</f>
-        <v>37.5</v>
+        <v>46.5</v>
       </c>
       <c r="M12" s="10">
         <f t="shared" si="3"/>
-        <v>1.7073170731707317</v>
+        <v>1.6940639269406392</v>
       </c>
       <c r="N12" s="13">
         <f t="shared" si="4"/>
-        <v>1.5759849906191368</v>
+        <v>1.5637513171759749</v>
       </c>
       <c r="O12" s="88"/>
     </row>
@@ -3939,39 +3936,39 @@
         <v>600</v>
       </c>
       <c r="F13" s="11">
-        <f>113+11+12+10</f>
-        <v>146</v>
+        <f>113+11+12+10+10</f>
+        <v>156</v>
       </c>
       <c r="G13" s="50">
         <f t="shared" si="0"/>
-        <v>0.24333333333333335</v>
+        <v>0.26</v>
       </c>
       <c r="H13" s="11">
         <v>550</v>
       </c>
       <c r="I13" s="11">
-        <f>123+40+9+11+8</f>
-        <v>191</v>
+        <f>123+40+9+11+8+8</f>
+        <v>199</v>
       </c>
       <c r="J13" s="50">
         <f t="shared" si="2"/>
-        <v>0.34727272727272729</v>
+        <v>0.36181818181818182</v>
       </c>
       <c r="K13" s="11">
         <f t="shared" si="5"/>
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="L13" s="93">
         <f>K13/H2</f>
-        <v>44.875</v>
+        <v>58.5</v>
       </c>
       <c r="M13" s="10">
         <f t="shared" si="3"/>
-        <v>1.3082191780821917</v>
+        <v>1.2756410256410255</v>
       </c>
       <c r="N13" s="13">
         <f t="shared" si="4"/>
-        <v>1.4271481942714819</v>
+        <v>1.3916083916083914</v>
       </c>
       <c r="O13" s="88"/>
     </row>
@@ -3992,39 +3989,39 @@
         <v>600</v>
       </c>
       <c r="F14" s="11">
-        <f>95+15+8+8+5</f>
-        <v>131</v>
+        <f>95+15+8+8+5+8</f>
+        <v>139</v>
       </c>
       <c r="G14" s="50">
         <f t="shared" ref="G14:G16" si="6">F14/E14</f>
-        <v>0.21833333333333332</v>
+        <v>0.23166666666666666</v>
       </c>
       <c r="H14" s="11">
         <v>450</v>
       </c>
       <c r="I14" s="11">
-        <f>80+13+11+2+7+6</f>
-        <v>119</v>
+        <f>80+13+11+2+7+6+7</f>
+        <v>126</v>
       </c>
       <c r="J14" s="50">
         <f t="shared" ref="J14:J17" si="7">I14/H14</f>
-        <v>0.26444444444444443</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="K14" s="11">
         <f t="shared" si="5"/>
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="L14" s="93">
         <f>K14/H2</f>
-        <v>41.375</v>
+        <v>54</v>
       </c>
       <c r="M14" s="10">
         <f t="shared" si="3"/>
-        <v>0.90839694656488545</v>
+        <v>0.90647482014388492</v>
       </c>
       <c r="N14" s="13">
         <f t="shared" ref="N14:N17" si="8">J14/G14</f>
-        <v>1.2111959287531806</v>
+        <v>1.2086330935251801</v>
       </c>
       <c r="O14" s="88"/>
     </row>
@@ -4178,11 +4175,11 @@
       </c>
       <c r="F18" s="33">
         <f>SUM(F5:F17)</f>
-        <v>1329</v>
+        <v>1459</v>
       </c>
       <c r="G18" s="58">
         <f t="shared" si="0"/>
-        <v>0.23732142857142857</v>
+        <v>0.26053571428571426</v>
       </c>
       <c r="H18" s="33">
         <f>SUM(H5:H17)</f>
@@ -4190,23 +4187,23 @@
       </c>
       <c r="I18" s="33">
         <f>SUM(I5:I17)</f>
-        <v>2663</v>
+        <v>4589.6000000000004</v>
       </c>
       <c r="J18" s="102">
         <f>I18/H18</f>
-        <v>0.34031948881789137</v>
+        <v>0.58653035143769972</v>
       </c>
       <c r="K18" s="34">
         <f t="shared" si="5"/>
-        <v>5162</v>
+        <v>3235.3999999999996</v>
       </c>
       <c r="L18" s="36">
         <f>K18/H2</f>
-        <v>645.25</v>
+        <v>539.23333333333323</v>
       </c>
       <c r="M18" s="63">
         <f>I18/F18</f>
-        <v>2.0037622272385254</v>
+        <v>3.1457162440027417</v>
       </c>
       <c r="N18" s="36" t="e">
         <f>AVERAGE(N5:N13)</f>
@@ -4779,11 +4776,11 @@
       </c>
       <c r="F30" s="20">
         <f t="shared" ref="F30:I30" si="16">+F29+F24+F18</f>
-        <v>1530</v>
+        <v>1660</v>
       </c>
       <c r="G30" s="67">
         <f t="shared" si="0"/>
-        <v>0.2528925619834711</v>
+        <v>0.27438016528925618</v>
       </c>
       <c r="H30" s="68">
         <f t="shared" si="16"/>
@@ -4791,15 +4788,15 @@
       </c>
       <c r="I30" s="69">
         <f t="shared" si="16"/>
-        <v>2942</v>
+        <v>4868.6000000000004</v>
       </c>
       <c r="J30" s="70">
         <f>I30/H30</f>
-        <v>0.22939571150097465</v>
+        <v>0.37961793372319691</v>
       </c>
       <c r="K30" s="69">
         <f t="shared" si="5"/>
-        <v>9883</v>
+        <v>7956.4</v>
       </c>
       <c r="L30" s="71" t="e">
         <f t="shared" si="11"/>
@@ -4807,7 +4804,7 @@
       </c>
       <c r="M30" s="72">
         <f>I30/F30</f>
-        <v>1.9228758169934641</v>
+        <v>2.9328915662650603</v>
       </c>
       <c r="N30" s="22" t="e">
         <f>AVERAGE(N29,N18,N24)</f>

--- a/Sep_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
+++ b/Sep_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E15F031-1C8E-400B-A498-488559FACADD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F28539E4-D28F-4B72-9102-D8AF7C0753DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Today Performance" sheetId="1" r:id="rId1"/>
